--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\지적재조사 통합시스템\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\지적재조사 업무시스템(최종)\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87AB896-DC64-46E4-B1C4-94F7CBA995D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D712829-6628-4C58-9DA3-FAFDAC933A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="질의회신" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="449">
   <si>
     <t>제목</t>
   </si>
@@ -715,9 +715,6 @@
     <t>수정여부</t>
   </si>
   <si>
-    <t>지적재조사경계결정이의신청기각결정취소</t>
-  </si>
-  <si>
     <t>[대법원 2025. 8. 14. 선고 2025두30653 판결]
 【판시사항】
 지적재조사에 관한 특별법 제14조 제1항 제1호에서 정한 ‘지상경계에 대하여 다툼이 없는 경우’의 의미
@@ -765,9 +762,6 @@
 4.  결론
 원심판결을 파기하고, 사건을 다시 심리·판단하도록 원심법원에 환송하기로 하여, 관여 대법관의 일치된 의견으로 주문과 같이 판결한다.
 대법관 마용주(재판장) 노태악 서경환(주심) 신숙희</t>
-  </si>
-  <si>
-    <t>지적재조사사업조장금이의신청기각처분취소청구의소</t>
   </si>
   <si>
     <t>[대전지방법원 2020. 12. 17. 선고 2019구합101143 판결]
@@ -857,9 +851,6 @@
 판사 오영표(재판장) 이혜선 이성열</t>
   </si>
   <si>
-    <t>지적재조사사업조정금지급청구의소</t>
-  </si>
-  <si>
     <t>[대법원 2024. 11. 28. 선고 2024두50711 판결]
 【판시사항】
 금전채권자가 채무자를 상대로 채무 이행을 청구하는 소를 제기한 후 채무자가 자신의 채무를 이행함으로써 원래의 금전채무가 소멸하여 그 범위에서 채권자의 채무이행청구는 기각될 수밖에 없고 채무의 이행지체로 인한 지연손해배상만 남게 된 경우, 지연손해금 산정에 대하여 소송촉진 등에 관한 특례법 제3조의 법정이율을 적용할 수 있는지 여부(소극)
@@ -893,9 +884,6 @@
 3.  결론
 상고를 기각하고 상고비용은 패소자가 부담하도록 하여, 관여 대법관의 일치된 의견으로 주문과 같이 판결한다.
 대법관 서경환(재판장) 신숙희 노경필(주심)</t>
-  </si>
-  <si>
-    <t>지적재조사사업조정금이의신청기각처분취소청구의소</t>
   </si>
   <si>
     <t>대법원 2022. 3. 17. 선고 2021두53894 판결
@@ -955,9 +943,6 @@
 (출처 : 대법원 2022. 3. 17. 선고 2021두53894 판결 | 사법정보공개포털 판례)</t>
   </si>
   <si>
-    <t>지적재조사조정금부과처분취소</t>
-  </si>
-  <si>
     <t>서울고등법원 (인천) 2025. 8. 19. 선고 2025누10078
 사건(인천)2025누10078 지적재조사조정금부과처분취소
 원고,항소인A
@@ -994,9 +979,6 @@
 3. 결론
 제1심판결은 정당하다. 원고의 항소를 기각한다.
 판사 정승규(재판장) 여한울 신재호</t>
-  </si>
-  <si>
-    <t>지적재조사 책임수행기관 지정·위탁 및 지정요건 조항의 위헌 여부</t>
   </si>
   <si>
     <t>헌법재판소 2025. 7. 17. 선고 2021헌마961
@@ -1103,9 +1085,6 @@
 재판관 김형두(재판장) 정정미 정형식 김복형 조한창 정계선 마은혁</t>
   </si>
   <si>
-    <t>지적재조사사업조정금부과처분취소소송</t>
-  </si>
-  <si>
     <t>부산고등법원 2025. 7. 11. 선고 2024누22426
 사건2024누22426 지적재조사사업 조정금 부과처분 취소소송
 원고,항소인A
@@ -1128,9 +1107,6 @@
 2. 결론
 이 사건 소는 부적법하므로 각하하여야 한다. 제1심판결은 이와 결론을 같이하여 정당하다. 따라서 원고의 항소는 이유 없으므로 이를 기각하기로 하여, 주문과 같이 판결한다.
 판사 박준용(재판장) 정현수 배인영</t>
-  </si>
-  <si>
-    <t>지적재조사 경계결정 이의신청 기각결정 취소 청구</t>
   </si>
   <si>
     <t>광주고등법원 2025. 6. 26. 선고 2024누12800
@@ -1209,9 +1185,6 @@
 판사 양영희(재판장) 이호산 황진희</t>
   </si>
   <si>
-    <t>경계결정처분취소</t>
-  </si>
-  <si>
     <t>대구지방법원 2021. 7. 15. 선고 2021구합20919
 사건2021구합20919 경계결정처분취소
 원고A
@@ -1242,9 +1215,6 @@
 3. 결론
 원고의 청구는 이유 있으므로 이를 인용한다.
 판사 이진관(재판장) 박가연 이도경</t>
-  </si>
-  <si>
-    <t>지적재조사경계확정처분취소청구</t>
   </si>
   <si>
     <t>2021. 4. 21. 선고 2020구합24655
@@ -1293,9 +1263,6 @@
 판사 차경환(재판장) 한대광 이기웅</t>
   </si>
   <si>
-    <t>지적재조사경계결정처분취소청구의소</t>
-  </si>
-  <si>
     <t>춘천지방법원 강릉지원 2023. 12. 21. 선고 2023구합30421
 사건2023구합30421 지적재조사 경계결정처분취소 청구의 소
 원고A
@@ -1377,9 +1344,6 @@
 판사 민지현(재판장) 김찬년 류의준</t>
   </si>
   <si>
-    <t>지적재조사경계확정처분취소등</t>
-  </si>
-  <si>
     <t>광주고등법원 2016. 11. 17. 선고 2016누4194
 사건2016누4194 지적재조사경계확정처분취소 등
 원고,항소인A
@@ -1417,9 +1381,6 @@
 3. 결론
 그렇다면 이 사건 소는 부적법하여 각하하여야 할 것인바, 제1심 판결은 이와 결론을 같이 하여 정당하므로 원고의 항소를 기각하기로 하여, 주문과 같이 판결한다.
 판사 이창한(재판장) 김호석 김성준</t>
-  </si>
-  <si>
-    <t>경계결정이의신청의결처분취소</t>
   </si>
   <si>
     <t>부산고등법원 창원제1행정부 판결
@@ -1635,9 +1596,6 @@
 판사 김태규(재판장) 안재훈 김동석</t>
   </si>
   <si>
-    <t>경계결정처분취소 청구의 소</t>
-  </si>
-  <si>
     <t>광주지방법원 제1행정부 판결
 사건2023구합13814 경계결정처분취소 청구의 소
 원고1. A
@@ -1677,13 +1635,6 @@
 5. 결론
 그렇다면 원고들의 청구는 이유 있으므로 이를 인용하기로 하여 주문과 같이 판결한다.
 판사 박상현(재판장) 김민석 김준석</t>
-  </si>
-  <si>
-    <t>지적재조사경계결정처분취소</t>
-  </si>
-  <si>
-    <t>지구지적재조사사업에의한사건토지의손실보상금과지적도회복</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>【질의회신집 5p】
@@ -8753,9 +8704,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>지적재조사사업예정경계의무효확인및취소</t>
-  </si>
-  <si>
     <t>전주지방법원 제1-2 행정부 판결
 사건2023구합12207 2021년도 지적재조사사업 예정경계의 무효확인 및 취소
 원고A
@@ -8803,9 +8751,6 @@
 원고의 주위적 청구는 이유 있으므로 이를 인용하기로 하여 주문과 같이 판결한다(원고의 주위적 청구를 인용하는 이상 예비적 청구에 관하여는 따로 판단하지 아니하고, 원고의 2024. 9. 21.자 변론재개신청 역시 받아들이지 아니한다).
 판사 김선영(재판장) 박세황 이동진</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지적재조사경계결정이의신청결정처분무효확인등</t>
   </si>
   <si>
     <t>제주지방법원 제1행정부 판결
@@ -8895,10 +8840,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>토지경계결정취소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>의정부지방법원 제1행정부 판결
 사건2020구합11133 토지경계결정취소
 원고1. A
@@ -8952,10 +8893,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>경계결정처분취소청구의소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>대구지방법원 제1행정부 판결
 사건2020구합24884 경계결정처분 취소청구의 소
 원고A
@@ -9004,10 +8941,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>지적재조사경계결정처분취소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>대전지방법원 제2행정부 판결
 사건2022구합615 지적재조사경계결정처분취소
 원고A
@@ -9044,12 +8977,732 @@
 판사 박현행(재판장) 장태관 박서우</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>지적재조사경계결정이의신청기각결정취소(2025두30653)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조장금이의신청기각처분취소청구의소(2019구합101143)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조정금지급청구의소(2024두50711)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조정금이의신청기각처분취소청구의소(2021두53894)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분취소(2025누10078)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사 책임수행기관 지정·위탁 및 지정요건 조항의 위헌 여부(2021헌마961)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조정금부과처분취소소송(2024누22426)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사 경계결정 이의신청 기각결정 취소 청구(2024누12800)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정처분취소(2021구합20919)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계확정처분취소청구(2020구합24655)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계결정처분취소청구의소(2023구합30421)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계결정이의신청기각결정취소(2024누520)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계확정처분취소등(2016누4194)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정이의신청의결처분취소(2018누11091)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정처분취소(2021구합603)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계결정이의신청기각결정취소(2018구합52745)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정처분취소(2018구합5905)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정처분취소 청구의 소(2023구합13814)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계확정처분취소등(2023누11260)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지적재조사경계결정처분취소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>24010)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경계결정처분취소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구합67118)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구지적재조사사업에의한사건토지의손실보상금과지적도회복(2022구합103125)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지적재조사사업예정경계의무효확인및취소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구합12207)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지적재조사경계결정이의신청결정처분무효확인등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구합5654)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토지경계결정취소(2020구합11133)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계결정처분취소청구의소(2020구합24884)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사경계결정처분취소(2022구합615)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금이의신청결과통지처분취소(2024구합51381)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천지방법원 제2행정부 판결
+사건2024구합51381 지적재조사 조정금 이의신청 결과통지처분취소
+원고1. A
+2.B
+원고들 소송대리인 법무법인 지상
+담당변호사 김선하, 이정준
+피고인천광역시 중구청장
+변론종결2024. 10. 11.
+판결선고2024. 11. 8.
+주 문
+1. 원고들의 청구를 모두 기각한다.
+2. 소송비용은 원고들이 부담한다.
+청구취지
+피고가 2023. 12. 8. 원고들에게 각 한 13,992,500원의 C지구지적재조사 조정금 이의신청결과통지처분을 취소한다.
+이 유
+1. 처분의 경위
+가. 피고는 원고들 소유의 인천 중구 D, E, F 토지를 포함하여 그 일원에 소재하는 토지에 관하여 지적재조사사업(이하 '이 사건 지적재조사'라 한다)을 실시하였고, 2023. 8. 4. 이 사건 지적재조사 결과 위 토지들 중 원고들이 1/2 지분씩 공유하고 있는 인천 중구 D 토지(이하 '이 사건 토지'라 한다)가 19.3m2 증가하여 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다) 제20조 내지 제21조에 따라 지적재조사 조정금이 발생하였다며 원고들에게 각각 지적재조사 조정금 14,137,200원{(19.3m2 × 1m2당 1,465,000원) X 1/2}을 납부할 것을 고지하였다.
+나. 원고들은 위 납부고지에 불복하여 2023. 9.경 피고에게 조정금 이의신청을 하였고, 피고는 2023. 12. 8. 이 사건 토지에 관하여 재감정평가한 결과 위 이의신청을 일부 받아들여 원고들에게 각각 기존보다 감액된 지적재조사 조정금 13,992,500원{(19.3 m2 × 1m2당 1,450,000원) X 1/2}(이하 '이 사건 조정금'이라 한다)을 납부할 것을 내용으로 하는 지적재조사 조정금 이의신청결과 통지를 하였다(이하 '이 사건 처분'이라 한다).
+[인정근거] 다툼 없는 사실, 갑 제1 내지 6호증의 각 기재, 변론 전체의 취지
+2. 관계 법령
+별지 기재와 같다.
+3. 원고들의 주장
+가. 피고는 행정절차법에 따른 사전절차를 이행하지 않았으며, 원고들의 의견을 확인하는 절차를 거치지 않았다.
+나. 이 사건 조정금 산정을 위한 감정인 선정을 일방적으로 선정하여 감정을 진행하는 등 원고들이 이 사건 지적재조사에 참여할 기회를 부여하지 않았다.
+4. 판단
+가. 행정절차법 위반 주장에 관한 판단
+행정절차법 제21조 제1항은 '행정청은 당사자에게 의무를 부과하거나 권익을 제한하는 처분을 하는 경우에는 미리 처분의 제목, 당사자의 성명 또는 명칭과 주소, 처분하려는 원인이 되는 사실과 처분의 내용 및 법적 근거, 그에 대하여 의견을 제출할 수 있다는 뜻과 의견을 제출하지 아니하는 경우의 처리방법, 의견제출기관의 명칭과 주소, 의견제출기한 등을 당사자 등에게 통지하여야 한다.'고 규정하고, 제22조 제3항은 '행정청이 당사자에게 의무를 부과하거나 권익을 제한하는 처분을 할 때 제1항에서 정한 청문을 하거나 제2항에서 정한 공청회를 개최하는 경우 외에는 당사자 등에게 의견제출의 기회를 주어야 한다.'고 규정하고 있으며, 제27조 제1항은 '당사자등은 처분 전에 그 처분의 관할 행정청에 서면이나 말로 또는 정보통신망을 이용하여 의견제출을 할 수 있다.'고 규정하고 있기는 하다.
+그러나 행정절차법 제3조 제1항은 '처분, 신고, 행정상 입법예고, 행정예고 및 행정지도의 절차에 관하여 다른 법률에 특별한 규정이 있는 경우를 제외하고는 이 법에서 정하는 바에 따른다.'라고 정하고 있고, 구 지적재조사에 관한 특별법(2024. 3. 19. 법률 제20395호로 개정되기 전의 것, 이하 '구 지적재조사법'이라 한다) 제3조 제1항은 '이 법은 지적재조사사업에 관하여 다른 법률에 우선하여 적용한다.'고 규정하고 있다.따라서 구 지적재조사법에서 지적재조사사업 조정금 부과 절차에 관한 규정을 두고 있다면, 그 규정이 우선하여 적용되고 행정절차법상 절차에 관한 규정은 적용되지 않는다고 할 것이다. 그런데 구 지적재조사법은 제4조 내지 제21조의2에서 기본계획의 수립, 시·도종합계획의 수립, 실시계획의 수립, 지적재조사지구의 지정, 토지현황조사, 지 적재조사측량, 경계의 확정, 조정금의 산정, 조정금의 지급·징수, 조정금에 대한 이의신청에 이르기까지 고시, 공람, 공청회, 주민설명회, 통보, 통지, 동의, 의견제출, 이의신청 등 여러 절차를 통해 토지소유자에게 지적재조사사업의 경과를 알리고 토지소유자의 의견을 반영하도록 하는 규정을 두고 있고, 제21조에서는 '지적소관청은 제20조 제1항에 따라 조정금을 산정하였을 때에는 지체 없이 조정금조서를 작성하고, 토지소유자에게 개별적으로 조정금액을 통보하여야 한다(제2항).'', '지적소관청은 제2항에 따라 조정금액을 통지한 날부터 10일 이내에 토지소유자에게 조정금의 수령통지 또는 납부고지를 하여야 한다(제3항).'라고 규정하고 있다.
+앞서 든 증거, 을 제3, 4호증의 각 기재, 변론 전체의 취지에 의하면, 이 사건 토지에 관하여도 위와 같은 절차를 거친 것으로 보이고, 조정금의 산정과 관련하여 지적 재조사법 제21조 제2항에 따라 미리 원고들에게 조정금액을 통보하였고, 원고들은 산정된 조정금에 관하여 이의를 하여 이 사건 처분에 이른 것으로 보이는데, 이러한 사정들을 위 관계 법령의 내용에 비추어 보면, 이 사건 처분에 대해서는 행정절차법 제21조(처분의 사전통지), 제22조(의견청취), 제27조(의견제출)가 적용된다고 볼 수 없으며, 이 사건 처분에 대하여 행정절차법이 적용됨을 전제로 한 원고의 이 부분 주장은 받아들일 수 없다.
+나. 감정인선정 절차에 있어서 위법 여부 판단
+구 지적재조사법 제20조 제3항 본문은 '조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가법인등 2인(토지소유자협의회가 추천한 감정평가법인등이 있는 경우에는 해당 감정평가법인등 1인을 포함한다. 다만, 추천이 없는 경우에는 지적소관청이 추천한다)이 평가한 감정평가액을 산술 평균하여 산정한다.'고 규정하고 있다. 이 사건 지적재조사와 관련하여 토지소유자협의회가 구성되어 해당 토지소유자협의회가 감정평가법인등을 추천하였다고 볼만한 사정은 없으므로, 위 규정에 의할 때 이 사건 지적재조사의 지적소관청인 피고의 추천으로 감정평가법인등을 선정할 수 있는바, 원고들에게 감정평가법인등의 선정에 참여할 기회가 부여되지 않았더라도 여기에 어떠한 위법이 있다고 할 수 없다. 따라서 원고들의 이 부분 주장도 이유 없다.
+5. 결론
+원고들의 청구는 이유 없으므로 이를 모두 기각하기로 하여 주문과 같이 판결한다.
+판사 호성호(재판장) 신창용 임현화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조정금결정처분취소(2023구합638)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산지방법원 제1행정부 판결
+사건2023구합638 지적재조사사업 조정금 결정처분 취소
+원고A
+피고울산광역시 동구청장
+변론종결2023. 12. 14.
+판결선고2024. 2. 1.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2022. 12. 7. 원고에 대하여 한 지적재조사 조정금 56,078,750원의 부과처분을 취소한다.
+이 유
+1. 처분의 경위
+가. 피고는 2020. 12. 17. B지구를 대상으로 2021년 지적재조사사업 실시계획을 수립하여 2022. 11. 9. 이를 완료하였다. 위 사업지구에는 원고가 1/2 공유지분을 소유한 울산 동구 C 대 1,163m2(이하 '이 사건 토지'라고 한다)가 포함되어 있다.
+나. 울산광역시 동구 경계결정위원회는 2022. 4. 5. 및 4.6. 이 사건 토지에 관하여 경계결정을 하였는데, 그 결과 이 사건 토지의 면적은 종전 1,163m2에서 1,200.7m2로 증가되었다. 위 경계결정위원회로부터 결과를 통지받은 피고는 2022. 4. 8. 경계에 관한 결정내용을 원고에게 통지하였고, 원고가 이의신청을 하지 않아 이 사건 토지에 관한 경계가 그대로 확정되었다.
+다. 피고는 감정평가법인등에 이 사건 토지의 가액에 관하여 감정평가를 의뢰하였는데, 회신된 결과에 의하면 이 사건 토지의 m2당 가격은 2,980,000원으로 평가되었다. 이에 따라 피고는 이 사건 토지의 조정금액을 112,346,000원(=증가된 면적 37.7m2m2 당 가격 2,980,000원)으로 산정한 뒤, 2022. 12. 7. 원고에게 지적재조사 조정금 56,173,000원(=112,346,000원÷2)을 납부할 것을 고지하였다.
+라. 원고는 위 다.항 기재 처분에 불복하여 2023. 2. 10. 피고에게 이의신청을 하였는데, 피고는 2023. 3. 28. 원고에게 울산광역시 동구 지적재조사위원회의 심의·의결을 거쳐 m2당 가격을 2,980,000원에서 2,975,000원으로 감액한다는 처리결과를 통지하면서 지적재조사 조정금 56,078,750원(=112,157,500원÷2)을 납부할 것을 고지하였다(위 2022. 12. 7.자 처분 중 일부 감액되고 남은 56,078,750원을 가리켜 이하 '이 사건 처분'이라고 한다).
+[인정 근거] 다툼 없는 사실, 갑 제1 내지 3, 8호증, 을 제1, 6, 12, 14호증의 각 기재, 변론 전체의 취지
+2. 이 사건 처분의 적법 여부
+가. 원고 주장의 요지
+다음과 같은 이유로 이 사건 처분은 위법하므로 취소되어야 한다.
+1) 제1 주장
+경계결정에 대한 이의신청 단계에서 피고는 원고에게 이 사건 토지에 관한 조정금액이 정확히 얼마인지 통지하지 않았다. 이로 인해 조정금액을 전혀 알 수 없었던 원고는 경계결정에 대하여 이의신청을 제기할 수 없었다.
+2) 제2 주장
+피고는 울산광역시장에게 B지구에 관한 지적재조사지구 지정신청 시 토지소유자 총수의 2/3 이상과 토지면적 2/3에 해당하는 토지소유자의 동의를 받아야 함에도 이를 충족하지 못한 상태에서 지적재조사지구 지정 신청을 하였다.
+3) 제3 주장
+지적재조사에 관한 특별법 제16조 제2항 및 제4항에 따르면, 지적소관청은 경계에 관한 결정을 신청하고자 할 때에는 지적확정예정조서에 토지소유자나 이해관계인의 의견을 첨부하여 경계결정위원회에 제출하여야 하고, 토지소유자나 이해관계인은 경계 결정위원회에 참석하여 의견을 진술할 수 있음에도 원고에게는 위와 같은 기회가 보장되지 않았다. 또한 피고가 토지소유자협의회를 제대로 구성하지 않아 원고를 비롯한 토지소유자들이 경계확정이나 조정금의 산정에 관하여 의견을 제시할 수 없었다.
+4) 제4 주장
+피고는 이 사건 처분이나 원고가 한 이의신청에 대한 결과를 통지하는 과정에서 행정심판 및 행정소송을 제기할 수 있는지 여부, 그 밖에 불복을 할 수 있는지 여부, 청구절차 및 청구기간, 그 밖에 필요한 사항을 고지하지 않았는바, 이 사건 처분은 행정절차법 제26조를 위반하였다.
+5) 제5 주장
+이 사건 토지에 관한 지적재조사를 통해 증가된 토지는 경사도가 30도 이상 되는 급경사이고, 도로가 정비되지 않은 상태이며 인근에 있는 아파트의 담장 등이 불규칙하게 설치되어 있는 점, 울산 동구 지역은 인구가 계속 감소하고 있을 뿐 아니라 진행 중이던 다수의 부동산 개발사업이 중단되었으며, 토지가격 역시 전국적으로 급락하고 있는 점 등의 사정이 있음에도 이 사건 토지에 관한 조정금액을 산정함에 있어 위와 같은 사정들은 반영되지 않았는바, 이 사건 토지에 관한 조정금액은 너무 과다하게 산정된 것이다.
+나. 관계 법령
+별지 기재와 같다.
+다. 판단
+1) 제1 주장에 관한 판단
+지적재조사에 관한 특별법 제18조 제1항은 '지적재조사사업에 따른 경계는 다음 각 호의 시기에 확정된다. 1. 제17조 제1항에 따른 이의신청 기간에 이의를 신청하지 아니하였을 때, 2. 제17조 제4항에 따른 이의신청에 대한 결정에 대하여 60일 이내에 불복의사를 표명하지 아니하였을 때'라고 규정하고 있고, 같은 법 제20조는 제1항에서'지적소관청은 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다'고 규정하면서 제3항 본문에서 '조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 「감정평가 및 감정평가사에 관한 법률」에 따른 감정평가법인등이 평가한 감정평가액으로 산정 한다'라고 규정하고 있다.
+살피건대, 위 규정들에 의하면 지적소관청은 경계가 확정된 뒤 확정 시점을 기준으로 감정평가법인등이 평가한 감정평가액으로 조정금을 산정하므로, 그 이전인 경 계결정에 대한 이의신청 단계에서는 정확한 조정금을 알 수 없고, 사전 통지도 불가능하다. 따라서 피고가 원고에게 이 사건 토지에 관한 조정금액을 사전에 통지한 바 없다고 하더라도 이 사건 처분에 어떠한 하자가 있다고 볼 수 없으므로 원고의 이 부분주장은 이유 없다.
+2) 제2 주장에 관한 판단
+지적재조사에 관한 특별법 제7조는 제1항에서 '지적소관청은 실시계획을 수립하여 시 . 도지사에게 지적재조사지구 지정 신청을 하여야 한다'고 규정하면서, 제2항에서'지적소관청이 시 ·도지사에게 지적재조사지구 지정을 신청하고자 할 때에는 다음 각 호의 사항을 고려하여 지적재조사지구 토지소유자(국유지 . 공유지의 경우에는 그 재산관리청을 말한다. 이하 같다) 총수의 3분의 2 이상과 토지면적 3분의 2 이상에 해당하는 토지소유자의 동의를 받아야 한다. 1. 지적공부의 등록사항과 토지의 실제 현황이 다른 정도가 심하여 주민의 불편이 많은 지역인지 여부, 2. 사업시행이 용이한지 여부, 3. 사업시행의 효과 여부'라고 규정하고 있고, 제8항에서는 '제2항에 따른 동의자 수의 산정방법, 동의절차, 그 밖에 필요한 사항은 대통령령으로 정한다'라고 규정하고 있다. 위와 같은 위임에 따라 같은 법 시행령 제7조 제1항은 '법 제7조 제2항에 따른 토지소유자 수 및 동의자 수는 다음 각 호의 기준에 따라 산정한다. 3. 토지등기부 및 토지대장· 임야대장에 소유자로 등재될 당시 주민등록번호의 기재가 없거나 기재된 주소가 현재 주소와 다른 경우 또는 소재가 확인되지 아니한 자는 토지소유자의 수에서 제외할 것'이라고 규정하고 있다.
+살피건대, 을 제16호증의 3 기재에 의하면 피고는 B지구 전체 소유자 205명에서 주소불명 등 소재가 확인되지 아니한 8명을 제외한 197명 중 133명(67.51%, 소수점 둘째 자리 미만 버림, 이하 같다) 및 전체 면적 110,897m2 중 90,277m2(81.40%)에 해당하는 소유자의 동의를 받아 2021. 4. 30. 울산광역시장에게 2021년 지적재조사 사업지구 지정신청을 한 사실이 인정된다. 따라서 피고의 지적재조사지구 지정신청은 그 요건을 충족하였음을 알 수 있는바, 이와 다른 전제에 있는 원고의 이 부분 주장은 이유없다.
+3) 제3 주장에 관한 판단
+앞서 든 증거, 을 제13, 14증의 각 기재 및 변론 전체의 취지에 의하면 피고는 2021. 12. 28. 원고를 비롯한 B지구 토지소유자들에게 지적확정예정조서를 통지하였는데, 위 통지서에는 '지적재조사 측량결과에 의견이 있는 경우 2022. 1. 14.(금)까지 지 적확정예정조서에 대한 의견서를 제출하여 달라'는 내용이 기재된 사실, 피고는 2022. 4. 8. 원고를 비롯한 B지구 토지소유자들에게 경계결정사항 통지를 하였는데, 위 통지서에는 '해당 통지서를 받은 날로부터 60일 이내에 이의신청서를 제출하여야 하고, 이의신청이 없을 경우 경계결정위원회의 결정대로 경계가 확정된다'는 내용과 참고사항으로 '지적재조사 측량에 따라 경계가 확정되어 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수 또는 지급하여야 하며, 조 정금은 경계가 확정된 시점을 기준으로 감정평가업자가 평가한 감정평가액으로 산정한 다'는 내용이 각 기재된 사실, 원고는 위 각 통지서를 송달받은 이후 지적확정예정조서에 대한 의견 또는 경계결정에 관한 이의신청을 제출하거나, 경계결정위원회에서의 의견진술 신청을 한 바 없는 사실이 각 인정되는바, 원고에게 지적재조사에 관한 특별법 제16조 제2항 및 제4항에 따른 의견제시 내지 의견진술의 기회가 보장되지 않았다고 볼 수 없다.
+또한 을 제8 내지 11호증의 각 기재에 의하면, 피고는 2021. 10. 18. 원고를 비롯한 B지구 토지소유자들에게 토지소유자협의회를 구성하고자 한다면서 참여를 원하는 토지소유자는 2021. 10. 28.까지 지원서를 제출하도록 안내하는 공문을 발송한 사실, 이에 따라 8명의 토지소유자가 피고에게 지원서를 제출하였고 2021. 11.경 위 8명을 위원으로 하는 B지구 토지소유자협의회가 구성된 사실이 각 인정되는바, 위 토지소유자협의회의 구성에 어떠한 위법이 있다고 볼 수 없다.
+따라서 원고의 이 부분 주장도 이유 없다.
+4) 제4 주장에 관한 판단
+행정절차법 제26조의 고지절차에 관한 규정은 행정처분의 상대방이 그 처분에 대한 행정심판의 절차를 밟는 데 편의를 제공하려는 것이어서 처분청이 위 규정에 따른 고지의무를 이행하지 아니하였다고 하더라도 경우에 따라 행정심판의 제기기간이 연장될 수 있음에 그칠 뿐, 그 때문에 심판의 대상이 되는 행정처분이 위법하다고 할수는 없으므로(대법원 2018. 2. 8. 선고 2017두66633 판결, 대법원 2016. 4. 29. 선고2014두3631 판결 등 참조), 이 사건 처분 당시 행정심판 및 행정소송을 제기할 수 있는지 여부와 그 밖에 불복을 할 수 있는지 여부, 불복청구의 절차와 기간, 방법, 불복 청구기관 등에 관한 사항이 고지되지 않았다고 하더라도 원고가 이 사건 처분에 대한 불복절차를 거치는 데에 있어서 별다른 어려움은 없었던 것으로 보이고, 달리 절차에 있어 이 사건 처분이 위법하다고 볼 수 없다. 따라서 원고의 이 부분 주장은 이유 없다.
+5) 제5 주장에 관한 판단
+앞서 살펴본 바와 같이 B지구 토지소유자협의회는 피고에게 조정금 산정방식에 관한 별도의 요청을 하지 않았으므로 지적재조사에 관한 특별법 제20조 제3항에 따라 이 사건 토지에 대한 조정금액은 '감정평가 및 감정평가사에 관한 법률에 따른 감정평가법인등이 평가한 감정평가액'으로 산정되어야 한다.
+살피건대, 변론 전체의 취지에 의하면 피고는 D협회(울산지회)로부터 감정평가 업체 2곳의 업체를 추천받아 감정평가업체로 선정하였고, 위 2개의 업체가 산정한 감정금액의 평균금액을 기초로 조정금 산정안이 마련되어 울산광역시 동구 지적재조사위 원회에서 심의·의결이 이루어진 사실이 인정되는바, 위각 감정평가업체가 수행한 비교표준지 선정, 시점 수정 및 지역요인, 개별요인, 기타요인 보정 등의 과정이 불합리하다거나 오류가 있다는 등의 위법사유가 있다고 보이지 않는다. 따라서 원고의 이 부분 주장 역시 이유 없다.
+3. 결론
+그렇다면, 원고의 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 이수영(재판장) 조한기 이고은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금산정처분취소청구(2023구합24144)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구지방법원 제1행정부 판결
+사건2023구합24144 조정금산정처분취소청구
+원고A
+소송대리인 변호사 이영환
+피고칠곡군수
+소송대리인 법무법인 광무 담당변호사 김승규
+변론종결2024. 9. 25.
+판결선고2024. 11. 13.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2023. 5. 31.[1] 원고에게 한 조정금 102,544,000원 산정처분을 취소한다.
+이 유
+1. 처분의 경위
+가. 피고는 지적소관청으로서 2021. 1. 1.부터 2022. 12. 31.까지 경북 칠곡군 B 외 101필지 합계 23,611㎡의 C지구(이하 'C지구'라 한다)에 관하여 구 지적재조사에 관한 특별법(2024. 3. 19. 법률 제20395호로 개정되기 전의 것, 이하 '구 지적재조사법'이라 한다)에 따라 지적재조사 사업을 실시하였다. 원고는 C지구 내에 위치한 경북 칠곡군 D 대 443㎡(이하 '이 사건 토지'라 한다)의 소유자이다.
+나. 피고는 2022. 7. 20. 칠곡군경계결정위원회의 의결을 거쳐 원고에게 이 사건 토지의 면적이 443㎡에서 1㎡로 감소한다는 내용의 지적재조사 경계결정을 통지하였다. 원고가 2022. 7. 28. 위 경계결정을 통지받은 후 60일 이내에 이의신청하지 않아 위 경계결정은 그대로 확정되었다.
+다. 피고는 위 경계결정에 따라 이 사건 토지 중 감소한 부분에 대한 조정금 산정을 위하여 주식회사 E(이하 'E'이라 한다)에 감정평가를 의뢰하였고, E는 피고에게 이 사건 토지 중 감소한 부분에 대한 조정금을 83,980,000원(= 190,000원 × 감소면적 442㎡)으로 감정하여 통보하였으며, 피고는 위 감정결과에 따라 원고에게 이 사건 토지 중 감소한 부분에 대한 조정금을 83,980,000원으로 통보하였다.
+라. E는 위 통보 이후 2023. 2. 9. 피고에게 현황 도로 부지와 도로 이외 부지로 구분하여 평가하여야 할 토지가 확인되었다는 이유로 이 사건 토지 중 감소한 부분에 대한 조정금을 101,218,000원(= 229,000원 × 감소면적 442㎡)로 정하여 통보하였고, 피고는 칠곡군 지적재조사위원회 심의·의결을 거쳐 2023. 3. 2. 원고에게 이 사건 토지 중 감소한 부분에 대한 조정금을 101,218,000원으로 재산정 통보하였다.
+마. 원고는 2023. 4. 18. 피고에게 위 재산정 통보에 따른 조정금 101,218,000원이주변 토지 시세에 비하여 너무 가격이 낮다는 이유로 이의신청을 하였다.
+바. 이에 피고는 주식회사 F(이하 'F'이라 한다)에 이 사건 토지 중 감소한 부분에 대한 조정금 산정을 위한 감정평가를 다시 의뢰하였고, F는 피고에게 이 사건 토지 중 감소한 부분에 대한 조정금을 102,544,000원(= 232,000원 × 감소면적 442㎡)으로 정하여 통보하였으며, 피고는 칠곡군 지적재조사위원회 심의·의결을 거쳐 2023. 5. 31. 원고에게 이 사건 토지 중 감소한 부분에 대한 조정금을 102,544,000원으로 하는 내용의 이의신청결과를 통지하였다(이하 '이 사건 처분'이라 한다).
+[인정 근거] 다툼 없는 사실, 갑 제1, 2, 5호증, 을 제3 내지 13호증(가지번호 있는 것들은 가지번호 포함)의 각 기재, 변론 전체의 취지
+2. 이 사건 처분의 적법 여부
+가. 원고의 주장
+이 사건 토지 중 감소한 부분에 대한 조정금은 이 사건 토지와 인접한 다른 토지의 조정금 산정례 및 토지거래사례와 비교하면 특별한 근거 없이 현저히 염가로 평가한 것으로서 위법하다.
+나. 관계 법령
+별지 '관계 법령' 기재와 같다.
+다. 판단
+1) 관련 법리
+구 지적재조사법 제20조 제1항은 '지적소관청은 경계확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다'고 규정하고, 같은 조 제3항은 '조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가 및 감정평가사에 관한 법률(이하 '감정평가법'이라 한다)에 따른 감정평가법인등이 평가한 감정평가액으로 산정한다. 다만, 토지소유자협의회가 요청하는 경우에는 제30조에 따른 시·군·구 지적재조사위원회의 심의를 거쳐 부동산 가격공시에 관한 법률에 따른 개별공시지가로 산정할 수 있다'고 규정하고 있다.
+감정평가의 성질상 평가 대상 토지 및 비교표준지의 실제 현황, 용도, 주변 환경 등을 확인하고 평가하는 작업, 즉 지역요인, 개별요인 등 품등비교에 있어 그 구체적인 세부 내용 내지 표현은 감정평가업자의 주관적인 가치, 인식 등에 따라 다소 다를 수 있고, 그 내용을 나타내는 우열수치 또한 차이가 있을 수 있음은 부득이하다 할 것이므로, 그 구체적인 세부 내용 내지 비교 우열수치의 산출에 있어 다소 차이가 있다 하더라도 그것이 감정평가업자의 명백한 고의 또는 과실에 따른 오류로 판단되지 않는 이상 위법하다고 볼 수 없다(대법원 2004. 5. 14. 선고 2003다38207 판결 등 참조).
+2) 구체적 판단
+앞서 든 증거, 갑 제3, 4, 6호증의 각 기재, 이 법원의 F 대구경북지사장에 대한 사실조회결과 및 변론 전체의 취지에 의하여 인정되는 다음과 같은 사정들을 종합하여 보면, 이 사건 토지 중 감소한 부분에 대한 조정금이 원고 주장과 같이 이 사건 토지 인근에 위치한 다른 토지의 시세나 조정금 액수와 비교하여 지나치게 낮게 산정되었다고 보기 어렵다. 따라서 원고의 주장은 이유 없다.
+① C지구에 대한 지적재조사 사업에는 토지소유자협의회가 없으므로, 피고는 지적재조사법 제20조 제3항에 따라 감정평가법에 따른 감정평가법인인 E이 평가한 감정액에 따라 원고에게 조정금을 통보하였고, 원고의 이의신청에 대하여 다시 감정평가법에 따른 감정평가법인인 F이 평가한 감정액에 따라 이 사건 처분을 하였는바, 그 과정에관련 법령을 위반한 잘못이 없다. 또한 위 감정평가법인들의 감정평가 결과는 1㎡당 229,000원(E), 232,000원(F)으로 그 가격에 큰 차이가 없다.
+② 감정평가법 제3조 제1항과 구 감정평가에 관한 규칙(2023. 9. 14. 국토교통부령 제1253호로 개정되기 전의 것) 제14조 제1항, 제2항에 따르면, 감정평가법인등이 토지를 감정평가하는 경우 인근지역 표준지 중 대상토지와 용도지역, 이용 상황, 주변 환경 등이 같거나 비슷한 표준지를 선정하여 해당 비교표준지의 표준지공시지가를 기준으로 대상토지 현황에 맞게 시점수정, 지역요인 및 개별요인 비교, 그 밖의 요인 보정을 거쳐 대상토지의 가액을 산정하여야 한다. 원고의 이의신청에 따라 이 사건 토지 중 감소한 부분에 대한 조정금 산정을 위하여 감정평가를 수행한 F는 이 사건 토지와 용도지역(2종 일반주거지역), 지목(대지), 주변 환경 등이 같거나 비슷하고 제반 가격 형성 요인이 유사하여 비교가능성이 인정되는 경북 칠곡군 G 대 99㎡를 비교표준지로 선정하였고, 이 사건 토지는 비교표준지에 비하여 획지조건(도로 등)에서 열세하다고 평가하였다. 이러한 개별요인 비교치 산정에 어떠한 위법이 있다고 보이지 않고, 그 평가에 이른 과정이나 참작된 여러 요소 등에 비추어 합리성을 갖춘 적정 감정으로 판단되며 달리 위 감정결과에 현저한 잘못이 있다거나 감정결과를 신뢰할 수 없다고 볼만한 객관적인 사정이 보이지 않는다.
+③ 원고는 이 사건 토지가 경북 칠곡군 H 도로 535㎡(이하 'H 토지'라 한다)와 획지조건을 제외한 나머지 요인이 동일하기 때문에 이 사건 토지 중 감소한 부분에 대한 조정금은 H 토지 중 감소한 부분에 대한 조정금과 같이 적어도 339,000원/㎡는 되어야 한다고 주장한다. 그러나 F이 작성한 개별필지 가격산출근거에 의하면 이 사건 토지의 지목은 대지, 획지조건은 0.39인데 반하여 H 토지의 지목은 도로, 획지조건은 0.57로서양 토지의 조건이 동일하지 않고, 위 토지들의 감소 부분이 모두 경북 칠곡군 I 도로에 합필되었다는 사정만으로 위 토지를 동일하게 평가하여야 한다고 보기도 어려우므로, 원고의 위 주장은 받아들이기 어렵다.
+3. 결론
+그렇다면 원고의 이 사건 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 채정선(재판장) 강수희 이준영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사사업조정금수령안내처분취소청구의소(2024구합5227)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제주지방법원 제1행정부 판결
+사건2024구합5227 지적재조사사업 조정금수령안내처분 취소청구의 소
+원고A
+피고서귀포시장
+변론종결2025. 1. 21.
+판결선고2025. 2. 18.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2024. 3. 8. 원고에게 한 조정금 이의신청에 대한 안내처분을 취소한다.
+이 유
+1. 처분의 경위
+○ 원고는 서귀포시 B 과수원 3,174㎡, C 임야 826㎡, D 과수원 2,162㎡, E 과수원 4,221㎡(이하 통틀어 '이 사건 토지'라 한다)의 소유자이다.
+○ 제주특별자치도지사는 이 사건 토지를 포함한 서귀포시 F 일원 271필지 합계 318,502㎡의 서귀포시 G 지구(이하 '이 사건 사업지구'라 한다)의 지적소관청인 피고의 신청에 따라 2021. 9. 1. 구 지적재조사에 관한 특별법(2024. 3. 19. 법률 제20395호로 개정되기 전의 것, 이하 '지적재조사법'이라 한다)에 근거하여 이 사건 사업지구를 지적재조사 사업지구로 지정·고시(제주특별자치도 고시 H)하였다.
+○ 피고는 이 사건 사업지구에 대한 지적재조사측량을 실시한 뒤 지적확정예정조서를 작성하였고, 원고에게 이 사건 토지의 면적이 합계 10,383㎡에서 10,052.3㎡로 감소한다는 내용의 지적확정예정조서를 통지하였다. 피고는 이의신청절차를 거쳐 2022. 9. 22. 서귀포시 경계결정위원회의 의결에 따라 이 사건 토지의 경계를 확정하는 결정을 하였다.
+○ 피고는 위 경계결정에 따라 이 사건 토지 중 감소한 330.7㎡(이하 '이 사건 감소부분'이라 한다)에 대한 조정금 산정을 위하여 주식회사 I(이하 회사명을 기재할 때 주식회사의 기재를 생략한다) 및 J감정평가법인에 감정평가를 의뢰하였고, 피고는 2022. 9. 27. 서귀포시 지적재조사위원회 심의·의결을 거쳐 2022. 10. 12. 원고에게 이 사건 감소부분에 대한 조정금을 아래와 같이 통보하였다(이하 '이 사건 선행처분'이라 한다).
+(단위: ㎡, 원)
+소재지	지번	지목	종전면적	확정면적	증감면적	㎡당 가격	조정금 산정금액
+K리	B	과	3,174	3,079.9	-103.1	331,500	34,177,650
+C	임	826	806.3	-19.7	418,500	8,244,450
+D	과	2,162	2,121.7	-40.3	380,000	15,314,000
+E	과	4,221	4,053.4	-167.6	314,000	52,626,400
+계			10,383	10,052.3	-330.7		110,362,500
+○ 원고는 2023. 8. 18. 이 사건 선행처분에 따른 조정금이 이 사건 토지의 시장가치에 비하여 지나치게 낮게 책정되었다는 이유로 이의신청을 하는 한편 제주특별자치도 행정심판위원회에 이 사건 선행처분의 취소를 구하는 행정심판을 제기하였으나 2023. 11. 20. 제주특별자치도 행정심판위원회는 원고의 신청을 기각하는 결정을 하였다.
+○ 피고는 조정금 이의신청에 따라 2024. 1. 17. L감정평가법인과 M감정평가법인에 이 사건 감소부분에 대한 조정금 산정을 위한 감정평가 법인을 다시 의뢰하였고, 2024. 2. 27. 서귀포시 지적재조사위원회 심의·의결을 거쳐, 2024. 3. 8. 원고에게 이 사건 감소부분에 대한 조정금을 아래와 같이 증액하는 내용의 이의신청 처리결과를 통지하였다(이하 '이 사건 처분'이라 한다)
+(단위: ㎡, 원)
+소재지	지번	지목	종전면적	확정면적	증감면적	㎡당 가격	조정금 재산정금액
+K리	B	과	3,174	3,079.9	-103.1	355,500	36,652,050
+C	임	826	806.3	-19.7	451,000	8,884,700
+D	과	2,162	2,121.7	-40.3	392,500	15,817,750
+E	과	4,221	4,053.4	-167.6	346,500	58,073,400
+계			10,383	10,052.3	-330.7		119,427,900
+[인정근거] 다툼 없는 사실, 갑 제1, 2호증, 을 제1 내지 9호증의 기재 또는 영상, 변론 전체의 취지
+2. 처분의 적법 여부[1]
+가. 원고의 주장
+원고는 2022. 4. 28. 경 이 사건 토지를 포함한 인접 토지 10필지 합계 22,507㎡를 13,546,896,000원(㎡당 가격 601,897원)에 매매하는 계약을 체결하였다. 그러나 이 사건 감소 부분에 대한 조정금은 ㎡당 가격이 346,000원 내지 451,000원에 불과하여 위 거래사례와 비교하면 특별한 근거 없이 현저히 염가로 평가하거나 인접 토지의 가격을 모두 다르게 평가한 것으로서 위법하다.
+나. 관계 법령
+별지 관계 법령 기재와 같다.
+다. 판단
+(1) 지적재조사법 제20조 제1항은 '지적소관청은 경계확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다'고 규정하고, 같은 조 제3항은 '조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가 및 감정평가사에 관한 법률(이하 '감정평가법'이라 한다)에 따른 감정평가법인등이 평가한 감정평가액으로 산정한다. 다만, 토지소유자협의회가 요청하는 경우에는 제30조에 따른 시·군·구 지적재조사위원회의 심의를 거쳐 부동산 가격공시에 관한 법률에 따른 개별공시지가로 산정할 수 있다'고 규정하고 있다.
+감정평가의 성질상 평가 대상 토지 및 비교표준지의 실제 현황, 용도, 주변 환경 등을 확인하고 평가하는 작업, 즉 지역요인, 개별요인 등 품등비교에 있어 그 구체적인 세부 내용 내지 표현은 감정평가업자의 주관적인 가치, 인식 등에 따라 다소 다를 수 있고, 그 내용을 나타내는 우열수치 또한 차이가 있을 수 있음은 부득이하다 할 것이므로, 그 구체적인 세부 내용 내지 비교 우열수치의 산출에 있어 다소 차이가 있다 하더라도 그것이 감정평가업자의 명백한 고의 또는 과실에 따른 오류로 판단되지 않는 이상 위법하다고 볼 수 없다(대법원 2004. 5. 14. 선고 2003다38207 판결 등 참조).
+(2) 앞서 든 증거, 을 제10호증의 기재, 감정인 N감정평가법인의 감정결과 및 변론 전체의 취지에 의하여 인정되는 다음과 같은 사정들을 종합하여 보면, 이 사건 감소분에 대한 조정금이 원고 주장과 같이 이 사건 토지 인근의 다른 토지의 시세와 비교하여 지나치게 낮게 산정되었다고 보기 어렵다. 따라서 원고의 주장은 이유 없다.
+① 이 사건 사업지구에 대한 지적재조사 사업에는 토지소유자협의회가 없으므로, 피고는 지적재조사법 제20조 제3항에 따라 감정평가법에 따른 감정평가법인인 I 및 J감정평가법인이 평가한 감정액에 따라 원고에게 조정금을 통보하였고, 원고의 이의신청에 대하여 다시 감정평가법에 따른 감정평가법인인 L감정평가법인이 평가한 감정액에 따라 이 사건 처분을 하였는바, 그 과정에 관련 법령을 위반한 잘못이 없다. 또한 위 감정평가법인들의 감정평가 결과는 아래 표와 같고 이 법원의 감정평가 결과와도 그 가격에 있어 큰 차이가 없다.
+(단위: 원)
+소재지	지번	지목	m2당 가격
+I	J	L	M	법원감정
+K리	B	과	330,000	333,000	359,000	352,000	359,000
+C	임	417,000	420,000	452,000	450,000	452,000
+D	과	378,000	382,000	394,000	391,000	394,000
+E	과	313,000	315,000	348,000	345,000	348,000
+② 감정평가법 제3조 제1항과 감정평가에 관한 규칙 제14조 제1항, 제2항에 따르면, 감정평가법인등이 토지를 감정평가하는 경우 인근지역 표준지 중 대상토지와 용도지역, 이용 상황, 주변 환경 등이 같거나 비슷한 표준지를 선정하여 해당 비교표준지의 표준지공시지가를 기준으로 대상토지 현황에 맞게 시점수정, 지역요인 및 개별요인 비교, 그 밖의 요인 보정을 거쳐 대상토지의 가액을 산정하여야 한다. 원고의 이의신청에 따라 이 사건 감소 부분에 대한 조정금 산정을 위하여 감정평가를 수행한 L감정평가법인 및 M감정평가법인은 이 사건 토지와 용도지역, 지목, 주변 환경 등이 같거나 비슷하고 제반 가격 형성요인이 유사하여 비교가능성이 인정되는 서귀포시 O 전 1,226㎡(이용상황 과수원)를 비교표준지로 선정하였고, 그 밖의 요인에 관한 보정치 산정을 위하여 서귀포시 P 전 946㎡(2020. 12. 7.자 거래, 토지단가 453,488원/㎡)를 선정하였는데, 법원감정에서 선정한 비교표준지 및 거래사례와 동일하다. L감정평가법인 및 M감정평가법인의 개별요인 비교치 산정 및 그 밖의 요인 보정을 위하여 인근의 평가사례 또는 거래사례를 참작하는 방법에 어떠한 위법이 있다고 보이지 않고, 그 평가에 이른 과정이나 참작된 여러 요소 등에 비추어 합리성을 갖춘 적정 감정으로 판단되며 달리 위 감정결과에 현저한 잘못이 있다거나 감정결과를 신뢰할 수 없다고 볼만한 객관적인 사정이 보이지 않는다.
+③ 원고는 이 사건 토지의 소유자가 동일하고 이용상태가 동일하므로 기준가액이 동일하게 평가되어야 한다고 주장한다. 그러나 2개 이상의 토지 등에 대한 감정평가는 개별평가를 원칙으로 하되, 예외적으로 2개 이상의 토지 등에 거래상 일체성 또는 용도상 불가분의 관계가 인정되는 경우에 일괄평가가 인정되는데, 여기서 '용도상 불가분의 관계'에 있는지 여부는 일단의 토지로 이용되고 있는 상황이 사회적·경제적·행정적 측면에서 합리적이고 그 토지의 가치 형성적 측면에서도 타당하다고 인정되는 관계에 있는 경우를 뜻한다. L감정평가법인과 M감정평가법인이 작성한 개별필지 가격산출근거에 의하면 이 사건 토지의 지목은 과수원 또는 임야로 동일하지 않고, 각 토지의 가로조건, 접근조건, 획지조건, 행정적 조건이 서로 다르고, 소유자가 동일하거나 이 사건 토지가 인접하여 위치하고 있다는 사정만으로 개별토지를 동일하게 평가하여야 한다고 보기도 어려우므로, 원고의 위 주장은 받아들이기 어렵다.
+라. 소결
+이 사건 처분은 적법하다.
+3. 결론
+원고의 청구는 이유 없으므로 기각한다.
+판사 홍순욱(재판장) 이승욱 이승현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타부담금부과처분취소(2023구합77420)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원지방법원 제3행정부 판결
+사건2023구합77420 기타부담금부과처분취소
+원고A 주식회사
+피고화성시장
+변론종결2024. 5. 16.
+판결선고2024. 6. 13.
+주 문
+1. 이 사건 소를 각하한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2023. 5. 1. 원고에게 한 지적재조사 조정금 32,133,390원의 부과처분을 취소한 다(원고가 청구취지에 적은 처분일은 2023. 11. 7.이나 그날은 조정금 부과가 부당하다는 민원에 대한 피고의 회신을 받은 날로 보이므로, 기록에 의해 인정되는 올바른 처분일로 바로잡는다).
+이 유
+1. 기초사실
+가. 피고는 2021년부터 화성시 B 일대에서 지적재조사 사업을 실시하고, 경계결정위 원회의 의결로써 원고 소유 토지에 관해 아래 표와 같이 면적의 증감이 생기도록 경계를 결정한 다음 2022. 11. 22. 원고에게 통지했다. 원고는 통지를 받고 60일 내에 이의를 하지 않아 변경된 경계가 확정되었다[[지적재조사에 관한 특별법」(이하 '지적재조사 법'이라 한다) 제17조 제1항, 제18조 제1항 제1호].
+이 유 표
+나. 피고는 감정평가를 거쳐 원고 소유 토지의 면적이 위와 같이 증감된 데 대한 조정금을 32,133,390원(이하 '이 사건 조정금'이라 한다)으로 결정하고, 2023. 5. 1. 조정금액 통보 및 납부고지서(이하 '이 사건 처분서'라 한다)를 원고 대표자 사내이사의 주소로 등기우편으로 발송했다. 원고 대표자 사내이사의 배우자가 같은 달 8. 이 사건 처분서를 받았다.
+다. 원고는 2023. 10. 16. 피고에게 이 사건 조정금 부과가 부당하다는 내용증명우편을 보냈다. 피고는 2023. 11. 6. 원고가 경계결정이나 조정금 부과에 대해 이의를 하지 않았으므로 더는 다툴 수 없다고 회신했다.
+라. 원고는 2023. 12. 21. 조정금 부과처분의 취소를 구하는 이 사건 소를 제기했다.
+[인정근거] 다툼 없는 사실, 갑 제1호증의 2, 을 제5, 10 내지 12호증의 기재, 변론 전체의 취지
+2. 소의 적법성에 관한 판단
+가. 행정처분에 대한 취소소송은 처분이 있음을 안 날부터 90일 이내에 제기해야 한다(행정소송법 제20조 제1항). 행정절차에서의 송달은 송달받을 사람(대표자 포함)의 주소에 우편을 보내는 방법으로 할 수 있고(행정절차법 제14조 제1항), 처분서가 상대방의 주소지에 송달되는 등 사회통념상 처분이 있음을 처분상대방이 알 수 있는 상태에 놓인 때에는 반증이 없는 한 처분이 있음을 알았다고 추정할 수 있다(대법원 2017. 3. 9. 선고 2016두60577 판결 등 참조).
+나. 이 사건 처분서가 2023. 5. 1. 원고 대표자 주소지에 송달된 사실은 앞서 보았으므로, 그날 이 사건 조정금이 부과된 사실을 알았다고 추정된다. 원고는 그로부터 90일이 지나서 이 사건 소를 제기했음은 기간계산상 분명하므로, 법에서 정한 제소기간을 넘겨 부적법하다.
+[조정금에 이의가 있는 토지소유자는 납부고지를 받은 날로부터 60일 이내에 지적소관청에 이의신청을 할 수 있는데(지적재조사법 제21조의2 제1항), 원고가 조정금 부과가 부당하다는 취지로 보낸 내용증명우편을 위 규정에서 정한 이의신청으로 보더라도 이미 정한 기간을 지나서 한 것이어서 부적법하므로, 그에 대한 회신을 받고 이 사건 소를 제기했다고 하여 제소기간을 준수한 것이 되지는 않는다]
+3. 결론
+이 사건 소는 부적법하므로 각하한다.
+판사 김은구(재판장) 김은솔 정종인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>손해배상(기)(2025나56841)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원지방법원 제3-3민사부 판결
+사건2025나56841 손해배상(기)
+원고,항소인A 종회
+소송대리인 법무법인 춘추 담당변호사 신태영
+피고,피항소인B
+제1심판결수원지방법원 여주지원 2025. 5. 22. 선고 2024가단23035 판결
+변론종결2026. 3. 19.
+판결선고2026. 4. 30.
+주 문
+1. 제1심판결 중 아래에서 지급을 명하는 금액에 해당하는 원고 패소 부분을 취소한다.
+피고는 원고에게 106,000,000원 및 이에 대하여 2024. 10. 31.부터 2026. 4. 30.까지는 연 5%, 그 다음날부터 다 갚는 날까지는 연 12%의 각 비율로 계산한 돈을 지급하라.
+2. 원고의 나머지 항소를 기각한다.
+3. 소송 총비용은 피고가 부담한다.
+4. 제1항의 금전지급 부분은 가집행할 수 있다.
+청구취지 및 항소취지
+제1심판결을 취소한다. 피고는 원고에게 106,000,000원 및 이에 대하여 소장 부본 송달일 다음날부터 다 갚는 날까지 연 12%의 비율로 계산한 돈을 지급하라.
+이 유
+1. 기초사실
+이 법원에서 이 부분에 관하여 설시할 이유는 제1심판결 제2쪽 제9행, 제11행, 제12행, 제14행의 '이 법원'을 '수원지방법원 여주지원'으로 각 고치고, 제2쪽 마지막행 다음에 아래 내용을 추가하는 외에는 제2, 3쪽 '1. 기초사실' 부분 기재와 같으므로 민사소송법 제420조 본문에 따라 이를 그대로 인용한다.
+【추가하는 부분】
+『 마. 피고는 2024. 4. 8. 양평군에 지적재조사사업 완료에 따른 조정금 지급청구를 하면서 원고 명의의 농협은행 통장사본(계좌번호 1 생략)을 첨부하였고, 양평군은 2024. 4. 15. 위 농협은행 통장으로 조정금 150,689,500원(이하 '이 사건 조정금'이라 한다)을 지급하였다.
+바. 피고는 위 농협은행 통장에서 2024. 4. 16. 자신의 계좌로 60,000,000원을 송금하였고, 2024. 4. 16.부터 2024. 6. 14.까지 D에게 10,000,000원, E에게 4,000,000원, F에게 22,000,000원, G에게 10,000,000원 합계 46,000,000원(=10,000,000원+4,000,000원+22,000,000원+10,000,000원)을 송금하였다. 』
+2. 원고 청구의 요지
+피고는 원고의 대표자가 아님에도 법률상 원인 없이 이 사건 조정금을 수령하여 그 중 106,000,000원을 임의로 소비하였으므로 원고에게 부당이득금 106,000,000원 및 이에 대한 지연손해금을 지급할 의무가 있다.
+3. 판단
+위 인정사실 및 앞서 든 증거들, 을 제5, 8호증의 각 기재에 변론 전체의 취지를 더하여 알 수 있는 다음과 같은 사정들을 종합하면, 피고가 법률상 원인 없이 이 사건 조정금 중 106,000,000원을 개인적으로 임의 사용하여 이득을 얻고 이로 인해 원고에게 같은 금액 상당의 손해가 발생하였다고 인정된다.
+① 피고는 2024. 3. 9. 원고의 회장에서 해임된 이후인 2024. 4. 8. 양평군에 이 사건 조정금 지급청구를 하였고, 피고가 지급청구 당시 제출한 원고의 농협은행 통장으로 조정금을 수령하였다.
+② 원고는 MG새마을금고 계좌(계좌번호 2 생략)를 종중 계좌로 사용해 왔고, 피고도 원고 회장직을 수행하면서 위 계좌를 활용하여 업무를 수행해온 점, 위 농협은행 통장을 보면 이 사건 조정금이 입금된 후 앞서 본 바와 같이 피고가 금원을 이체한 외에는 달리 원고 종중의 업무와 관련된 입출금 내역이 확인되지 않는 점 등을 고려하면, 농협은행 통장은 피고가 이 사건 조정금을 수령하기 위한 목적으로 개설한 것으로 보인다.
+③ 피고는 D, E 등으로부터 원고 관련 소송비용으로 차용한 46,000,000원을 변제하였다고 주장하나, 피고가 기재한 것으로 보이는 총회공금 수입지출현황 장부(을 제8호증)에 따르더라도 원고 관련 소송비용은 위 금액에 미치지 않는다.
+④ 피고는 원고 회장직 수행에 따른 급여 명목으로 60,000,000원을 송금 받았다는취지로 주장하나, 원고가 적법한 의사결정 절차를 거쳐 피고에게 회장 급여로 위 금액을 지급하기로 하였다는 점을 인정할 자료가 없다.
+⑤ 총회공금 수입지출현황 장부는 영수증 등과 같은 객관적인 지출증빙 자료가 첨부되어 있지 않은 수기장부로 그 내용을 그대로 믿기 어렵고, 달리 피고가 106,000,000원을 종중 업무를 위하여 지출하였다는 점을 인정할 증거가 없다.
+따라서 피고는 원고에게 부당이득금 106,000,000원 및 이에 대하여 원고가 구하는 바에 따라 소장 부분 송달일 다음날인 2024. 10. 31.부터 피고가 이행의무의 존부와 범위에 관하여 항쟁함이 상당하다고 인정되는 이 법원 판결 선고일인 2026. 4. 30.까지는 민법에서 정한 연 5%, 그 다음날부터 다 갚는 날까지는 소송촉진 등에 관한 특례법에서 정한 연 12%의 각 비율로 계산한 지연손해금을 지급할 의무가 있다.
+4. 결론
+원고의 이 사건 청구는 위 인정범위 내에서 이유 있어 인용하고, 나머지 청구는 이유 없어 기각하여야 한다. 제1심판결은 이와 결론을 일부 달리하여 부당하므로 원고의 항소를 일부 받아들여 위 인정범위 내에서 제1심판결을 취소하고 피고에 대하여 이 법원에서 인정한 위 금액의 지급을 명하며, 원고의 나머지 항소는 기각하기로 하여 주문과 같이 판결한다.
+판사 권현영(재판장) 고연금 안동범</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사에따른조정금재결처분취소청구의소(2024구합246)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제주지방법원 제1행정부 판결
+사건2024구합246 지적재조사에 따른 조정금 재결처분 취소 청구의 소
+원고A
+피고제주시장
+변론종결2024. 10. 8.
+판결선고2024. 11. 19.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2023. 10. 13. 원고에 대하여 한 지적재조사 조정금 부과 처분을 취소한다.
+이 유
+1. 처분의 경위
+○ 피고는 원고 소유의 제주시 B(이 사건 토지)에 관하여 지적재조사에 관한 특별법(지적재조사법)에 따라 지적재조사사업을 하여, 2021. 7. 1. 종전 면적 834m²에서 20.8m²(이 사건 증가면적)가 증가한 854.8m²로 지적확정예정통지를 하였다.
+○ 피고는 경계결정위원회의 심의를 거쳐 지적확정예정통지와 같이 경계결정을 하고, 2022. 3. 15. 원고에게 통지하였다(이 사건 경계결정).
+○ 원고는 2023. 7. 17. 이 사건 경계결정의 무효확인 등을 구하는 행정심판을 청구하였으나, 2023. 9. 20. 원고의 청구는 기각되었다.
+○ 피고는 2023. 10. 13. 지적재조사 조정금을 최종적으로 33,477,600원으로 정하였다(이 사건 처분).
+○ 원고는 2024. 1. 12. 이 사건 처분에 대한 이의신청 결정처분 취소 등을 구하는 행정심판을 청구하였으나, 2024. 3. 21. 원고의 청구는 기각되었다.
+[인정근거] 다툼 없는 사실, 갑 제1, 3호증, 을 제1 내지 10호증(가지번호 포함)의 기재, 변론 전체의 취지
+2. 처분의 적법 여부
+가. 원고의 주장
+원고는 돌담을 경계로 이 사건 토지를 매수하였다. 이 사건 증가면적은 이 사건 토지 밭담 경계선에 이웃집 돌담과 이 사건 토지 밭담 사이에 끼어 있는 부정형의 자투리땅으로, 수많은 돌들이 겹겹이 쌓아져 있어 토지로 사용할 수 없다. 피고의 지적측량은 이 사건 토지와 동떨어진 곳에서 이루어졌다. 따라서 지적측량을 다시 확인해야 하고 명확한 근거로 조정금 청구를 해야 한다.
+나. 판단
+먼저, 피고의 지적측량이 이 사건 토지와 동떨어진 곳에서 이루어져 지적측량을 다시 확인해야 한다는 취지의 원고 주장에 대하여, 앞서 든 증거에 변론 전체의 취지를 종합하면, 이 사건 경계결정에 대한 원고의 행정심판청구는 2023. 9. 20. 기각되었고, 원고는 이에 불복하는 행정소송을 제기하지 않아 이 사건 경계결정은 확정된 사실을 인정할 수 있는바, 지적재조사 경계가 확정된 경우 지적소관청은 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급하는 절차를 진행하므로, 원고는 조정금을 산정한 이 사건 처분에 대한 불복소송에서 지적측량을 다시 확인한다는 주장을 할 수 없다. 더구나 '지상경계에 대하여 다툼이 없는 경우 토지소유자가 점유하는 토지의 현실경계'를 기준으로 경계를 설정하여야 하는바, 이 사건 경계결정에 어떠한 위법이 있다고도 보이지 않는다.
+다음으로, 원고는 명확한 근거로 조정금을 산정해야 한다는 취지로 주장하나, 앞서 든 증거에 의하면, 피고는 지적조사법 제20조 제1항, 제3항에 따른 절차를 준수하여 조정금을 산정하였다고 판단되고 조정금 산정에 어떠한 위법이 있다고 보이지 않는다.
+따라서 이 사건 처분은 적법하고 원고의 주장은 이유 없다.
+3. 결론
+원고의 청구는 이유 없으므로 기각한다.
+판사 홍순욱(재판장) 박진희 이승현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사업조정금결정처분취소(2023구합621)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산지방법원 제1행정부 판결
+사건2023구합621 지적재조사업 조정금 결정처분 취소
+원고A
+피고울산광역시 동구청장
+변론종결2023. 12. 14.
+판결선고2024. 2. 1.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고는 2022. 12. 8. 원고에 대하여 한 지적재조사 조정금 37,712,000원의 부과처분을 취소한다.
+이 유
+1. 처분의 경위
+가. 피고는 2020. 12. 17. B지구를 대상으로 2021년 지적재조사사업 실시계획을 수립하여 2022. 11. 9. 이를 완료하였다. 위 사업지구에는 원고가 소유한 울산 동구 C대 320m2 및 D 대 273m2(이하 통틀어 '이 사건 각 토지'라 한다)가 포함되어 있다.
+나. 울산광역시 동구 경계결정위원회는 2022. 4. 5. 및 4. 6. 이 사건 각 토지에 관하여 경계결정을 하였는데, 그 결과 C는 320m2에서 324.8m2로, D는 273m2에서 284.6m2로 각 증가되었다. 위 경계결정위원회로부터 결과를 통지받은 피고는 2022. 4. 8. 경계에 관한 결정내용을 원고에게 통지하였고, 원고가 이의신청을 하지 않아 이 사건 각 토지에 관한 경계가 그대로 확정되었다.
+다. 피고는 감정평가법인등에 이 사건 각 토지의 가액에 관하여 감정평가를 의뢰하였는데, 회신된 결과에 의하면 C의 m2당 가격은 2,270,000원으로, D의 m2당 가격은 2,330,000원으로 각 평가되었다. 이에 따라 피고는 이 사건 각 토지의 조정금액을 합계 37,924,000원[=C 10,896,000원(=증가된 면적 4.8m2xm2당 가격 2,270,000원)+D 27,028,000원(=증가된 면적 11.6m2×m2당 가격 2,330,000원)]으로 산정한 뒤, 2022. 12. 8. 원고에게 지적재조사 조정금 37,924,000원을 납부할 것을 고지하였다.
+라. 원고는 위 다.항 기재 처분에 불복하여 2023. 2. 10. 피고에게 조정금 이의신청을 하였는데, 피고는 2023. 3. 31. 원고에게 울산광역시 동구 지적재조사위원회의 심의 ·
+의결을 거쳐 C의 m2당 가격을 20,000원을 감액한 2,250,000원으로, D의 m2당 가격을 10,000원 감액한 2,320,000원으로 한다는 처리결과를 통지하면서, 지적재조사 조정금 합계 37,712,000원[=10,800,000원(증가된 면적 4.8m2xm2당 가격 2,250,000원)+ 26,912,000원(=증가된 면적 11.6m2xm2당 가격 2,320,000원)]을 납부할 것을 고지하였다(위 2022. 12. 8.자 처분 중 일부 감액되고 남은 37,712,000원을 가리켜 이하 '이사건 처분'이라고 한다).
+[인정 근거] 다툼 없는 사실, 갑 제1 내지 3, 8호증, 을 제1, 6, 12, 14호증의 각 기재, 변론 전체의 취지
+2. 이 사건 처분의 적법 여부
+가. 원고 주장의 요지
+다음과 같은 이유로 이 사건 처분은 위법하므로 취소되어야 한다.
+1) 제1 주장
+경계결정에 대한 이의신청 단계에서 피고는 원고에게 이 사건 토지에 관한 조정금액이 정확히 얼마인지 통지하지 않았다. 이로 인해 조정금액을 전혀 알 수 없었던 원고는 경계결정에 대하여 이의신청을 제기할 수 없었다.
+2) 제2 주장
+피고는 울산광역시장에게 B지구에 관한 지적재조사지구 지정신청 시 토지소유자 총수의 2/3 이상과 토지면적 2/3에 해당하는 토지소유자의 동의를 받아야 함에도 이를 충족하지 못한 상태에서 지적재조사지구 지정 신청을 하였다.
+3) 제3 주장
+지적재조사에 관한 특별법(이하 '지적재조사법'일아 한다) 제16조 제2항 및 제4항에 따르면, 지적소관청은 경계에 관한 결정을 신청하고자 할 때에는 지적확정예정조 서에 토지소유자나 이해관계인의 의견을 첨부하여 경계결정위원회에 제출하여야 하고, 토지소유자나 이해관계인은 경계결정위원회에 참석하여 의견을 진술할 수 있음에도 원고에게는 위와 같은 기회가 보장되지 않았다. 또한 피고가 토지소유자협의회를 제대로 구성하지 않아 원고를 비롯한 토지소유자들이 경계확정이나 조정금의 산정에 관하여 의견을 제시할 수 없었다.
+4) 제4 주장
+피고는 이 사건 처분이나 원고가 한 이의신청에 대한 결과를 통지하는 과정에서 행정심판 및 행정소송을 제기할 수 있는지 여부, 그 밖에 불복을 할 수 있는지 여부, 청구절차 및 청구기간, 그 밖에 필요한 사항을 고지하지 않았는바, 이 사건 처분은 행정절차법 제26조를 위반하였다.
+5) 제5 주장
+이 사건 각 토지에 관한 지적재조사를 통해 증가된 토지는 건물주차장 밖 도로쪽 땅으로 원고에게 아무런 재산적 가치가 없는 점, 울산 동구 지역은 최근 땅값이 하락하였을 뿐 아니라 인구가 계속 감소하였으며, 최근 경매 동향에 따르면 가장 번화가인 토지도 평당 186만 원 수준으로 낙찰되고 있는 점 등의 사정이 있음에도 이 사건 각 토지에 관한 조정금액을 산정함에 있어 위와 같은 사정들은 반영되지 않았는바, 이 사건 각 토지에 관한 조정금액은 너무 과다하게 산정된 것이다.
+나. 관계 법령
+별지 기재와 같다.
+다. 판단
+1) 제1 주장에 관한 판단
+지적재조사법 제18조 제1항은 '지적재조사사업에 따른 경계는 다음 각 호의 시기에 확정된다. 1. 제17조 제1항에 따른 이의신청 기간에 이의를 신청하지 아니하였을 때, 2. 제17조 제4항에 따른 이의신청에 대한 결정에 대하여 60일 이내에 불복의사를 표명하지 아니하였을 때'라고 규정하고 있고, 같은 법 제20조는 제1항에서 '지적소관청은 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다'고 규정하면서 제3항 본문에서 조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 「감정평가 및 감정평가사에 관한 법률」에 따른 감정평가법인등이 평가한 감정평가액으로 산정한다'라고 규정하고 있다.
+살피건대, 위 규정들에 의하면 지적소관청은 경계가 확정된 뒤 확정 시점을 기준으로 감정평가법인등이 평가한 감정평가액으로 조정금을 산정하므로, 그 이전인 경 계결정에 대한 이의신청 단계에서는 정확한 조정금을 알 수 없고, 사전 통지도 불가능하다. 따라서 피고가 원고에게 이 사건 각 토지에 관한 조정금액을 사전에 통지한 바 없다고 하더라도 이 사건 처분에 어떠한 하자가 있다고 볼 수 없으므로 원고의 이부분 주장은 이유 없다.
+2) 제2 주장에 관한 판단
+지적재조사법 제7조는 제1항에서 '지적소관청은 실시계획을 수립하여 시 · 도지사에게 지적재조사지구 지정 신청을 하여야 한다'고 규정하면서, 제2항에서 '지적소관 청이 시 . 도지사에게 지적재조사지구 지정을 신청하고자 할 때에는 다음 각 호의 사항을 고려하여 지적재조사지구 토지소유자(국유지 · 공유지의 경우에는 그 재산관리청을 말한다. 이하 같다) 총수의 3분의 2 이상과 토지면적 3분의 2 이상에 해당하는 토지소유자의 동의를 받아야 한다. 1. 지적공부의 등록사항과 토지의 실제 현황이 다른 정도가 심하여 주민의 불편이 많은 지역인지 여부, 2. 사업시행이 용이한지 여부, 3. 사업시행의 효과 여부'라고 규정하고 있고, 제8항에서는 '제2항에 따른 동의자 수의 산정방법, 동의절차, 그 밖에 필요한 사항은 대통령령으로 정한다'라고 규정하고 있다. 위와 같은 위임에 따라 같은 법 시행령 제7조 제1항은 '법 제7조 제2항에 따른 토지소유자 수 및 동의자 수는 다음 각 호의 기준에 따라 산정한다. 3. 토지등기부 및 토지대장·
+임야대장에 소유자로 등재될 당시 주민등록번호의 기재가 없거나 기재된 주소가 현재 주소와 다른 경우 또는 소재가 확인되지 아니한 자는 토지소유자의 수에서 제외할 것'이라고 규정하고 있다.
+살피건대, 을 제16호증의 3 기재에 의하면 피고는 B지구 전체 소유자 205명에서 주소불명 등 소재가 확인되지 아니한 8명을 제외한 197명 중 133명(67.51%, 소수점 둘째 자리 미만 버림, 이하 같다) 및 전체 면적 110,897m2 중 90,277m2(81.40%)에 해당하는 소유자의 동의를 받아 2021. 4. 30. 울산광역시장에게 2021년 지적재조사 사업지구 지정신청을 한 사실이 인정된다. 따라서 피고의 지적재조사지구 지정신청은 그 요건을 충족하였음을 알 수 있는바, 이와 다른 전제에 있는 원고의 이 부분 주장은 이유없다.
+3) 제3 주장에 관한 판단
+앞서 든 증거, 을 제13, 14증의 각 기재 및 변론 전체의 취지에 의하면 피고는 2021. 12. 28. 원고를 비롯한 B지구 토지소유자들에게 지적확정예정조서를 통지하였는데, 위 통지서에는 '지적재조사 측량결과에 의견이 있는 경우 2022. 1. 14.(금)까지 지 적확정예정조서에 대한 의견서를 제출하여 달라'는 내용이 기재된 사실, 피고는 2022. 4. 8. 원고를 비롯한 B지구 토지소유자들에게 경계결정사항 통지를 하였는데, 위 통지서에는 '해당 통지서를 받은 날로부터 60일 이내에 이의신청서를 제출하여야 하고, 이의신청이 없을 경우 경계결정위원회의 결정대로 경계가 확정된다'는 내용과 참고사항으로 '지적재조사 측량에 따라 경계가 확정되어 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수 도는 지급하여야 하며, 조 정금은 경계가 확정된 시점을 기준으로 감정평가업자가 평가한 감정평가액으로 산정한 다'는 내용이 각 기재된 사실, 원고는 위 각 통지서를 송달받은 이후 지적확정예정조서에 대한 의견 또는 경계결정에 관한 이의신청을 제출하거나, 경계결정위원회에서의 의견진술 신청을 한 바 없는 사실이 각 인정되는바, 원고에게 지적재조사법 제16조 제2항 및 제4항에 따른 의견제시 내지 의견진술의 기회가 보장되지 않았다고 볼 수 없다.
+또한 을 제8 내지 11호증의 각 기재에 의하면, 피고는 2021. 10. 18. 원고를 비롯한 B지구 토지소유자들에게 토지소유자협의회를 구성하고자 한다면서 참여를 원하는 토지소유자는 2021. 10. 28.까지 지원서를 제출하도록 안내하는 공문을 발송한 사실, 이에 따라 8명의 토지소유자가 피고에게 지원서를 제출하였고 2021. 11.경 위 8명을 위원으로 하는 B지구 토지소유자협의회가 구성된 사실이 각 인정되는바, 위 토지소유자협의회의 구성에 어떠한 위법이 있다고 볼 수 없다.
+따라서 원고의 이 부분 주장도 이유 없다.
+4) 제4 주장에 관한 판단
+행정절차법 제26조의 고지절차에 관한 규정은 행정처분의 상대방이 그 처분에 대한 행정심판의 절차를 밟는 데 편의를 제공하려는 것이어서 처분청이 위 규정에 따른 고지의무를 이행하지 아니하였다고 하더라도 경우에 따라 행정심판의 제기기간이 연장될 수 있음에 그칠 뿐, 그 때문에 심판의 대상이 되는 행정처분이 위법하다고 할수는 없으므로(대법원 2018. 2. 8. 선고 2017두66633 판결, 대법원 2016. 4. 29. 선고2014두3631 판결 등 참조), 이 사건 처분 당시 행정심판 및 행정소송을 제기할 수 있는지 여부와 그 밖에 불복을 할 수 있는지 여부, 불복청구의 절차와 기간, 방법, 불복 청구기관 등에 관한 사항이 고지되지 않았다고 하더라도 원고가 이 사건 처분에 대한 불복절차를 거치는 데에 있어서 별다른 어려움은 없었던 것으로 보이고, 달리 절차에 있어 이 사건 처분이 위법하다고 볼 수 없다. 따라서 원고의 이 부분 주장은 이유 없다.
+5) 제5 주장에 관한 판단
+앞서 살펴본 바와 같이 B지구 토지소유자협의회는 피고에게 조정금 산정방식에 관한 별도의 요청을 하지 않았으므로 지적재조사법 제20조 제3항에 따라 이 사건 토지에 대한 조정금액은 '감정평가 및 감정평가사에 관한 법률에 따른 감정평가법인등이 평가한 감정평가액'으로 산정되어야 한다.
+살피건대, 변론 전체의 취지에 의하면 피고는 E협회(울산지회)로부터 감정평가업 체 2곳의 업체를 추천받아 감정평가업체로 선정하였고, 위 2개의 업체가 산정한 감정금액의 평균금액을 기초로 조정금 산정안이 마련되어 울산광역시 동구 지적재조사위원 회에서 심의·의결이 이루어진 사실이 인정되는바, 위 각 감정평가업체가 수행한 비교표준지 선정, 시점 수정 및 지역요인, 개별요인, 기타요인 보정 등의 과정이 불합리하다거나 오류가 있다는 등의 위법사유가 있다고 보이지 않는다. 또한, 원고는 이 사건 각 토지의 측량이 잘못되었으므로 재측량을 요청한다는 취지로도 주장하나, 위에서 본바와 같이 이 사건 각 토지의 경계에 관하여 피고가 2022. 4. 8. 통지한 경계결정사항 이 그대로 확정되었으므로, 이 사건 소로서 그 경계를 다툴 수 없다. 따라서 원고의 이부분 주장 역시 이유 없다.
+3. 결론
+그렇다면, 원고의 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 이수영(재판장) 조한기 이고은</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금부과처분취소(2022구합67860)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원지방법원 제2행정부 판결
+사건2022구합67860 조정금 부과 처분 취소
+원고A
+소송대리인 변호사 강두원
+피고평택시장
+변론종결2023. 3. 23.
+판결선고2023. 4. 27.
+주 문
+1. 피고가 2021. 12. 9. 원고에게 한 지적재조사 조정금 부과처분 63,468,000원 중 58,056,000원을 초과한 부분을 취소한다.
+2. 원고의 나머지 청구를 기각한다.
+3. 소송비용 중 1/2은 원고가, 나머지는 피고가 각 부담한다.
+청구취지
+피고가 2021. 12. 9. 원고에게 한 지적재조사 조정금 부과처분 63,468,000원 중 52,644,000원을 초과한 부분을 취소한다.
+이 유
+1. 처분의 경위
+가. 피고는 경기도지사가 2020. 11. 10. 경기도 고시 B로 지정 고시한 평택시 C 일원 240필지 총 149,362m2(지구명 D지구)에 관한 지적재조사사업(이하 '이 사건 사업'이라 한다)의 사업시행자이고, 원고는 이 사건 사업지구 내에 있는 평택시 E 대지(이하 '이 사건 토지'라 한다)의 소유자이다.
+나. 평택시 경계결정위원회는 2021. 4. 20. 이 사건 토지의 면적을 645m2에서 809m2로 164m2만큼 증가하는 것으로 경계를 변경하기로 결정하였다(이하 위 164m2를 '이 사건 증가면적'이라 한다). 피고는 2021. 4. 21. 원고에게 이를 통지하였고, 원고는 2021. 4. 29. 이를 수령하였다.
+다. 피고로부터 감정평가를 의뢰받은 감정평가법인 2곳은 2021. 9. 29.을 기준으로 이 사건 토지의 전체 면적 809m2의 가액을 평가한 후 1m2당 가액에 이 사건 증가면적 164m2를 곱하여 이 사건 토지 중 이 사건 증가면적 부분의 가액을 산정하였다.
+라. 피고는 평택시 지적재조사위원회의 심의를 거쳐 위 감정평가액을 기초로 원고가 납부할 조정금을 64,698,000원으로 산정하여 2021. 12. 9. 원고에게 위 조정금을 납부할 것을 고지하였고(이하 '이 사건 처분'이라 한다), 원고는 위 납부고지에 대하여 이의신청을 하였다.
+마. 원고의 위 이의신청에 따라 피고는 이 사건 증가면적 부분의 가액을 재산정하기 위하여 다시 감정평가를 의뢰하였고, 그 의뢰를 받은 감정평가법인 2곳은 2021. 9. 29.을 기준으로 이 사건 토지의 전체 면적 809m2의 가액을 평가(이하 '이 사건 지적재조 사 감정평가'라 한다)한 후 1m2당 가액에 이 사건 증가면적 164m2를 곱하여 이 사건 토지 중 이 사건 증가면적 부분의 가액을 산정하였다.
+바. 피고는 평택시 지적재조사위원회 심의·의결을 거쳐 원고가 납부할 조정금을 63,468,000원으로 감축하여 재산정한 다음 2022. 8. 31. 원고에게 위 감액된 조정금을 납부할 것을 고지하였다.
+[인정근거] 다툼 없는 사실, 갑 제1호증의 1, 2, 갑 제2 내지 5호증, 갑 제6호증의 1, 2, 을 제1, 2호증, 을 제3호증의 1, 2. 을 제4호증의 1, 2, 을 제5호증의 1, 2, 을 제6, 7호증, 을 제8호증의 1, 2, 을 제10호증의 1, 2, 을 제11호증의 1, 2, 을 제13 내지 16호증의 각 기재, 갑 제7호증의 영상, 변론 전체의 취지
+2. 판단
+가. 원고 주장의 요지
+원고는 다음과 같은 사유로 이 사건 지적재조사 감정평가가 위법하고, 원고가 납부할 조정금을 적법하게 산정하면 52,644,000원(= 321,000원/m2 × 164m2)이 되므로, 이 사건 처분 중 위 52,644,000원을 초과하는 부분은 취소되어야 한다고 주장한다(원고는 예비적으로 이 사건 토지 전체 면적을 대상으로 감정하는 것이 적법하다면 이사건 처분 중 58,056,000원을 초과하는 부분이 취소되어야 한다고 주장하나, 이는 앞서 본 원고 주장의 수량만을 감축하여 주장하는 것에 불과하다).
+1) 이 사건 토지 중 이 사건 증가면적 부분의 가액은 이 사건 토지의 경계가 확정된 시점인 2021. 6. 29.을 기준으로 평가되어야 하는데, 이 사건 지적재조사 감정평가는 2021. 9. 29.을 기준으로 이 사건 토지의 가액을 산정하였다.
+2) 원고가 납부할 조정금은 이 사건 토지 중 이 사건 증가면적 부분만을 대상으로한 감정평가액을 기초로 산정하여야 하는데, 이 사건 지적재조사 감정평가는 이 사건 토지 전체 면적을 대상으로 감정하여 1m2당 가액을 계산한 후 이 사건 증가면적으로 환산하였다.
+나. 관계 법령
+별지 '관계 법령' 기재와 같다.
+다. 이 사건 처분의 적법 여부에 관한 판단
+1) 감정평가의 기준시점
+가) 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다) 제20조 제3항은 조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가법인 등이 평가한 감정평가액으로 산정한다고 정하고 있다. 지적소관청으로부터 경계결정위원회의 경계에 관한 결정을 통지받은 토지소유자가 이에 대하여 불복하는 경우 통지를 받은 날부터 60일 이내에 지적소관청에 이의신청을 할 수 있는데(지적재조사법 제17조 제1항, 제16조 제6항 참조), 지적재조사법 제18조 제1항 제1호는 위 이의신청 기간에 이의를 신청하지 아니하였을 때 지적재조사사업에 따른 경계가 확정된다고 정하고 있다.
+나) 평택시 경계결정위원회가 2021. 4. 20. 이 사건 토지의 면적을 645m2에서 809m2로 164m2만큼 증가하는 것으로 경계를 변경하기로 결정한 사실, 피고가 2021. 4. 21. 원고에게 위 결정을 통지하였고, 원고가 2021. 4. 29. 이를 수령한 사실은 앞서 본바와 같으며, 원고가 위 평택시 경계결정위원회의 결정에 대하여 이의신청을 하지 아니한 사실은 당사자 사이에 다툼이 없다. 위 인정사실에 의하면, 이 사건 사업에 따른 이 사건 토지의 경계는 위 2021. 4. 29.로부터 지적재조사법 제17조 제1항에서 정한 이의신청기간인 60일이 경과하였음이 역수상 명백한 2021. 6. 29. 지적재조사법 제18조 제1항 제1호에 따라 확정되었다고 보는 것이 타당하다. 따라서 지적재조사법 제20조 제3항에 따라 원고가 납부할 조정금은 위 2021. 6. 29.을 기준으로 감정평가법인 등이 평가한 감정평가액으로 산정하여야 하므로, 2021. 9. 29.을 기준으로 감정한 이 사건 지적재조사 감정평가는 그 평가의 기준시점이 잘못되어 위법하다.
+다) 피고는, 지적소관청은 지적재조사지구에 있는 모든 토지에 대하여 제18조에 따른 경계 확정이 있었을 때 사업완료 공고를 하고(지적재조사법 제23조 제1항 참조), 기존의 지적공부를 폐쇄하며 새로운 지적공부를 작성하여야 하므로(지적재조사법 제24조 제1항 참조), 피고가 이 사건 사업완료 공고를 하고 새로운 지적공부가 작성되었을 때 비로소 이 사건 토지에 관한 지적공부상 면적이 증가된다는 이유로, 이 사건 증가면적 부분에 대한 감정평가는 피고가 이 사건 사업완료 공고를 하고 새로운 지적공부를 작성한 2021. 9. 29.을 기준으로 이루어져야 한다고 주장한다. 그러나 지적재조 사법 제23조 제1항, 제24조 제1항은 지적소관청의 사업완료 공고, 기존의 지적공부 폐쇄 및 새로운 지적공부 작성의 시점을 정한 규정에 해당하고, 그 시점을 기준으로 조정금 산정의 기초가 되는 증감면적에 대한 감정평가의 기준시점을 정한 규정에 해당한다고 볼 수는 없다. 설령 모든 토지에 대한 경계가 확정된 이후에서야 개별 토지의 증감면적에 대한 감정평가를 의뢰하는 것이 가능하다 하더라도, 그러한 사정이 감정평가의 기준시점을 개별 토지의 해당 경계확정시점으로 정하여 개별 토지별 증감면적에 대한 감정평가를 하는 데 지장을 초래한다고 볼 수 없다.
+2) 감정평가방법
+가) 지적재조사법 제20조 제1항은 지적소관청은 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다고 정하고 있다. 국토교통부 고시인 지적재 조사 업무규정 제25조 제3항 본문은 조정금은 지적확정예정조서의 지번별 증감면적에 법 제20조 제3항에 따른 감정평가액의 제곱미터당 금액 또는 개별공시지가를 곱하여 산정한다고 정하고, 제5항은 지적소관청은 조정금 산정을 위한 감정평가수수료를 예산에 반영할 수 있으며, 감정평가를 하고자 할 경우에는 해당 토지의 증감된 면적에 대하여만 의뢰하여야 한다고 정하고 있다.
+나) 아래에서 보는 바와 같은 지적재조사사업의 목적, 지적재조사법 관련 규정의 문언과 형식 등을 종합하여 보면, 조정금 산정을 위한 감정평가 시 면적증가 부분 토지를 별도의 새로운 토지로 보아 해당 면적증가 부분에만 고유하게 적용될 현황, 특성 등을 반영한 별도의 감정평가방법을 적용하여야 한다고 보기 어려우므로, 증감면적을 포함한 필지 전체 면적에 대하여 감정평가를 하여 필지별 1m2당 가액을 계산한 후 증 감면적의 가액으로 환산하여 평가하는 것이 타당하다.
+(1) 지적재조사사업은 토지의 지적공부 등록사항과 현황을 일치시키는 것이 그 사업의 내용이므로, 지적재조사사업에 따라 새로이 결정된 토지의 경계가 기존 지적공부상 토지의 경계와 다르게 결정, 확정되고, 그 결과 새로운 지적공부의 토지 면적이 기존 지적공부의 토지 면적보다 크게 기재되는 결과가 발생한다 하더라도, 특별한 사정이 없는 한 이는 기존 토지가 동일성을 유지한 채 경계설정을 달리 하게 되는 것일 뿐, 기존 토지에 동일성을 달리하는 별도의 새로운 토지가 덧붙여지는 것이 아니다. (2) 지적재조사법 제20조 제1항과 지적재조사 업무규정 제25조 제3항 본문은 1 '필지별' 또는 '지번별' 증감면적을 기준으로 조정금을 산정한다고 정하고 있음은 앞서 본 바와 같다. 위와 같은 지적재조사사업의 목적 등을 고려하여 위 규정의 문언을 해석하면, 이는 하나의 토지에 대하여 그 증감면적을 초과하는 범위에서 조정금을 산정하여서는 아니 된다는 점을 주의적으로 규정한 것으로 보는 것이 타당하다. 오히려 위 규정을 지적재조사사업으로 인하여 증감된 면적에 대해서만 감정평가를 의뢰하여야 한다는 취지로 해석하는 것은 그 문언의 가능한 의미를 벗어난다.
+(3) 지적재조사 업무규정 제25조 제3항 본문은 감정평가에 의하지 아니하고 개별공시지가에 따라 조정금을 산정하는 경우 지번별 증감면적에 개별공시지가를 곱하여 산정한다고 규정하고 있음은 앞서 본 바와 같다. 증감면적에만 적용되는 개별공시지가를 전체 필지 또는 지번과 별도로 산정할 수는 없으므로, 개별공시지가에 따라 조정금을 산정하는 경우에는 지번별 증감면적에 전체 필지 또는 지번에 적용되는 개별공시지가를 곱하여 조정금을 산정하게 된다. 지적재조사 업무규정 제25조 제3항 본문이 감정평가에 의하는 경우에만 특별히 지적재조사사업 이전의 경계와 면적을 기준으로 증감된 부분의 토지 특성을 별도로 조사한 감정평가액을 기준으로 조정금을 산정하라는 취지로 보기는 어려우므로, 감정평가에 의하는 경우에도 개별공시지가를 적용하는 경우와 마찬가지로 증감면적에 적용되는 단위면적당 가액은 필지 전체 면적에 대한 가액을 기준으로 산정하라는 의미로 해석하는 것이 타당하다.
+(4) 앞서 본 바와 같이 지적재조사 업무규정 제25조 제5항 후단은 감정평가를 하고자 할 경우에는 해당 토지의 증감된 면적에 대하여만 의뢰하여야 한다고 정하고 있다. 감정평가법인에 증감면적을 포함한 필지 전체 면적에 대하여 감정평가를 하여 필지별 1m2당 가액을 계산한 후 증감면적의 가액을 평가해달라고 의뢰하더라도 감정목적물은 증감면적에 대한 부분으로 한정된다. 위 규정은 감정목적물을 증감면적에 한정 하라는 취지일 뿐, 감정목적물에 대한 감정평가방식까지 정한 규정이라고 보기 어렵다. 3) 원고가 납부할 조정금 산정
+이 법원의 F감정평가사사무소장에 대한 감정촉탁 결과 및 변론 전체의 취지를 종합하면, 위 2021. 6. 29.을 감정평가의 기준시점으로 한 이 사건 토지의 전체 면적 809m2에 대한 감정평가액은 286,386,000원이고, 1m2당 감정평가액은 354,000원인 사실을 인정할 수 있다. 따라서 이 사건 토지 중 이 사건 증가면적 부분에 관하여 원고가 납부할 조정금은 58,056,000원(= 위 354,000원 × 이 사건 증가면적 164m2)이 된다. 피고가 이 사건 처분으로 원고에게 조정금으로 64,698,000원을 납부할 것을 고지한 사실은 앞서 본 바와 같으므로, 이 사건 처분 중 위 58,056,000원을 초과하는 부분은 위법하여 취소되어야 한다.
+3. 결론
+그렇다면, 원고의 이 사건 청구는 위 인정 범위 내에서 이유 있어 인용하고, 나머지 청구는 이유 없어 기각하기로 하여 주문과 같이 판결한다.
+판사 김태환(재판장) 이승일 이성열</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분무효확인(2023구합11402)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전주지방법원 제2행정부 판결
+사건2023구합11402 지적재조사조정금부과처분 무효확인
+원고A종중
+소송대리인 변호사 국순화
+피고전주시 덕진구청장
+변론종결2024. 6. 13.
+판결선고2024. 7. 18.
+주 문
+1. 피고가 2022. 6. 16. 원고에 대하여 한 지적재조사 조정금 부과처분이 무효임을 확인한다.
+2. 소송비용은 피고가 부담한다.
+청구취지
+주문과 같다.[1]
+이 유
+1. 처분의 경위
+가. 원고는 전주시 덕진구 B동(이하 'B동'이라 한다) C 임야 4,409m2(이하 '이 사건 종전 토지'라고 한다) 중 4476/4760 지분의 소유자이다.
+나. 피고는 2018. 12. 31. 지적재조사사업 실시계획을 공고하였고, 전주시장은 2019. 3. 4. 원고 소유의 이 사건 종전 토지가 포함된 B지구(D 일원)를 지적재조사사업(이하'이 사건 지적재조사사업'이라 한다) 지구로 지정 고시하였다.
+다. 피고는 지적소관청으로서 이 사건 지적재조사사업 지구에 관한 지적재조사 측량 등을 실시하고, 그 산하 경계결정위원회의 심의·의결을 거쳐 이 사건 종전 토지의 경계를 다소 변경하여 아래 표의 '확정 토지'란 기재와 같이 그 면적을 증가시키는 내용으로 경계를 결정(이하 '이 사건 경계결정'이라 한다)하고, 2021. 12. 24. 원고에게 위 경계결정을 통지하였다.
+이 유 표
+라. 원고는 2022. 1. 4. '지적재조사가 불필요하다'는 내용으로 이 사건 경계결정에 대한 이의를 신청하였다. 피고 산하 경계결정위원회는 원고의 이의신청을 기각하는 결정(이하 '이 사건 이의결정'이라 한다)을 하였고, 피고는 위 결정내용을 통보받아 2022. 5.3. 그 결정서(을 제9호증, 이하 '이 사건 이의결정서'라고 한다)를 작성하였다.
+마. 피고는 감정평가 및 그 산하 지적재조사위원회의 심의·의결을 거쳐 이 사건 종전 토지의 면적이 위와 같이 증가된 데에 대한 조정금을 42,565,400원으로 산정하고, 2022. 6. 16. 원고에게 위 조정금액을 통보하면서 그 조정금의 납부고지(이하 '이 사건 처분'이라 한다)를 하였다.
+[인정근거] 다툼 없는 사실, 갑 제5 내지 8호증, 을 제2 내지 7, 9 내지 13호증의 각 기재 또는 영상, 변론 전체의 취지
+2. 원고의 주장
+이 사건 처분에는 다음과 같은 위법이 있고, 그 하자가 중대·명백하여 무효이다.
+가. 이 사건 지적재조사사업을 통한 경계결정의 위법
+이 사건 종전 토지는 공간정보의 구축 및 관리 등에 관한 법률(이하 '공간정보관리법'이라 한다) 제84조에 따라 지적공부의 등록사항을 정정해야 하는 토지에 해당한다. 그럼에도 피고는 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다)에 따른 이 사건 지적재조사사업을 통해 이 사건 종전 토지의 경계를 결정하였는바, 이 사건 처분은 위와 같은 위법한 경계결정에 기초한 것이어서 위법하다.
+나. 이 사건 이의결정 통지 절차의 위법
+피고는 이 사건 경계결정에 대한 원고의 이의신청에 대하여 아무런 답변을 하지아니하였고, 원고는 위 이의신청에 대한 결정서도 송부받지 못하였는바, 이 사건 처분은 지적재조사법 제17조 제5항 소정의 절차를 거치지 않은 채 이루어진 것이어서 위법하다.
+3. 관계 법령
+별지 기재와 같다.
+4. 이 사건 처분의 적법 여부
+가. 이 사건 지적재조사사업을 통한 경계결정의 위법 여부
+1) 살피건대, 갑 제1 내지 4호증의 각 기재에 의하면 원고가 2019. 1.25. 한국국토정보공사 전주지사장에게 이 사건 종전 토지에 관한 지적측량을 의뢰한 사실, 한국국토정보공사 전주지사장이 2019. 2. 8. 피고에게 지적업무처리규정 제20조 제8항[2]에 따라 이 사건 종전 토지에 관한 지적측량 결과 그 지적공부에 오류(면적)가 발견되었음을 통지한 사실은 인정된다.
+2) 그러나 피고가 위 통지를 받기 전인 2018. 12. 31. 이 사건 지적재조사사업에 관한 실시계획을 공고하고, 2019. 3. 4. 이 사건 종전 토지를 포함한 D 일원이 위 지적재조사사업 지구로 지정 고시된 사실은 앞서 본 바와 같다. 여기에 지적재조사법 제3조는 제1항에서 '이 법은 지적재조사사업에 관하여 다른 법률에 우선하여 적용한다'고 규정하면서, 제2항에서 '지적재조사사업을 시행할 때 이 법에서 규정하지 아니한 사항에 대하여는 공간정보관리법에 따른다'고 규정하고, 공간정보관리법은 제3조에서 '측량과 지적공부·부동산종합공부의 작성 및 관리, 지명의 결정에 관하여 다른 법률에 특별한 규정이 있는 경우를 제외하고는 이 법에 따른다'고 규정하여, 이 사건 지적재조사 사업에 의한 토지의 경계 확정과 면적 증감에 따른 조정금 산정 및 부과에 관하여는 지적재조사법이 공간정보관리법에 우선하여 적용된다고 할 것인 점 등의 사정을 더하여 보면, 피고가 지적재조사법에 따른 이 사건 지적재조사사업을 통해 이 사건 종전 토지의 경계를 결정한 것에 어떠한 위법이 있다고 볼 수 없다. 따라서 원고의 위 주장은 이유 없다.
+나. 이 사건 이의결정 통지 절차의 위법 여부
+1) 관련 규정
+가) 지적소관청이 통지한 경계에 관한 결정에 대해 토지소유자나 이해관계인이 이의를 신청한 경우, 지적소관청은 그 이의신청서에 의견서를 첨부하여 경계결정 위원회에 송부하여야 하고(지적재조사법 제17조 제3항), 경계결정위원회는 이의신청을 송부받은 날부터 30일 이내에 이의신청에 대한 결정을 하여야 하며(위 법 제17조 제4항), 경계결정위원회는 이의신청에 대한 결정을 하였을 때에는 그 내용을 지적소관청에 통지하여야 하고, 지적소관청은 결정내용을 통지받은 날로부터 7일 이내에 결정서를 작성하여 이의신청인에게는 그 정본을, 그 밖의 토지소유자나 이해관계인에게는 그 부본을 송달하여야 한다. 이 경우 토지소유자는 결정서를 송부받은 날부터 60일 이내에 경계결정위원회의 결정에 대하여 행정심판이나 행정소송을 통하여 불복할지 여부를 지적소관청에 알려야 한다(위 법 제17조 제5항).
+나) 토지소유자가 위 이의신청에 대한 결정에 대하여 60일 이내에 불복의사를 표명하지 아니하였을 때에는 지적재조사사업에 따른 경계가 위 결정대로 확정된다 (지적재조사법 제18조 제1항 제2호). 지적소관청은 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급하고(위 법 제20조 제1항), 조정금을 산정하였을 때에는 지체 없이 조정금조서를 작성하여 토지소유자에게 개별적으로 조정금액을 통보하여야 하며(위 법 제21조 제2항), 조정금의 수령통지 또는 납부고지를 하여야 한다(위 법 제21조 제3항).
+2) 이 사건 이의결정서의 송부 완료 여부
+이 사건 경계결정에 대한 원고의 이의신청에 대하여 피고 산하 경계결정위원 회가 위 이의신청을 기각하는 내용의 이 사건 이의결정을 하였고, 피고가 그 결정내용을 통지받아 이 사건 결정서를 작성한 사실은 앞서 본 바와 같다. 한편, 을 제8, 14호증의 1·2의 각 기재에 의하면 피고가 2022. 5. 12. 이 사건 이의결정서를 첨부하여 'B 지구 지적재조사사업 이의신청에 따른 경계결정 통지'라는 제목의 공문(민원봉사실-G)을 작성하고, 그 무렵 위 공문을 원고의 주소지에 우편 발송한 것으로 보이기는 한다.
+그러나 나아가 실제 이 사건 이의결정서가 첨부된 위 공문이 원고에게 송달되었다고 볼만한 아무런 자료가 없는바[3], 이 사건 이의결정서의 송부가 적법하게 완료되었다고 볼 수 없다.
+3) 이 사건 처분의 무효 여부
+가) 하자 있는 행정처분이 당연무효가 되기 위해서는 그 하자가 법규의 중요한 부분을 위반한 중대한 것으로서 객관적으로 명백한 것이어야 하며, 하자가 중대하고 명백한지 여부를 판별함에 있어서는 그 법규의 목적, 의미, 기능 등을 목적론적으로 고찰함과 동시에 구체적 사안 자체의 특수성에 관하여도 합리적으로 고찰함을 요한다(대법원 2012. 2. 16. 선고 2010두10907 판결 등 참조). 한편 행정청이 어느 법률관계나 사실관계에 대하여 어느 법률의 규정을 적용하여 행정처분을 한 경우에 그 법률관계나 사실관계에 대하여는 그 법률의 규정을 적용할 수 없다는 법리가 명백히 밝혀지지 아니하여 그 해석에 다툼의 여지가 있는 때에는 행정관청이 이를 잘못 해석하여 행정처분을 하였더라도 이는 그 처분 요건사실을 오인한 것에 불과하여 그 하자가 명백하다고 할 수 없지만, 그 법률관계나 사실관계에 대하여 그 법률의 규정을 적용할 수 없다는 법리가 명백히 밝혀져 그 해석에 다툼의 여지가 없음에도 불구하고 행정청이 위 규정을 적용하여 처분을 한 때에는 그 하자가 중대하고 명백하다고 할 것이다(대법원 2012. 10. 25. 선고 2010두25107 판결 등 참조). 그리고 행정청이 법령규정의 문언상 처분 요건의 의미가 분명함에도 합리적인 근거 없이 그 의미를 잘못 해석한 결과, 처분 요건이 충족되지 아니한 상태에서 해당 처분을 한 경우에는 법리가 명백히 밝혀지지 아니하여 그 해석에 다툼의 여지가 있다고 볼 수는 없다(대법원 2014. 5.16. 선고 2011두27094 판결 등 참조).
+나) 위 법리와 앞서 본 지적재조사법의 관련 규정에 비추어 이 사건을 보건대, 위에서 든 증거에 변론 전체의 취지를 더하여 인정할 수 있는 다음과 같은 사정을 종합하면, 이 사건 처분은 이 사건 이의결정서의 송부가 적법하게 완료되지 않음으로써 이 사건 종전 토지에 관한 경계가 확정되지 아니한 상태에서 이루어진 것으로서 지 적재조사법이 정한 조정금의 징수에 관한 처분 요건을 갖추지 못한 하자가 있고, 이러한 하자는 중대하고도 명백하여 무효사유에 해당한다.
+1 지적재조사법 제20조 제1항에 의하면 위 법 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우 조정금의 징수 또는 지급의 대상이 되는바, 이 사건 종전 토지에 관한 '경계의 확정'은 지적재조사법 제20조 제1항이 정한 조정금의 징수, 즉 이 사건 처분의 요건에 해당한다.
+2 원고가 피고로부터 통지받은 이 사건 종전 토지에 관한 이 사건 경계 결정에 대하여 이의신청을 한 사실은 앞서 본 바와 같으므로, 이 사건 사업에 따른 경계는 지적재조사법 제18조 제1항 제2호에서 정한 시기인 '제17조 제4항에 따른 이의신청에 대한 결정에 대하여 60일 이내에 불복의사를 표명하지 아니하였을 때'에 확정된다. 그런데 앞서 본 바와 같이 원고에 대한 이 사건 이의결정서의 송부가 적법하게 완료되지 아니한 이상 원고가 이 사건 이의결정에 대하여 60일 이내에 불복의사를 표명하지 아니한 경우에 해당한다고 볼 수 없는바, 이 사건 종전 토지에 관하여 지적재조 사법 제18조에 따른 경계가 확정되었다고 볼 수 없다. 결국, 이 사건 처분은 지적재조 사법 제20조 제1항이 정한 조정금의 징수에 관한 처분 요건을 갖추지 못하였다고 할 것이어서, 법규의 중요한 부분을 위반한 중대한 하자가 있다.
+3 이 사건 이의결정서가 첨부된 공문을 발송한 피고로서는 직접 그 송달 내지 반송 여부를 직접 어렵지 않게 확인할 수 있었을 것인바[4], 위 이의결정서의 송부가 완료되지 아니하여 지적재조사법 제18조에 따른 경계 확정이 된 것으로 볼 수 없는 상태임을 충분히 알 수 있었을 것으로 보인다. 그럼에도 피고는 '경계의 확정'이라는 지적재조사법에서 정한 조정금 징수에 관한 처분 요건이 충족되지 않은 상태에서 이 사건 경계결정에 따라 증가된 면적을 기초로 산정한 조정금을 부과하는 이 사건 처분을 하였는바, 이러한 하자는 객관적으로도 명백하다고 볼 수 있다.
+다) 위에서 본 바와 같이 이 사건 처분에 위법이 있고, 그 하자가 중대·명백하므로, 이 사건 처분은 당연 무효이다.
+5. 결론
+그렇다면, 원고의 청구는 이유 있으므로 이를 인용하기로 하여, 주문과 같이 판결한다.
+판사 이평근(재판장) 김민재 정유성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9086,11 +9739,32 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF1F2225"/>
       <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="돋움"/>
       <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -9122,10 +9796,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9450,7 +10124,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9458,7 +10132,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9466,7 +10140,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="313.5" x14ac:dyDescent="0.3">
@@ -9474,7 +10148,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="313.5" x14ac:dyDescent="0.3">
@@ -9482,7 +10156,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9490,7 +10164,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -9498,7 +10172,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="379.5" x14ac:dyDescent="0.3">
@@ -9506,7 +10180,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="396" x14ac:dyDescent="0.3">
@@ -9514,7 +10188,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9522,7 +10196,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9530,7 +10204,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9538,7 +10212,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9546,7 +10220,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9554,7 +10228,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9562,7 +10236,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9570,7 +10244,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9578,7 +10252,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9586,7 +10260,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="313.5" x14ac:dyDescent="0.3">
@@ -9594,7 +10268,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="379.5" x14ac:dyDescent="0.3">
@@ -9602,7 +10276,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -9610,7 +10284,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9618,7 +10292,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="379.5" x14ac:dyDescent="0.3">
@@ -9626,7 +10300,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -9634,7 +10308,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9642,7 +10316,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9650,7 +10324,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -9658,7 +10332,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="379.5" x14ac:dyDescent="0.3">
@@ -9666,7 +10340,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9674,7 +10348,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -9682,7 +10356,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -9690,7 +10364,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -9698,7 +10372,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -9706,7 +10380,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9714,7 +10388,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9722,7 +10396,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="396" x14ac:dyDescent="0.3">
@@ -9730,7 +10404,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9738,7 +10412,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9746,7 +10420,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9754,7 +10428,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9762,7 +10436,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -9770,7 +10444,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="247.5" x14ac:dyDescent="0.3">
@@ -9778,7 +10452,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9786,7 +10460,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -9794,7 +10468,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="214.5" x14ac:dyDescent="0.3">
@@ -9802,7 +10476,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9810,7 +10484,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9818,7 +10492,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9826,7 +10500,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9834,7 +10508,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="330" x14ac:dyDescent="0.3">
@@ -9842,7 +10516,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -9850,7 +10524,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9858,7 +10532,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -9866,7 +10540,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9874,7 +10548,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9882,7 +10556,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="330" x14ac:dyDescent="0.3">
@@ -9890,7 +10564,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="313.5" x14ac:dyDescent="0.3">
@@ -9898,7 +10572,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9906,7 +10580,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9914,7 +10588,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="247.5" x14ac:dyDescent="0.3">
@@ -9922,7 +10596,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9930,7 +10604,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9938,7 +10612,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -9946,7 +10620,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9954,7 +10628,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -9962,7 +10636,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="330" x14ac:dyDescent="0.3">
@@ -9970,7 +10644,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9978,7 +10652,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9986,7 +10660,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -9994,7 +10668,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="313.5" x14ac:dyDescent="0.3">
@@ -10002,7 +10676,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10010,7 +10684,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="379.5" x14ac:dyDescent="0.3">
@@ -10018,7 +10692,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10026,7 +10700,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10034,7 +10708,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="214.5" x14ac:dyDescent="0.3">
@@ -10042,7 +10716,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10050,7 +10724,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10058,7 +10732,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10066,7 +10740,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10074,7 +10748,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -10082,7 +10756,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10090,7 +10764,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10098,7 +10772,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10106,7 +10780,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10114,7 +10788,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="280.5" x14ac:dyDescent="0.3">
@@ -10122,7 +10796,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10130,7 +10804,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="247.5" x14ac:dyDescent="0.3">
@@ -10138,7 +10812,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -10146,7 +10820,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -10154,7 +10828,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10162,7 +10836,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10170,7 +10844,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="330" x14ac:dyDescent="0.3">
@@ -10178,7 +10852,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="148.5" x14ac:dyDescent="0.3">
@@ -10186,7 +10860,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="132" x14ac:dyDescent="0.3">
@@ -10194,7 +10868,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -10202,7 +10876,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="247.5" x14ac:dyDescent="0.3">
@@ -10210,7 +10884,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -10218,7 +10892,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="165" x14ac:dyDescent="0.3">
@@ -10226,7 +10900,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="132" x14ac:dyDescent="0.3">
@@ -10234,7 +10908,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="165" x14ac:dyDescent="0.3">
@@ -10242,7 +10916,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="181.5" x14ac:dyDescent="0.3">
@@ -10250,7 +10924,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="247.5" x14ac:dyDescent="0.3">
@@ -10258,7 +10932,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="280.5" x14ac:dyDescent="0.3">
@@ -10266,7 +10940,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="297" x14ac:dyDescent="0.3">
@@ -10274,7 +10948,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="280.5" x14ac:dyDescent="0.3">
@@ -10282,7 +10956,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10290,7 +10964,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10298,7 +10972,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="363" x14ac:dyDescent="0.3">
@@ -10306,7 +10980,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10314,7 +10988,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10322,7 +10996,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10330,7 +11004,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10338,7 +11012,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="264" x14ac:dyDescent="0.3">
@@ -10346,7 +11020,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10354,7 +11028,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10362,7 +11036,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10370,7 +11044,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10378,7 +11052,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10386,7 +11060,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10394,7 +11068,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10402,7 +11076,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10410,7 +11084,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10418,7 +11092,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10426,7 +11100,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10434,7 +11108,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10442,7 +11116,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10450,7 +11124,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10458,7 +11132,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10466,7 +11140,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10474,7 +11148,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10482,7 +11156,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10490,7 +11164,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10498,7 +11172,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10506,7 +11180,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10514,7 +11188,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10522,7 +11196,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10530,7 +11204,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10538,7 +11212,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10546,7 +11220,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10554,7 +11228,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10562,7 +11236,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10570,7 +11244,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10578,7 +11252,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10586,7 +11260,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10594,7 +11268,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10602,7 +11276,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10610,7 +11284,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10618,7 +11292,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10626,7 +11300,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10634,7 +11308,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="330" x14ac:dyDescent="0.3">
@@ -10642,7 +11316,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10650,7 +11324,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10658,7 +11332,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10666,7 +11340,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10674,7 +11348,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10682,7 +11356,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10690,7 +11364,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10698,7 +11372,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10706,7 +11380,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10714,7 +11388,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10722,7 +11396,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10730,7 +11404,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10738,7 +11412,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10746,7 +11420,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10754,7 +11428,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10762,7 +11436,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10770,7 +11444,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10778,7 +11452,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10786,7 +11460,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10794,7 +11468,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10802,7 +11476,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="396" x14ac:dyDescent="0.3">
@@ -10810,7 +11484,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10818,7 +11492,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10826,7 +11500,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10834,7 +11508,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10842,7 +11516,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10850,7 +11524,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10858,7 +11532,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10866,7 +11540,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10874,7 +11548,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10882,7 +11556,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10890,7 +11564,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10898,7 +11572,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10906,7 +11580,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
@@ -10914,7 +11588,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="346.5" x14ac:dyDescent="0.3">
@@ -10941,10 +11615,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF1320A-8011-43B2-81F0-3F2013FBE1D1}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="54.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="255.625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10961,218 +11635,298 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>403</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>195</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>197</v>
+        <v>405</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>199</v>
+        <v>406</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>201</v>
+        <v>407</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>203</v>
+        <v>408</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>205</v>
+        <v>409</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>207</v>
+        <v>410</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>209</v>
+        <v>411</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>211</v>
+        <v>412</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>191</v>
+        <v>413</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>214</v>
+        <v>414</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>216</v>
+        <v>415</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>207</v>
+        <v>416</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>417</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>221</v>
+        <v>419</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>214</v>
+        <v>420</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>223</v>
+      <c r="A21" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>207</v>
+      <c r="A22" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>224</v>
+        <v>423</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>422</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\지적재조사 업무시스템(최종)\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D712829-6628-4C58-9DA3-FAFDAC933A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C05C779-1BCA-43BF-81E8-645D7A331966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="질의회신" sheetId="1" r:id="rId1"/>
     <sheet name="판례검색" sheetId="2" r:id="rId2"/>
+    <sheet name="고충민원" sheetId="3" r:id="rId3"/>
+    <sheet name="등록사항정정" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="472">
   <si>
     <t>제목</t>
   </si>
@@ -9697,12 +9699,629 @@
 판사 이평근(재판장) 김민재 정유성</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>지적재조사조정금채권양도청구등(2021가단51145)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전지방법원 서산지원 판결
+사건2021가단51145 지적재조사 조정금 채권양도 청구 등
+원고A
+소송대리인 법무법인 한국
+담당변호사 한덕열
+피고1. B(망 C의 상속인)
+2. D(망 C의 상속인)
+3. E(망 C의 상속인)
+4. F(망 C의 상속인)
+5. G(망 C의 상속인)
+6. H(망 C의 상속인)
+7. I(망 C의 상속인)
+피고들 소송대리인 변호사 김용문
+변론종결2022. 3. 30.
+판결선고2022. 5. 11.
+주 문
+1. 원고의 피고들에 대한 청구를 모두 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+대전지방법원 서산지원 2021년 금제1273호로 공탁된 89,584,000원에 대한 공탁금출급 청구권이 원고에게 있음을 확인한다.
+이 유
+1. 인정사실
+다음 각 사실은 갑 제1 내지 3호증의 각 기재에 변론 전체의 취지를 종합하여 인정된다.
+가. 충남 서산시 J 도로 509m²(이하 '이 사건 토지'라고 한다)에 관하여 1936. 11. 24. C 앞으로 1936. 10. 10.자 매매를 원인으로 한 소유권이전등기가 마쳐졌다. 한편, C는 1947. 7. 10. 사망하였고, 피고들이 C(이하 '망인'이라고 한다)의 재산을 상속하였다.
+나. 이 사건 토지는 2020. 12. 16. 지적재조사로 인하여 대한민국 소유의 충남 서산시 K 도로 834m²(이하 '이 사건 합필 후 토지'라고 한다)로 합필되었다.
+다. 서산시는 2021. 7. 15. 원고와 망인의 상속인들인 피고들을 피공탁자로 하여 대전지방법원 서산지원 2021년 금제1273호로 이 사건 토지에 대한 지적재조사 조정금 89,584,000원을 공탁하였다(이하 '이 사건 공탁금'이라고 한다).
+2. 원고의 주장에 관한 판단
+가. 주장
+원고는 1962. 2. 5.경 C와 이 사건 토지에 관하여 매매계약을 체결하였고, 그때부터 평온, 공연하게 20년 이상 이 사건 토지를 경작하였으며, 이로써 1982. 2. 5. 이 사건 토지에 대한 취득시효가 완성되었다. 그런데 지적재조사로 인하여 피고들의 이 사건 토지에 관한 소유권이전등기의무가 이행불능 되었으므로 원고는 이 사건 공탁금에 대하여 대상청구권을 행사한다.
+나. 판단
+그러므로 우선 이 사건 토지에 대한 원고의 점유취득시효가 완성되었는지에 관하여 보건대, 이 사건 토지의 지목 및 이 사건 합필 후 토지의 지목이 모두 '도로'인 사실은 앞서 본 바와 같고, 을나 제2, 3호증의 각 영상에 변론 전체의 취지를 종합하면, 이 사건 토지 중 일부가 적어도 1962.경 이전부터 현재까지 그 면적이나 형상을 달리하면서 도로로 이용되고 있는 사실이 인정되는바, 이러한 사정에 비추어 볼 때 원고가 이 사건 토지에서 벼농사를 하였었다는 내용의 원고 주장에 부합하는 갑 제8호증의 1 내지 3의 각 기재는 이를 그대로 믿기 어렵고, 원고가 제출한 나머지 증거들만으로는 원고가 이 사건 토지를 점유하였다는 점을 인정하기 부족하며, 달리 이를 인정할 증거가 없다. 또한, 1필의 토지의 일부에 대한 시효취득을 인정하기 위하여는 그 부분이 다른 부분과 구분되어 시효취득자의 점유에 속한다는 것을 인식하기에 족한 객관적인 징표가 계속하여 존재할 것을 요한다고 할 것인데(대법원 1993. 12. 14. 선고 93다5581 판결, 대법원 1997. 3. 11. 선고 96다37428 판결 등 참조), 이 사건 토지 중 일부가 면적이나 형상을 달리하면서 도로로 제공된 이상, 도로로 사용되는 나머지 토지가 원고의 점유에 속한다는 것을 인식하기에 족한 객관적인 징표가 계속하여 존재한다고 보기도 어렵다. 따라서 원고가 이 사건 토지를 20년 이상 점유하였음을 전제로 한 원고의 점유취득시효 주장은 받아들이지 아니한다[한편, 민법상 이행불능의 효과로서 채권자의 전보배상청구권과 계약해제권 외에 별도로 대상청구권을 규정하고 있지는 않으나 해석상 대상청구권을 부정할 이유는 없는 것이지만, 점유로 인한 부동산 소유권 취득기간 만료를 원인으로 한 등기청구권이 이행불능으로 되었다고 하여 대상청구권을 행사하기 위하여는, 그 이행불능 전에 등기명의자에 대하여 점유로 인한 부동산 소유권 취득기간이 만료되었음을 이유로 그 권리를 주장하였거나 그 취득기간 만료를 원인으로 한 등기청구권을 행사하였어야 하고, 그 이행불능 전에 그와 같은 권리의 주장이나 행사에 이르지 않았다면 대상청구권을 행사할 수 없다고 봄이 공평의 관념에 부합한다(대법원 1996. 12. 10. 선고 94다43825 판결 참조)고 할 것이다. 그런데 원고가 이 사건 토지에 대한 지적재조사가 완료되고 대한민국 앞으로 소유권이전등기가 경료됨으로써 이 사건 토지에 대한 점유취득시효 완성을 원인으로 한 등기청구권이 이행불능으로 되기 이전에 피고들에게 그 권리를 주장하였거나 등기청구권을 행사하였다고 볼 만한 아무런 증거가 없으므로, 원고의 피고들에 대한 대상청구권 행사는 허용될 수 없다. 따라서 어느 모로 보나 원고의 주장은 이유 없다].
+3. 결론
+그렇다면 원고의 피고들에 대한 청구는 모두 이유 없으므로 이를 기각한다.
+판사 하선화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금취소(2015구합1557)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주지방법원 제1행정부 판결
+사건2015구합1557 지적재조사 조정금 취소
+원고A
+피고광주광역시 서구청장
+변론종결2016. 4. 21.
+판결선고2016. 5. 12.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2015. 5. 14. 원고에 대하여 한 조정금 1,895,400원 부과처분을 취소한다.
+이 유
+1. 처분의 경위
+가. 원고는 1999. 11. 22. 광주 서구 B 152.1m2(이하 '이 사건 토지'라 한다)에 관하여 1998. 8. 31.자 협의분할에 의한 상속을 원인으로 한 소유권이전등기를 마쳤다.
+나. 피고는 2013. 7. 24. 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다)에 따라 광주 서구 C동 일대 409필지에 대하여 지적재조사사업(이하 '이 사건 사업'이라 한다) 실시계획을 수립하고, 이에 따라 2013. 12. 3.부터 한국국토정보공사 서부지사를 측량대행자로 지정하여 지적재조사측량을 실시하였다.
+다. 서구 경계결정위원회는 2014. 10. 31. 이 사건 사업지구에 포함된 토지 409필지의 경계결정을 심의·의결하였는데, 이 사건 토지의 면적은 156m2로 결정되어 종전보다 3.9m2 증가하였고, 피고는 같은 날 원고에게 위 경계결정 내용을 통지하였다. 그런데, 원고는 이에 대하여 아무런 이의도 제기하지 않았다.
+라. 서구 지적재조사위원회는 2015. 3. 9. 이 사건 사업으로 면적이 증감된 토지의 조정금 산정 등에 관한 사항을 심의·의결하였는데, 이 사건 토지에 관한 조정금은 개별공시지가를 기준으로 하여 1,895,400원(= 위 3.9m2 × 개별공시지가 486,000원/m2)으로 산정되었다.
+마. 이에 따라 피고는 2015. 5. 4. 원고에게 이 사건 토지에 관한 조정금이 위와 같이 산정되었음을 통보한 다음, 같은 달 14. 원고에게 조정금 1,895,400원을 납부고지(이하 '이 사건 처분'이라 한다)하였다.
+바. 원고는 2015. 7. 14. 피고에게 이 사건 처분에 대한 이의신청을 하였고, 피고는 2015. 8.13. 위 이의신청을 기각하였다.
+[인정근거] 다툼 없는 사실, 갑 제1 내지 8호증의 각 기재, 변론 전체의 취지
+2. 처분의 적법 여부
+가. 원고의 주장
+원고의 남편이 1978. 10. 17.경 이 사건 토지를 매수하여 그 지상에 주택을 신축하였고, 이후 원고가 1998년경 남편으로부터 이 사건 토지와 그 지상 주택을 상속받아 지금까지 살아오고 있는데, 그 동안 토지 현황이나 면적에 아무런 변동이 없었다. 그럼에도 피고는 원고에게 아무런 소명의 기회도 주지 않고 경계결정위원회 등을 개최하여 이 사건 토지의 면적이 증가하였다는 사유로 조정금을 부과하였으므로, 이 사건 처분은 위법하다.
+나. 관계법령
+별지 관계법령 기재와 같다.
+다. 판단
+1) 지적재조사법 제20조 제1항은 지적소관청은 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다고 규정하고 있고, 제3항은 조정금은 지적소관청이 사업지구를 지정하여 고시하였을 때의 개별공시지가를 기준으로 정하거나, 같은 법 제28조에 따른 감정평가법인에 의뢰하여 평가한 감정평가액으로 산정한다고 규정하고 있으며, 제5항은 그 밖에 조정금의 산정에 필요한 사항은 대통령령으로 정한다고 규정하고 있다. 그리고 같은 법 시행령 제12조 제1호는 개별공시지가를 기준으로 조정금을 산정하는 경우 '지적확정조서의 필지별 증감면적'에 '사업지구 지정고시일 당시의 개별공시지가'를 곱하는 방법에 의하도록 규정하고 있다.
+2) 앞서 본 사실 및 관계법령에 변론 전체의 취지를 더하여 인정되는 다음과 같은 사정들 즉, ①피고가 적법하게 지정·고시된 이 사건 사업의 사업시행자로서 2014. 10. 31. 서구 경계결정위원회의 심의·의결을 거쳐 이 사건 토지 면적을 종전에 비해 3.9m2 증가한 156m2로 결정하고, 같은 날 원고에게 위 경계결정을 통지한 점, ②그런데, 원고는 그에 대해 아무런 이의도 제기하지 아니한 점, ③ 피고는 서구 지적재조사위원회의 심의·의결을 거쳐 증가된 면적 3.9m2에 개별공시지가를 적용하여 조정금을 1,895,400원으로 산정하였는데, 그 과정에서 원고에게 위와 같이 조정금이 산정되었음을 이 사건 처분 전에 미리 통지한 점 등을 종합하여 보면, 피고가 지적재조사법에 따라 적법하게 이 사건 사업을 시행하였고, 그 결과 이 사건 토지의 면적이 증가되었다고 할 것이다. 따라서 피고는 이 사건 토지 현황이 변경되었는지 여부와 상관없이 그 면적의 증가를 이유로 토지소유자인 원고에게 지적재조사법에 따라 산정한 조정금을 부과할 수 있으므로, 원고의 주장은 이유 없다.
+3. 결론
+원고의 이 사건 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 박길성(재판장) 김선숙 정철희</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분취소(2023구합62435)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원지방법원 제2행정부 판결
+사건2023구합62435 지적 재조사조정금 부과처분 취소
+원고A
+피고화성시장
+변론종결2023. 11. 2.
+판결선고2023. 11. 23.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2022. 5.30. 원고에게 부과·고지한 지적재조사 조정금 70,889,950원은 이를 취소한다.
+이 유
+1. 처분의 경위
+가. 원고는 2017. 2. 7. 화성시 B리(이하 'B리'라고만 한다) C 주유소용지 3,978m2(이하 '이 사건 제1 토지'라 한다) 및 D 도로 17m2(이하 '이 사건 제2 토지'라 하고, 이사건 제1 토지와 합하여 '이 사건 각 토지'라 한다)에 관한 소유권이전등기를 마쳤다.
+나. 피고는 2020년 8월경 이 사건 각 토지를 포함한 화성시 E 일원(이하 'F지구'라 한다)을 지적재조사 사업지구로 지정·고시하였다.
+다. 원고는 2020년 12월경 이 사건 제1 토지의 면적이 3,978m2에서 4,077.8m2로 99.8m2, 이 사건 제2 토지의 면적이 17m2에서 21.1m2로 4.1m2 각 증가(합계 103.9m2 증가) 된다는 내용의 경계설정합의서를 작성하여 피고에게 제출하였고, 피고는 2021. 4. 29. 위 경계설정합의서와 같이 이 사건 각 토지의 면적을 변경한다는 내용의 지적확정예정 조서를, 2021. 8. 4. 동일한 내용의 경계결정을 각 원고에게 통지하였으며, 2021. 11. 5. 지적재조사 사업완료 공고(사업완료일 2021. 11. 4.)를 하였다.
+라. 피고는 2022. 3. 10. 이 사건 각 토지에 관한 감정평가(이하 '이 사건 1차 감정평가'라 한다) 및 화성시 지적재조사위원회 심의를 거쳐 원고에게 이 사건 각 토지의 면적 증가에 따라 조정금 70,914,550원(= 이 사건 제1 토지 70,359,000원 + 이 사건 제2토지 555,550원, 이상 감정인 2인의 감정평가액을 산술평균한 금액)을 납부할 것을 고지하였다.
+마. 원고는 2022. 4. 19. 피고에게 이의신청을 제기하였고, 피고는 2022. 5. 30. 재차 이 사건 각 토지에 관한 감정평가(이하 '이 사건 2차 감정평가'라 한다) 및 화성시 지 적재조사위원회 심의를 거쳐 원고에게 이 사건 각 토지의 면적 증가에 따른 조정금 70,889,950원[= 이 사건 제1 토지 70,359,000원(이 사건 2차 감정평가에 따라 감정인 2인의 감정평가액을 산술평균한 금액은 70,708,300원이었으나, 2차 화성시 지적재조사 위원회 심의에서 이 사건 1차 감정평가에 따라 감정인 2인의 감정평가액을 산술평균한 금액인 70,359,000원으로 결정) + 이 사건 제2 토지 530,950원(이 사건 2차 감정평가에 따라 감정인 2인의 감정평가액을 산술평균한 금액)]을 납부할 것을 고지하였다(이하 '이 사건 처분'이라 한다). 위 고지서는 2022. 6. 3. 원고에게 송달되었다.
+바. 원고는 이 사건 처분에 불복하여 행정심판을 청구하였으나, 경기도행정심판위원 회는 2022. 11. 28. 원고의 행정심판 청구를 기각하였다.
+[인정 근거] 다툼 없는 사실, 갑 제1 내지 4호증(가지번호 있는 경우 각 가지번호 포함), 을 제 1 내지 17호증의 각 기재 및 영상, 변론 전체의 취지
+2. 이 사건 처분의 적법 여부
+가. 원고의 주장 요지
+지적재조사 사업으로 이 사건 각 토지의 면적이 증가된 부분은 인근 토지의 면적이 이 사건 각 토지에 편입된 것으로, 그 지목이 구거, 도로 등에 해당하여 가치가 없는 토지이다. 그럼에도 이 사건 1, 2차 감정평가는 그 지목이 주유소용지, 도로 등에 해당한다고 보아 면적이 증가된 부분의 감정평가액을 산정하였으므로, 위 각 감정평가는 위법하고, 이를 기초로 한 이 사건 처분도 위법하다.
+나. 관계 법령
+별지 관계 법령 기재와 같다.
+다. 판단
+1) 지적재조사사업은 지적공부의 등록사항이 토지의 실제 현황과 일치하지 아니하는 경우 이를 바로 잡기 위하여 실시하는 사업으로(지적재조사에 관한 특별법 제1조, 제2조 제2호), 지적재조사사업에 따라 새로이 결정된 토지의 경계가 기존 지적공부상 토지의 경계와 다르게 결정·확정되고, 그 결과 새로운 지적공부의 토지 면적이 기존 지적공부의 토지 면적보다 증가 또는 감소되는 결과가 발생한다 하더라도, 특별한 사정이 없는 한 이는 기존 토지가 동일성을 유지한 채 경계설정을 달리 하게 되는 것일 뿐, 기존 토지에 동일성을 달리하는 별도의 새로운 토지가 덧붙여지는 것이 아니다.
+2) 지적재조사에 관한 특별법 제20조 제1항은 '지적소관청은 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 산정하여 징수하거나 지급한다'고 정하고 있고, 지적재조사 업무규정 제25조 제3항 본문은 조정금은 지적확정예정조서의 지번별 증감면적에 법 제20조 제3항에 따른 감정평가액의 제곱미터당 금액 또는 개별공시지가를 곱하여 산정한다'고 정하고 있다. 위 규정들의 문언을 앞서 본 지적재조사사업의 목적 등과 종합하여 보면, 면적이 증감된 당해 '필지별' 또는 '지번별'로 조정금을 산정하고, 그 필지 또는 지번의 가액이 조정금 산정 기준이 된다고 해석하는 것이 타당하다.
+3) 지적재조사법상 경계결정이 완료되면 토지 소유자는 변경된 경계와 면적에 따라 향후 재산권을 행사하게 된다. 그렇다면 지적재조사법상 조정금은 지적재조사 후 확정된 면적을 기준으로 형성될 토지에 상응하는 손실보상이나 이익환수의 성격으로 볼 수 있으므로, 지적재조사로 증감이 발생한 당해 필지의 가액을 기준으로 조정금을 산정하는 것이 규정의 합목적적 해석에도 부합한다.
+4) 따라서 이 사건 각 토지의 조정금은 각 그 현황인 '주유소용지'(이 사건 제1 토지) 또는 '도로'(이 사건 제2 토지)를 기준으로 감정평가한 금액으로 산정되어야 하고, 이 사건 각 토지의 증가된 면적만큼 그 면적이 감소한 인근 토지의 지목을 기준으로 정해져야 하는 것은 아니다. 결국 감정평가를 통해 산정된 이 사건 각 토지의 단위가격을 기초로 한이 사건 처분은 적법하고, 이와 다른 전제에 선 원고의 주장은 받아들일 수 없다.
+3. 결론
+그렇다면 원고의 이 사건 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 김태환(재판장) 박은지 이성열</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분취소(2024구합270)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전주지방법원 제1-2행정부 판결
+사건2024구합270 지적재조사조정금 부과처분 취소
+원고A
+피고전주시 완산구청장
+변론종결2025. 5. 22.
+판결선고2025. 6. 19.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2023. 12. 3. 원고에 대하여 한 지적재조사조정금 부과처분을 취소한다.
+이 유
+1. 당사자 사이에 다툼이 없는 사실
+가. 이 사건 각 토지에 관한 지적재조사 사업 시행 경위
+1) 전주시 완산구 B(공부상 기존 면적 214m2, 이하 '이 사건 제1 토지'라 한다), C (공부상 기존 면적 663m2, 이하 '이 사건 제2 토지'라 한다)를 비롯한 D지구는 2021. 5. 24. 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다) 제7조, 제8조에 기하여 지적재조사지구로 지정·고시되었다.
+2) 위 지적재조사사업에 관한 완산구 경계결정위원회는 2022년경 지적재조사법 제16조에 기하여 이 사건 각 토지 등의 경계를 결정하였다. 위 결정에 따르면, 이 사건 제1 토지의 면적은 252.8m2가 되어 기존에 비해 38.8m2가 증가하고, 이 사건 제2 토지의 면적은 793.1m2가 되어 기존에 비해 130.1m2가 증가한다.
+3) 원고는 2023. 4. 7. 지적재조사법 제17조 제1항에 기하여 위 결정 중 이 사건 제2 토지에 관한 부분에 관하여 이의를 신청하였다. 이에 따라 완산구 경계결정위원회는 2023. 5. 18. 원고의 주장을 받아들여 이 사건 제2 토지의 경계를 새로 결정하였다. 위 결정에 따르면, 이 사건 제2 토지의 면적은 765.6m2가 되어 기존에 비해 102.6m2가 증가한다.
+4) 이 사건 제1, 2 토지의 경계는 위와 같은 과정을 거쳐 지적재조사법 제18조에 기하여 새로이 확정되었는바, 결과적으로 이 사건 제1 토지의 면적은 252.8m2가 되어 기존에 비해 38.8m2가 증가하고, 이 사건 제2 토지의 면적은 765.6m2가 되어 기존에 비해 102.6m2가 증가하게 되었다.
+나. 이 사건 처분의 경위
+1) 피고는 지적재조사법 제20조에서 규정하는 절차를 거친 후 2023. 8. 1. 원고에게, 이 사건 제1 토지에 관한 조정금으로 14,705,200원(= 증가 면적 38.8m2 × m2당 가격 379,000원), 이 사건 제2 토지에 관한 조정금으로 32,524,200원(= 증가 면적 102.6m2 × m2당 가격 317,000원)을 부과하는 처분을 하였다.
+2) 원고는 2023. 8. 22. 지적재조사법 제21조의2 제1항에 기하여 위 조정금 부과처분에 대하여 이의를 신청하였다. 이에 따라 피고는 지적재조사법 제21조에서 규정하는 절차를 거친 후 2023. 12. 1. 이 사건 제1 토지에 관한 조정금으로 14,123,200원(= 증가 면적 38.8m2 × m2당 가격 364,000원), 이 사건 제2 토지에 관한 조정금으로 32,524,200원(= 증가 면적 102.6m2 X m2당 가격 317,000원)을 부과하는 처분(이하 이 사건 처분'이라 한다)을 하였다.
+다. 전심절차 진행 경위
+1) 원고는 2024. 2. 26. 전북특별자치도 행정심판위원회에 이 사건 처분을 취소하여 달라는 내용의 행정심판을 청구하였다.
+2) 위 위원회는 2024. 5. 29. 원고의 청구를 기각하는 재결을 하였고, 2024. 6. 14. 이를 원고에게 통지하였다.
+2. 원고의 주장
+원고 전에 이 사건 제1, 2 토지의 소유자였던 E은, 이 사건 제1, 2 토지의 소유권을 취득한 뒤 그 지상에 건축물을 신축함에 있어 인접한 토지인 F, G(이하 '인접 토지'라 한다)의 소유자와 구두로 인접 토지의 일부분(20여평)을 매수하는 내용의 매매계약을 체결한 다음 매매대금을 지불하는 등 위 각 토지 소유자와 합의 하에 건축물의 담장을 설치하였으나, 위 구두 매매계약에 따른 분할측량이나 이전등기는 따로 하지 않았다. 그리고 원고는 2003. 10. 15. E으로부터 위와 같이 E이 건축한 건축물이 있는 현황을 기초로 하여 이 사건 제1, 2 토지를 매수하고 2004. 1. 6. 그에 따른 소유권이전등기를 마쳤다.
+따라서 이러한 상태를 기초로 이 사건 제1, 2 토지에 관하여 지적재조사측량을 실시하면 E이 매수한 부분과 관련하여 이 사건 제1, 2 토지의 면적은 증가하고 인접 토지의 면적은 줄어들 수밖에 없다. 그러나 이와 관련된 면적, 즉 이 사건 제1, 2 토지에 관한 면적 증가분 중 인접 토지의 면적 감소로 인한 부분은 E이 인접 토지 중 일부분을 매수한 다음 이를 기초로 건축물의 담장 등을 설치한 것으로 인한 결과인바, E으로부터 당시 현황 그대로 이 사건 제1, 2 토지를 매수한 원고 역시 이 부분의 소유권을 취득한 것으로 볼 수 있는데다가 점유취득시효도 완성된 것이다. 인접 토지의 소유자 역시 면적 증가 부분의 권리가 원고에게 귀속된다는 점에 대하여 이의하지 않고 있다.
+그럼에도 이 사건 제1, 2 토지의 면적 증가분 중 인접 토지와 관련된 부분과 나머지를 나누어 정확하게 살펴보지 않고 단지 공부상 면적 증가만을 근거로 조정금을 부과하게 되면 원고는 매매대금을 이중으로 지급하게 되는 결과가 되고, 추후 복잡한 구상 절차를 거쳐야 되는바, 이 사건 처분은 위법하여 취소되어야 한다.
+3. 관계 법령
+[별지] 관계 법령과 같다.
+4. 판단
+개별 토지의 경계 변동 여부와 상관없이 지적공부상 면적 증감이 있는 경우 지적재 조사법 제20조 제1항에 따른 조정금 지급·징수의 대상이 된다(대법원 2020. 5. 14. 선고 2017두68639 판결 등 참조).
+원고는 제2항과 같은 이유로 이 사건 제1, 2 토지에 관한 면적 증가분 중 인접 토지의 면적 감소로 인한 부분에 대해서는 조정금이 부과되어서는 아니 된다고 주장하나, 지적재조사법 제16조 내지 제18조에서 정한 절차에 기한 경계결정으로 인하여 토지의 지적공부상 면적이 변동되는 결과가 발생하였다면, 그에 토지의 매매나 점유취득시효의 완성에 관련된 부분이 포함되어 있다고 하더라도 지적재조사법 제20조 제1항에 기한 조정금을 부과하는 것이 불가피하다. 토지 소유자로서는 이러한 상황을 피하기 위해서는 경계결정 단계에서 해당 부분이 자신 소유 토지에 편입되지 않도록 하여야 할 뿐이다.
+즉, 원고 주장의 전제대로 원고가 기존에 이미 해당 부분의 소유권을 취득하였거나 별도로 점유취득시효까지 완성되었다고 하더라도 공부상 이 사건 제1, 2 토지의 면적증가가 있는 것이 분명한 이상 증가분 전체에 대해서 조정금을 부과하는 것은 불가피하다.
+원고의 주장은 이유 없다.
+5. 결론
+그렇다면 원고의 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 임현준(재판장) 이건희 이동진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분취소청구의소(2023구합25277)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구지방법원 제2행정부 판결
+사건2023구합25277 지적재조사 조정금 부과처분 취소 청구의 소
+원고A
+소송대리인 법무법인 태양
+담당변호사 백오기
+피고대구광역시 동구청장
+변론종결2024. 7. 18.
+판결선고2024. 10. 31.
+주 문
+1. 원고의 청구를 기각한다.
+2. 소송비용은 원고가 부담한다.
+청구취지
+피고가 2023. 9. 11. 원고에게 한 지적재조사 조정금 51,267,200원의 부과처분 중 31,109,600원을 초과하는 부분을 취소한다.
+이 유
+1. 처분의 경위
+가. 원고는 대구 동구 B대 116m2(이하 '이 사건 토지'라 한다)의 소유자이다.
+나. 이 사건 토지가 포함된 C지구(대구 동구 D 일원)는 2022. 4. 20. 지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다)에 따라 C지구 지적재조사 사업(이하 '이 사건 사업'이라 한다) 지구(이하 '이 사건 사업지구'라 한다)로 지정·고시(대구광역시 고시 E)되었고, 피고는 지적소관청으로서 이 사건 사업을 실시하였다.
+다. 대구 동구 경계결정위원회는 2022. 11, 8. 지적조사에 따른 이 사건 사업지구 내 토지들의 경계를 결정하였고, 그 결과 이 사건 토지의 면적이 기존 116m2에서 145.6m2로 29.6m2가 증가되었다.
+라. 피고는 2022. 11. 9. 원고에게 위 경계결정의 내용을 통지하였고, 원고가 이에 대하여 이의하지 아니하여 이에 따라 지적공부가 정리되었으며, 이 사건 토지의 등기 표 제부에도 면적을 145.6m2로 변경하는 등기가 마쳐졌다.
+마. 이 사건 토지의 지적공부상 면적이 증가함에 따라, 피고는 주식회사 F 및 주식회사 G의 감정평가 결과를 산술평균한 금액을 기초로 하여 2023. 5. 24. 원고에게 조정금 52,569,600원(= 1,776,000원 × 29.6m2)을 납부할 것을 고지하였고, 원고는 2023. 6. 15. 피고에게 조정금 액수가 부당하게 과다하다는 이유로 이의신청서를 제출하였다.
+바. 이에 피고는 주식회사 H(이하 'H'이라 한다) 및 주식회사 I(이하 T'이라 한다)에 이 사건 토지에 대한 감정평가를 의뢰하였고, 대구 동구 지적재조사위원회는 두 감정평가 결과를 토대로 조정금을 일부 감액하여 51,267,200원(= 1,732,000원 × 29.6m2)으로 심의· 의결하였다.
+사. 피고는 2023. 9. 11. 원고의 조정금을 위 이의신청 심의결과에 따른 조정금으로 변경하고, 원고에게 이를 통지(이하 '이 사건 처분'이라 한다)하였다.
+[인정근거] 다툼 없는 사실, 갑 제1, 2, 4 내지 13호증, 을 제1호증(가지번호 있는 것은 각 가지번호 포함, 달리 특정하지 않는 한 이하 같다)의 각 기재, 변론 전체의 취지
+2. 원고의 주장
+가. 절차적 하자 주장
+지적재조사법 제20조 제3항에 의하면, 토지소유자협의회가 요청하는 경우에는 개별공시지가로 조정금을 산정할 수 있는데, 피고는 원고에게 위 규정에 따라 개별공시지가를 기준으로 조정금을 산정할 기회를 부여하지 않은 채 개별공시지가가 아닌 H 및 I의 감정평가액을 기초로 조정금을 산정하였다. 또한, 피고는 토지소유자협의회를 적법한 절차에 따라 구성하지도 않았다.
+나. 내용상 하자 주장
+H 및 I은 감정평가를 실시하면서 실제 현황에 따른 이용가능성 등을 고려하지 않았으므로, 위 두 감정평가법인의 감정평가 결과는 부당하다. 그럼에도 피고는 위두감 정평가법인의 감정평가액을 기초로 조정금을 산정하였는바, 이 사건 처분의 m2당 조정
+금액은 이 사건 토지의 개별공시지가에 비하여 과도하게 높게 평가되어 부당하다. 따라서 이 사건 처분 중 이 사건 토지의 개별공시지가를 기준으로 산정한 조정금 31,109,600원(=1,051,000원 × 29.6m2)을 초과하는 부분은 위법하여 취소되어야 한다.
+3. 관계 법령
+별지 '관계 법령' 기재와 같다.
+4. 이 사건 처분의 적법 여부에 관한 판단
+가. 절차적 하자 주장에 관한 판단
+1) 지적재조사법 제13조 제1항은 "지적재조사지구의 토지소유자는 토지소유자 총수의 2분의 1 이상과 토지면적 2분의 1 이상에 해당하는 토지소유자의 동의를 받아 토지소유자협의회를 구성할 수 있다."고 정하고 있고, 같은 법 제20조 제3항 단서는 조정금 산정과 관련하여 "토지소유자협의회가 요청하는 경우에는 제30조에 따른 시·군· 구 지적재조사위원회의 심의를 거쳐 부동산 가격공시에 관한 법률에 따른 개별공시지가로 산정할 수 있다."고 정하고 있다. 그러나 위와 같은 규정만으로 피고가 원고에대하여 토지소유자협의회 구성이 가능하다거나 이를 전제로 개별공시지가를 적용하여 조정금을 산정할 수 있음을 알렸어야 한다거나 그와 관련한 의견제출 기회를 제공하였어야 하는 절차적 의무를 부담한다고 할 수는 없다.
+2) 또한, 앞서 든 증거들, 을 제2호증의 기재 및 변론 전체의 취지에 의하면, 피고는 토지소유자협의회를 구성하기 위하여 2021. 11.경부터 2022. 3.경까지 이 사건 사업지구 전체 토지소유자 170명 중 122명 및 전체 면적 58,139m2 중 44,947m2에 해당하는 소유자의 동의를 받은 사실, 피고는 토지소유자협의회에 참여를 원하는 토지소유자로부터 신청을 받고 이에 따라 6명을 위원으로 하는 이 사건 사업지구 토지소유자협의 회가 구성된 사실이 각 인정되는바, 위 토지소유자협의회의 구성에 어떠한 위법이 있다고 볼 수 없다.
+3) 나아가, 앞서 든 증거들 및 변론 전체의 취지에 의하면, 2022. 6. 10. 이 사건 사업지구 토지소유자협의회에서 조정금 산정에 대한 기준을 감정평가로 한다는 안건이 의결된 사실, 이에 따라 피고가 2개의 감정평가법인에 의뢰하여 평가한 감정평가 결과를 기준으로 조정금이 산정된 사실 등이 인정되고, 이는 지적재조사법 제20조에 따라 이루어진 것으로 적법하다고 보인다. 따라서 '피고가 개별공시지가가 아닌 H 및 I의 감정평가액을 기초로 이 사건 토지에 대한 조정금을 산정하였으므로, 이 사건 처분은 위
+법하다.'는 취지의 원고의 주장은 받아들이지 않는다.
+나. 내용상 하자 주장에 관한 판단
+이 사건 처분에서 정한 조정금이 부당하게 과도한지 여부에 관하여 보건대, 앞서 든 증거들에 변론 전체의 취지에 의하여 인정되는 다음과 같은 사정들, 즉 1 H 및 I은 용도지역, 이용상황, 지목, 주위환경 등을 고려하여 비교표준지를 선정하고, 비교표준지 공시지가의 시점 수정을 위한 지가변동률을 감안함과 아울러 개별요인(가로조건, 접근조건, 환경조건, 획지 조건, 행정적 조건, 기타 조건)을 비교하여 격차율을 산정한 다음, 그 밖의 요인 보정을 위하여 인근의 거래사례 등을 참작하는 방법으로 조정금 산정의 기초가 되는 토지 단가를 산정한 것으로 보이는 점, 2 특히 개별요인 및 그밖의 요인 보정치 산정 등에 있어 합당한 근거 없이 자의적으로 한 것이라고 볼 만한 사정은 없는 점, 3 결국, H 및 I의 감정평가 결과는 모두 관련 법령에 따라 조정금을 적절히 산정한 것으로 보이고 달리 오류가 있다거나 위법함을 인정할 자료가 없는 점, 4 피고는 지적재조사법 제20조 제3항 및 제4항이 정한 바에 따라 위 두 감정평가법인의 감정결과를 기초로 대구 동구 지적재조사위원회의 심의, 의결을 거쳐 조정금을 산정하여 이 사건 처분을 하였으며, 그 과정에 관련 법령을 위반한 잘못이나 오류도 없는 점, 5 원고는 조정금이 개별공시지가에 비하여 과도하다고 주장하고 있을 뿐, 감정평가 내용이나 위 조정금 산정 과정에 구체적으로 어떠한 위법이 있는지에 관하여는 아무런 증명을 하고 있지 않은 점 등을 종합하여 보면, 이 사건 처분의 m2당 조정금액이 지나치게 높게 산정되었다고 보기 어렵다. 따라서 원고의 이 부분 주장도 받아들이지 않는다.
+5. 결론
+그렇다면 원고의 청구는 이유 없으므로 이를 기각하기로 하여 주문과 같이 판결한다.
+판사 이상오(재판장) 전제균 유진홍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지연손해금(2024나51724)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산고등법원 제2-1 민사부 판결
+사건2024나51724 지연손해금
+원고,항소인겸피항소인1. 주식회사 A
+2. B
+3. C
+4. D
+원고들 소송대리인 법무법인 엘에이비파트너스 담당변호사 안진호, 류민희
+피고,피항소인겸항소인1. 주식회사 E
+2. 유한회사 F
+피고들 소송대리인 변호사 임준규
+제1심판결부산지방법원 2024. 1. 24. 선고 2023가합42627 판결
+변론종결2024. 11. 14.
+판결선고2024. 12. 19.
+주 문
+1. 원고들과 피고들의 항소를 모두 기각한다.
+2. 항소비용은 각자 부담한다.
+청구취지 및 항소취지
+1. 청구취지
+주위적으로, 피고들은 연대하여 원고 주식회사 A에게 1,375,150,684원, 원고 B에게 125,013,699원, 원고 C, D에게 각 83,342,466원 및 위 각 돈에 대하여 이 사건 소장 송달 다음날부터 다 갚는 날까지 연 12%의 비율로 계산한 돈을 지급하라. 예비적으로, 피고들은 연대하여 원고 주식회사 A에게 473,586,760원 및 그 중 92,531,760원에 대하여 이 사건 청구취지 및 청구원인 변경신청서 송달 다음날부터 다 갚는 날까지 연 12%의 비율로 계산한 돈을 지급하라.
+2. 항소취지
+가. 원고들
+제1심판결 중 아래에서 추가로 지급을 명하는 돈에 해당하는 원고들 패소 부분을 취소한다. 피고들은 연대하여 원고 주식회사 A에게 901,563,927원, 원고 B에게 125,013,699원, 원고 C, D에게 각 83,342,466원 및 위 각 돈에 대하여 이 사건 소장 송달 다음날부터 다 갚는 날까지 연 12%의 비율로 계산한 돈을 지급하라.
+나. 피고들
+제1심판결 중 피고들 패소 부분을 취소하고, 그 취소 부분에 해당하는 원고 주식회사 A의 청구를 모두 기각한다.
+이 유
+1. 제1심판결 인용
+이 법원이 이 사건에 관하여 설시할 이유는, 제1심 판결문 제4면 네모 상자 안의 표 중 '잔금 270억 원'에 대한 '금액'란의 "원고 A: 21억 4,500만 원"을 "원고 A: 214억 5,000만 원"으로 고치고, 원고들 및 피고들이 당심에서 보충 내지 강조하는 주장과 관련하여 아래 2.항의 판단을 덧붙이는 이외에는 제1심판결 이유 기재와 같으므로, 민사소송법 제420조 본문에 의하여 약어 포함 이를 그대로 인용한다.
+[원·피고들의 주된 항소이유는 제1심에서의 주장과 크게 다르지 않다.
+원고들은 피고들을 상대로 하여, 이 사건 계약에서 애당초 원고들(매도인)의 이 사건 토지 인도의무를 배제하기로 하는 명시적 합의가 있었음을 전제로 '주위적으로, 원고들은 잔금지급일인 2023. 1. 6. 피고들에게 이 사건 토지에 관한 소유권이전등기에 필요한 서류 일체의 이행제공을 하였음에도 피고들이 잔금을 지급하지 않았으므로, 이 사건 계약 제3조 제5항에 따른 미지급 잔금 260억 원에 대한 연 20%의 지연손해금 지급을 구하고, 예비적으로, 원고 A는 원고들이 이행의 제공을 한 시점 이후로 지적재조사 조정금과 재산세를 부과 받았으므로, 피고들은 이 사건 계약 제12조에 따라 원고 A가 납부하였거나 납부하여야 할 위 돈의 지급을 구한다'는 취지의 이 사건 청구를 하였다.
+이에 대하여 제1심은, 주위적 청구에 대하여는 '이 사건 계약에서 이 사건 토지에 대한 원고들의 현실의 인도 의무를 배제하기로 합의한 것을 넘어 간접점유 이전 의무까지 배제하기로 합의한 것으로 볼 수는 없으므로, 민법 제587조의 규정에 따라 그러한 간접점유 이전 의무를 다하지 아니한 원고들은 피고들을 상대로 미지급 잔금에 대한 지연손해금을 청구할 수 없다'고 하여 이를 전부 기각하는 한편, 예비적 청구에 대하여는 '이 사건 계약 제12조에 따라 피고들은 원고 A에게 원고 A가 납부하였거나 납부하여야 할 지적재조사 조정금과 재산세 합계 473,586,760원 및 이에 대한 지연손해금을 지급하여야 한다'는 일부 인용[1] 판결을 선고하였다.
+이러한 제1심의 사실인정과 판단은 정당한 것으로 수긍할 수 있다.]
+2. 추가 판단사항
+가. 인도의무 배제 합의의 여부 및 민법 제587조 적용 가부 관련
+1) 원고들 주장
+이 사건 계약서의 문언에 의하면, 원·피고들은 이 사건 계약에서 매도인인 원고들의 이행의무 중 매매 목적물인 이 사건 토지의 인도의무를 전적으로 배제하기로 합의하였음이 명백하므로 이 사건에서는 임의규정인 민법 제587조가 적용될 수 없고, 따라서 원고들은 이 사건 토지의 인도와 관련된 어떠한 의무도 이행할 필요가 없이 피고들을 상대로 이 사건 계약 제3조 제5항에서 약정한 미지급 잔금 260억 원에 대한 연 20%의 지연손해금을 청구할 수 있다.
+2) 당심 판단
+가) 민법 제587조가 임의규정으로서 당사자 사이의 합의에 의해 그 적용이 배제될 수 있다는 데에는 이론(異論)의 여지가 없다.
+나) 그러나 이 사건 계약서(갑 제2호증)에서 매도인(원고들)이 매매 목적물(이 사건 토지) 인도와 관련된 일체의 의무를 부담하지 않기로 합의하였음이 문언의 객관적 의사 명백하다거나, 계약해석의 일반 원칙상으로 그와 같이 해석된다고 볼 수는 없다. 그 구체적인 이유는 아래와 같다.
+① 이 사건 계약서(갑 제2호증)의 어디에서도 '민법 제587조 적용 배제'를 명시적으로 약정하고 있지 아니하다. 원·피고들 사이에 미지급 잔금에 대한 적용 이율을 연 20%로 하기로 하는 약정(이 사건 계약서 제3조 제5항)이 있었다는 사실을 들어 '민법 제587조 적용 배제'를 묵시적으로나마 합의하였다고 추단할 수도 없다.
+② 이 사건 계약서 제4조 제1항에서 "원고들은 피고들에 대해 매매부동산을 인도할 의무를 부담하지 아니한다."라고 규정하고, 제5조 제2항에서 "원고들은 피고들에게 매매부동산을 인도할 의무는 없고..."라고 규정하고 있음은 인정되나, 위와 같은 규정들이 이루어지게 된 경위가 '매매목적물인 이 사건 토지를 O가 원고들로부터 임차하여 사용하고 있어서, 원고로서는 통상의 부동산매매에서 매도인 측이 부담하는 이행의무들 중 핵심적 내용이 되는 「목적물 인도의무(점유 이전의무)」를 통상적인 방식, 즉 「현실의 인도」 방식으로는 이행할 수 없기 때문이다'는 데에 있었음은 당사자 사이에 다툼이 없으므로, 위 계약 규정들이 가리키는 "인도할 의무"는 「현실의 인도」에 한정하여 해석함이 상당하다.
+③ 원고들이 O와의 임대차계약(점유매개관계)에 기하여 이 사건 토지를 간접점유하고 있음은 당사자 사이에 다툼이 없다. 이 경우 매도인인 원고로서는 O에 대한 채권적 청구권인 목적물반환청구권 양도[2]의 방식으로 매매목적물인 이 사건 토지를 매수인 피고들에게 인도하여야 한다. 그럼에도 원고들은 당심 변론종결시까지도 이러한 의무를 이행하지 아니하였다.[3]
+④ 계약의 해석에서, 특히 당사자 일방이 주장하는 계약의 내용이 상대방에게 중대한 책임을 부과하게 되는 경우에는 그 문언의 내용을 더욱 엄격하게 해석하여야 한다(대법원 2022. 3. 31. 선고 2019다226395 판결 등 참조). 원고들의 주장대로라면, 원고들은 이 사건 토지 인도의무를 전혀 이행하지 않고서도, ㉠ 피고들에게 당초 잔금지급일로 약정한 날의 다음날인 2023. 1. 7.부터 하루당 약 14,246,575원(= 260억 원 × 20% × 1/365, 원 미만은 버림, 이하 같다)의 막대한 지연손해금 책임을 무제한적으로 부과할 수 있는 동시에, ㉡ O로부터는 하루당 약 1,166,666원(= 3,500만 원 × 1/30)의 높은 차임을 계속적으로 수취할 수 있는 이중이득을 취하게 되어,[4] 계약해석의 원칙으로서 고려하여야 할 사회정의와 형평의 이념, 사회일반의 상식과 거래의 통념에도 어긋나는 불합리한 결과가 된다.
+⑤ 한편 원고들은, 이 사건 계약서 제6조 제2항에서 "매수인인 피고들이, 매도인인 원고들과 O 사이의 이 사건 토지에 대한 임대차계약상 임대인의 지위를 당연 승계한다"고 규정하고 있으므로, 위와 같은 점유이전 절차는 따로 필요하지 않다는 취지로도 주장하나, 위 조항은 단지 매매계약 당사자인 원·피고들 사이의 상대적·대내적 약정에 불과하여 제3자인 O에 대하여도 당연히 구속력을 가진다고 보기는 어려울 뿐만 아니라,[5] 물권법의 강행규정성(물권법정주의)에도 반하는 것이어서 받아들일 수 없다.
+다) 그러므로 이와 달리, 원·피고들이 이 사건 계약을 통하여 민법 제587조의 적용을 배제하기로 합의하였음을 전제로 하는 원고들의 이 부분 주장은, 나머지 점에 대하여 더 나아가 살필 필요 없이 이유 없다.
+나. 지적재조사 조정금의 부담자 관련
+1) 피고들 주장
+가) 지적재조사 조정금의 발생시기는 「지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다)」에 따라 경계가 확정된 시점이고, 이 법원의 부산 연제구청장에 대한 사실조회회신결과에 의하면 이 사건 토지 중 G 토지에 관하여 실시된 지적재조사로 인한 경계 확정시점은 2022. 8. 6.인바, 이는 이 사건 계약서 제12조에서 원고들과 피고들 사이의 세금, 공과금 부담책임 분배 기준시점으로서 약정한 잔금지급일(2023. 1. 6.) 이전이므로 지적재조사 조정금 431,055,000원은 원고들이 부담하여야 한다. 설령 그렇지 않다고 하더라도, 이 사건 계약이 체결된 시점(2022. 5.경)은 이미 경계확정을 위한 일필지조사 및 경계조사가 이루어진 이후로서 원고들은 위 G 토지에 관하여 지적재조사 조정금을 납부하여야 함을 알고 있었으므로 이러한 점에 있어서도 위 지적재조사 조정금은 원고들이 부담하여야 한다.
+나) 한편, 이 사건 계약서 제1조 제2항에서는 "본 매매계약은 원고들이 소유한 매매부동산 일체를 현 상태 그대로 피고들에게 매도하기 위한 계약"이라고 규정하고, 제2조에서는 "매매부동산에 대한 면적은 토지대장상의 면적을 기준으로 하되, 실제 측량 등으로 인하여 계약상의 면적의 조정이 있을 경우에도 상호 별도 정산은 없는 것으로 한다"라고 규정함으로써, 지적재조사 조정금이 발생하더라도 원래 소유자인 원고들이 이를 부담하기로 약정하였다.
+2) 당심 판단
+가) 이 사건 계약서 제12조는, 원고들이 잔금지급일인 2023. 1. 6.까지 이 사건 계약서 제4조 제2항의 방법으로 이행의 제공(소유권이전등기에 필요한 서류 일체를 피고들에게 제공)을 하는 것을 조건으로, 위 잔금지급일(2023. 1. 6.) 이후에 부과되는 이 사건 토지에 관한 세금, 공과금 등은 피고들이 부담하기로 약정한 것이 문언상 명백하다. 그런데 원고들이 위 잔금지급일(2023. 1. 6.)까지 이 사건 계약서 제4조 제2항의 방법으로 이행의 제공을 한 사실, 원고 A가 2023. 2. 9.경 부산 연제구청장으로부터 지적재조사법 제20조에 따라 위 G 토지에 관한 지적재조사 조정금 431,055,000원의 납부를 고지받고 그 중 5,000만 원을 납부한 사실은 앞서 본 바와 같으므로, 지적재조사법에 따른 지적재조사 조정금 발생시기(경계확정 시점)가 언제인지, 원고들이 이 사건 계약이 체결될 당시 위 G 토지의 경계확정을 위한 일필지조사 및 경계조사가 이루어진 사실을 알았는지 등의 여부와 상관없이, 이 사건 계약서 제12조에서 약정한 바에 따라 피고들이 위 지적재조사 조정금을 부담함이 타당하다.
+나) 나아가, 이 사건 계약서 제1조 제2항 및 제2조는, 매매계약 당사자인 원·피고들 사이에서 '매매 목적물인 이 사건 토지를 현 상태대로 매매하기로 하고, 향후 측량 결과 실제 면적이 토지대장상의 그것과 다르다는 사실이 밝혀지더라도 이를 이유로 상호 매매대금의 증감을 요구하지 않기로 한다'는 약정임이 명백하므로, 위 조항들은 제3자인 행정관청에 의해 부과되는 이 사건 토지에 관한 세금, 공과금 등을 누가 부담할 것인지를 판단함에 있어서 합당한 근거가 될 수 없다.
+다) 따라서 이에 반하는 피고들의 이 부분 주장은 어느 모로 보나 이유 없다.
+3. 결론
+그렇다면 원고들의 주위적 청구는 이유 없어 이를 모두 기각하고, 원고 A의 예비적 청구는 위 인정범위 내에서 이유 있어 인용하고 나머지 청구는 이유 없어 기각하여야 한다. 제1심판결은 이와 결론을 같이 하여 정당하므로 원고들과 피고들의 항소는 이유 없어 이를 모두 기각하기로 하여, 주문과 같이 판결한다.
+판사 박진웅(재판장) 최희영 임상민
+상하급심 판례2
+미주
+[1] 원고 A가 청구하는 지연손해금(이 사건 청구취지 및 청구원인 변경신청서가 피고들에게 송달된 다음날부터 소송촉진 등에 관한 특례법이 정한 연 12%의 비율로 계산한 지연손해금) 중 일부를 기각하였을 뿐, 원고 A의 예비적 청구를 대부분 인용하였다.
+[2] 민법 제196조(점유권의 양도)
+① 점유권의 양도는 점유물물의 인도로 그 효력이 생긴다. ② 전항의 점유권의 양도에는 제188조제2항, 제189조, 제190조의 규정을 준용한다. 민법 제190조(목적물반환청구권의 양도)
+제3자가 점유하고 있는 동산에 관한 물권을 양도하는 경우에는 양도인이 그 제3자에 대한 반환청구권을 양수인에게 양도함으로써 동산을 인도한 것으로 본다.
+[3] 이와 관련하여 원고들은, "원고들이 간접점유 이전을 위해 어떠한 이행제공을 추가로 하여야 한다는 것인지 불분명하다."고 주장하나(항소이유서 제15면 참조), 이와 같은 이유에서 타당하지 않다.
+[4] 실제로도 원고들은 당심 변론종결일까지 이 사건 토지 임대차와 관련하여 O로부터 월 3,500만 원의 차임을 계속 수령하여 오고 있다. 이 사건 토지 매매와 관련하여 종래 소유자인 원고들로부터 그 점유이전에 대한 적법한 통지를 받은 적이 없는 O로서는 원고들에게 계속하여 월차임을 지급하는 것이 오히려 당연한 것으로 보이고 이러한 결과가 발생하게 된 직접적인 원인은 간접점유의 이전(목적물반환청구권의 양도) 의무를 이행하지 아니한 원고들에게 있다.
+[5] 이 사건 계약서 제6조 제4항에서는 '임차인(O)의 임대차계약 승계 반대 등'으로 임대차계약이 승계되지 못할 가능성도 상정(想定)하고 있는바, 이러한 사정을 뒷받침하는 또 다른 정황이 된다.
+유사판례
+부산지방법원 2024. 1. 24. 선고 2023가합42627 판결 지연손해금
+1. 기초사실 가. 부산 연제구 G, H, I.J 토지는 원고 주식회사 A(구 상호: 주식회사 K, 이하 통칭하여 '원고 A'라 한다)가, 부산 연제구 L, M. N 토지는 원고 B이 3/7 지분을, 원고 C, D가 각 2/7 지분을 보유하고 있다(이하 위 7필지의 토...
+부산지방법원 2018. 1. 11. 선고 2017가단301731 판결 매매대금
+1. 기초 사실 가. 원고들은 2015. 7. 17. 피고들과 별지 목록 기재 각 부동산(이하 통틀어 '이 사건 부동산'이라고 한다)에 관하여 대금 17억 원에 매도하기로 하는 매매계약(이하 '이 사건 매매계약'이라고 한다)을 체결하였는데, 그 주요 내용은 아래와 같다...
+서울중앙지방법원 2018. 10. 5. 선고 2017가합589622 판결 소유권이전등기
+1. 기초사실 가. 원고는 공동주택 신축사업을 위하여 2016. 7. 18. 피고들로부터 서울시 성북구 E, F.G 소재 토지 3,304m2(각 토지의 위치 및 형상은 별지 도면과 같다)와 G 지상 건물 53.36m2(이하 위 각 토지 및 건물을 합하여 '이 사건 각 ...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금부과처분취소(2018구합14931)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>의정부지방법원 제1행정부 판결
+사건2018구합14931 조정금부과처분취소
+원고1. A
+2.B
+3. C
+4.D
+5. E
+6.F
+원고들 소송대리인 변호사 박문우
+피고양주시장
+변론종결2019. 4. 9.
+판결선고2019. 5. 21.
+주 문
+1. 피고가 2018. 2. 13. 원고 A에게 부과처분한 지적재조사 조정금 164,700,000원 중 154,086,000원을 초과한 부분을, 원고 B에게 부과처분한 지적재조사 조정금 42,075, 000원 중 39,363,500원을 초과한 부분을, 원고 C에게 부과처분한 지적재조사 조정금 42,075,000원 중 39,363,500원을 초과한 부분을, 원고 D에게 부과처분한 지적재 조사 조정금 208,800,000원 중 167,400,000원을 초과한 부분을, 원고 E에게 부과처분한 지적재조사 조정금 106,825,500원 중 95,571,000원을 초과한 부분을, 원고 F에게 부과처분한 지적재조사 조정금 46,800,000원 중 43,784,000원을 초과한 부분을 각 취소한다.
+2. 원고들의 나머지 청구를 각 기각한다.
+3. 소송비용은 피고가 부담한다.
+청구취지
+피고가 2018. 2. 13. 원고 A에게 부과처분한 지적재조사 조정금 164,700,000원 중 154,080,000원을 초과한 부분을, 원고 B에게 부과처분한 지적재조사 조정금 42,075,000원 중 39,363,000원을 초과한 부분을, 원고 C에게 부과처분한 지적재조사 조정금 42,075,000원 중 39,363,000원을 초과한 부분을, 원고 D에게 부과처분한 지적 재조사 조정금 208,800,000원 중 167,395,000원을 초과한 부분을, 원고 E에게 부과처분한 지적재조사 조정금 106,825,500원 중 95,570,000원을 초과한 부분을, 원고F에게 부과처분한 지적재조사 조정금 46,800,000원 중 43,783,000원을 초과한 부분을 각 취소한다.
+이 유
+1. 처분의 경위
+가. 피고의 지적재조사사업의 시행 및 조정금의 산정
+1) 피고는 2015. 11. 6. 양주시 G 일원 185필지 172,811m2를 사업지구로 하여 'H 지구 지적재조사사업'(이하 '이 사건 사업'이라 한다)의 실시계획(사업기간 2016. 1.경부터 2017. 12.경까지)을 수립하고 사업구역 내 토지소유자들로부터 동의를 받아 이 사건 사업을 시행하였다.
+2) 피고는 지적재조사측량을 거친 다음 양주시 경계결정위원회의 의결을 통하여 지적재조사에 따른 이 사건 사업구역 내 토지들의 경계를 결정하고 2017. 8.경 토지소유자들에게 경계결정 내용을 통지하였다. 한편 양주시 지적재조사위원회는 2017. 8. 18. 경계 확정으로 인하여 지적공부상의 면적 증감이 발생되는 토지에 대한 조정금 산정기준에 관한 심의를 한 결과, 조정금 산정기준은 감정평가법인에서 평가한 '감정평가 액'으로 결정하고, 감정평가액 산정기준일은 경계확정일로 정하기로 의결하였다.
+3) 피고는 2017. 9. 27. 이 사건 사업구역 내 조정금 산정대상 토지에 대하여 주식회사 I과 주식회사 J에 각 감정평가를 의뢰하였고, 양주시 지적재조사위원회는 2017. 11. 15. 회의를 개최하여 위 각 회사가 평가한 감정평가액을 토대로 조정금을 결정하였다.
+나. 원고들에 대한 조정금 부과
+1) 원고들은 이 사건 사업구역 내 양주시 K동 소재 토지 소유자들로서, 원고들이 소유한 각 토지의 지적공부상의 면적이 이 사건 사업의 시행에 따른 경계 확정으로 증가되었고, 이에 피고는 2018. 2. 13. 원고들에게 증가된 면적에 대한 조정금(아래 표1 '조정결과' 기재 조정금이다)을 각 부과하였다.
+2) 원고들은 2018. 2. 28.부터 2018. 4. 3.까지 사이에 피고에게 이 사건 각 처분에 따른 조정금 액수가 부당하게 과다하다는 이유로 이의신청서를 각 제출하였다. 양주시 지적재조사위원회는 2018. 5. 14. 원고들의 이의신청에 대한 적정성을 심의한 후, 원고 D, E에 대하여는 조정금을 일부 감액하고, 나머지 원고들에 대한 조정금은 기존 원안대로 심의·의결하였고(아래 표 '이의신청결과' 기재 조정금이다), 피고는 2018. 7. 26. 원고들에게 이의신청결과에 따른 각 조정금을 납부할 것을 통지하였다.
+3) 원고들 소유의 토지에 대한 구체적인 조정금 부과 내역은 아래 표 기재와 같다(이하 원고들 소유의 아래 토지를 통틀어 '이 사건 각 토지'라고 하고, 원고들에 대한 2018. 2. 13.자 각 조정금 부과처분을 '이 사건 각 처분'이라 한다).
+이 유 표
+다. 이 법원의 감정촉탁결과
+이 법원의 감정촉탁에 따라 R감정평가사사무소 감정인 S이 이 사건 각 토지의 경 계확정일(원고들이 피고로부터 경계에 관한 결정을 통지받은 날부터 60일 이내에 이의신청을 하지 않음으로써 경계 결정이 확정된 날이다)을 기준으로 산정한 감정평가액은 아래 표 기재와 같다(위 감정촉탁결과를 이하 '법원감정'이라 한다).
+이 유 표
+[인정근거] 다툼 없는 사실, 갑 제1, 3호증, 을 제1 내지 4, 6, 7호증(가지번호 있는 것은 가지번호 각 포함)의 각 기재, 이 법원의 R감정평가사사무소 감정인 S에 대한 감정촉탁결과, 변론 전체의 취지
+2. 이 사건 각 처분의 적법 여부
+가. 원고들 주장의 요지
+1) 지적재조사에 관한 특별법 제20조 제3항 단서에 의하면, 조정금의 산정은 토지 소유자협의회가 요청하는 경우 개별공시지가로 산정할 수 있다고 규정하고 있음에도, 피고가 이에 따르지 않고 감정평가업자가 평가한 감정평가액을 기준으로 이 사건 각 부과처분을 한 것은 위법하다.
+2) 이 사건 조정금 산정의 기준이 된 주식회사 I과 주식회사 J의 각 감정평가에는 표준지 선정, 개별요인의 적용 등에 있어서 위법이 있음에도 피고는 위 각 감정평가결과를 산술 평균한 금액을 기준으로 조정금을 산정하여 이 사건 각 부과처분을 하였고, 법원감정에서 산정된 조정금도 지나치게 과다하다.
+나. 관계 법령
+별지 기재와 같다.
+다. 판단
+1) 개별공시지가로 산정되어야 한다는 주장
+가) 지적재조사에 관한 특별법 제20조 제3항은 "조정금은 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가 및 감정평가사에 관한 법률에 따른 감정평가업자가 평가한 감정평가액으로 산정한다. 다만, 토지소유자협의회가 요청하는 경우에는 제30조에 따른 시·군·구 지적재조사위원회의 심의를 거쳐 부동산 가격공시에 관한 법률에 따른 개별공시지가로 산정할 수 있다"고 규정하고 있는바, 이는 지적재조사사업에 의한 조정금의 산정은 감정평가업자가 평가한 감정평가액으로 산정함을 원칙으로 하고, 지 적재조사 사업구역에 토지소유자협의회가 구성되어 토지소유자협의회가 요청한 경우는 개별공시지가로 산정할 수 있도록 예외를 두고 있을 뿐이다. 또한 위 법 제13조 제1항에 의하면, "사업지구의 토지소유자는 토지소유자 총수의 2분의 1 이상과 토지면적 2분의 1 이상에 해당하는 토지소유자의 동의를 받아 토지소유자협의회를 구성할 수 있다"고 규정하고 있어서 토지소유자협의회의 구성도 토지소유자들이 임의로 결정할 수 있는 것이다.
+나) 이 사건에 관하여 보건대, 을 제7호증의 기재에 변론 전체의 취지를 종합하면, 피고는 2015. 11. 9. 이 사건 사업구역 내 토지소유자들에게 이 사건 사업에 대한 실시계획 수립에 대한 안내를 하면서 토지소유자 협의회 구성에 관한 동의서를 동봉함으로써 관련 내용도 함께 안내하였으나, 이 사건 사업구역 내에 별도로 토지소유자협의회가 구성되지 아니한 사실이 인정된다. 따라서 이 사건 조정금 산정에 관하여 토지 소유자협의회가 구성되어 있음을 전제로 하는 지적재조사에 관한 특별법 제20조 제3항 단서는 적용될 여지가 없으므로, 피고가 이 사건 각 토지에 관한 조정금을 감정평가업자가 평가한 감정평가액으로 산정한 것 자체에 위법이 있다고 할 수 없다. 따라서 원고들의 이 부분 주장은 이유 없다.
+2) 감정평가에 관한 주장
+가) 보상금 증감에 관한 소송에 있어서 재결의 기초가 된 각 감정기관의 감정평가와 법원감정인의 감정평가가 평가방법에 있어 위법사유가 없고 개별요인비교를 제외한 나머지 가격산정요인의 참작에 있어서는 서로 견해가 일치하나 개별요인비교에 관하여만 평가를 다소 달리한 관계로 감정 결과에 차이가 생기게 된 경우 그 중 어느 감정평가의 개별요인비교의 내용에 오류가 있음을 인정할 자료가 없는 이상 각 감정평가 중 어느 것을 취신하여 정당보상가액으로 인정하는가 하는 것은 그것이 논리칙과 경험칙에 반하지 않는 이상 법원의 재량에 속한다(대법원 2005. 1. 28. 선고 2002두4679판결 등 참조). 지적재조사법 제20조 제3항에 의하면, 조정금도 경계가 확정된 시점을 기준으로 감정평가 및 감정평가사에 관한 법률에 따른 감정평가업자가 평가한 감정평가액으로 산정하도록 정하고 있는바, 조정금 부과의 기초가 된 감정평가와 법원감정인의 감정평가가 모두 위법사유가 없는 경우에는 그 중 어느 감정평가의 품등비교 내용 등에 오류가 있음을 인정할 자료가 없는 이상, 각 감정평가 중 어느 것을 더 신뢰하는가 하는 것은 사실심 법원의 재량에 속한다고 봄이 상당하다.
+나) 앞서 든 증거들에 변론 전체의 취지를 더하여 인정되는 다음과 같은 사정들, 즉 1 주식회사 I과 주식회사 J, 법원감정인은 모두 개별평가에 있어 이 사건 각 토지의 접근조건, 환경조건, 획지조건, 행정적조건, 기타조건에 관하여 각 세부사항별로 상세하게 평가하였고, 그 밖의 요인 보정치 산정에 있어서도 용도지역, 이용상황 등을 고려하여 거래사례를 선정하고 이 사건 각 비교표준지와의 개별요인 비교·평가를 거쳐 감정결과에 반영한 점, 2 이와 같은 개별요인 분석은 객관적인 측정절차에 따른 구체적인 수치로의 확정이 불가능하며 감정평가업자의 전문적인 견해에 따라 다소 차이가 있을 수밖에 없는 점 등을 고려하면, 이 사건 각 처분의 조정금 산정을 위한 주식회사 I과 주식회사 J의 각 감정평가와 법원감정결과는 모두 관련 법령에 따라 조정금을 적절히 산정한 것으로 보이고 달리 위 각 감정의 비교표준지 및 거래사례의 선정, 품등비교 내용, 방식 등에 오류가 있음을 인정할 자료가 없으므로 위 각 감정은 모두 적법하다고 할 것이나(피고는, 인근지역의 거래사례 참작이나 획지조건 평가에 있어 법원감정이 적절하지 않다는 취지로 주장하나, 을 제5호증의 기재만으로는 법원감정에 어떠한 오류가 있다고 보기 어렵다), 법원감정이 이 사건 각 토지의 특성과 가격형성상 제 반요인 등을 보다 더 적절히 반영하였다고 판단되므로 법원감정에 따라 조정금을 산정하기로 한다.
+3) 따라서 이 사건 각 처분 중 법원감정에 따라 산정된 정당한 조정금, 즉 원고 A에 대한 조정금 164,700,000원 중 154,086,000원을 초과한 부분, 원고 B에 대한 조정금 42,075,000원 중 39,363,500원을 초과한 부분, 원고 C에 대한 조정금 42,075,000원중 39,363,500원을 초과한 부분, 원고 D에 대한 조정금 208,800,000원 중 167,400,000원을 초과한 부분, 원고 E에 대한 조정금 106,825,500원 중 95,571,000원을 초과한 부분, 원고 F에 대한 조정금 46,800,000원 중 43,784,000원을 초과한 부분은 모두 위법하다고 할 것이므로, 이를 각 취소한다.
+3. 결론
+그렇다면 원고들의 청구는 위 인정범위 내에서 이유 있어 인용하고, 나머지 청구는 이유 없어 각 기각하기로 하여 주문과 같이 판결한다.
+판사 변민선(재판장) 안금선 김미경
+별지
+별지
+유사판례
+부산지방법원 2019. 4. 19. 선고 2018구합1207 판결 조정금부과처분취소
+1. 처분의 경위 가. 피고의 지적재조사 사업 실시 1) 원고는 부산 해운대구 B 대 639m2(이하 '이 사건 토지'라 한다)의 소유자이다. 2) 피고는 2016. 1. 26. 이 사건 토지를 포함한 부산 해운대구 C 일원에서 사업기간 2016. 1. 경부터 2017...
+부산지방법원 2020. 10. 8. 선고 2019구합23969 판결 조정금부과처분취소
+1. 처분의 경위 가. 원고는 지적재조사에 관한 특별법에 따라 부산 중구 C 일원에 추진한 'D지구 지 적재조사사업(이하 '이 사건 사업'이라 한다)'의 사업지구 내 B(이하 '이 사건 토지'라 한다)의 소유자이고, 피고는 위 사업의 시행자이다. 나. 부산광역시장은 지...
+대구지방법원 2020. 5. 20. 선고 2019구합271 판결 지적재조사조정금부과처분취소
+1. 처분의 경위 가. 피고의 지적재조사사업 실시 1) 원고는 대구 동구 B 대 321㎡(이하 '이 사건 토지'라 한다)의 소유자이다. 2) 피고는 2015. 12. 10. 이 사건 토지를 포함한 대구 동구 C 일원을 사업지구로 하여 D 지적재조사사업(이하 '이 사건 ...
+유사판례 모두 보기
+사건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지적재조사조정금이의신청결정취소청구의소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2021</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2225"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>10673)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전고등법원 제1행정부 판결
+사건2021누10673 지적재조사 조정금 이의신청결정 취소청구의 소
+원고,항소인A
+소송대리인 법무법인 세계로
+담당변호사 이현, 지종엽
+피고,피항소인대전광역시 유성구청장
+제1심판결대전지방법원 2021. 2. 10. 선고 2019구합106995 판결
+변론종결2022. 4. 21.
+판결선고2022. 6. 16.
+주 문
+1. 제1심판결을 취소하고, 이 사건 소 중 2018. 10. 8.자 지적재조사 조정금 부과처분의 무효확인을 구하는 부분을 각하한다.
+2. 이 법원에서 변경한 원고의 청구에 따라 피고가 2019. 2. 25. 원고에 대하여 한 이의신청 결과통지 및 그에 따른 조정금 납부통지 처분을 취소한다.
+3. 소송총비용 중 1/3은 원고가 부담하고, 나머지는 피고가 부담한다.
+청구취지 및 항소취지
+1. 청구취지
+(1) 피고가 2018. 10. 8. 원고에 대하여 한 지적재조사 조정금 부과처분은 무효임을 확인한다. (2) 피고가 2019. 2. 25. 원고에 대하여 한 이의신청 결과통지 및 그에 따른 조정금 납부통지 처분을 취소한다[원고는 이 사건 소 제기 당시 2019. 2. 21.자 지적재조사 조정금 이의신청에 대한 결정처분의 취소를 구하다가 제1심에서 (1)항 기재와 같이 청구취지를 변경하였고, 그 후 항소심에 이르러 다시 (2)항 기재와 같은 청구취지를 추가하였다].
+2. 항소취지
+제1심판결을 취소한다. 피고가 2018. 10. 8. 원고에 대하여 한 지적재조사 조정금 부과처분은 무효임을 확인한다.
+이 유
+1. 처분의 경위
+이 법원이 이 부분에 설시할 이유는 아래와 같이 고치는 것 외에는 제1심판결 이유 중 제1항 기재와 같으므로, 행정소송법 제8조 제2항, 민사소송법 제420조 본문에 따라 이를 그대로 인용한다.
+○ 제1심판결 제2면 아래에서 제6, 7행의 "(이하 아래 바.항과 같이 감액되고 남은 조정금에 대한 부분을 '이 사건 처분'이라 한다)."를 "(이하 '이 사건 처분'이라 한다)"로 고친다.
+○ 제1심판결 제2면 아래에서 제2행의 "납부고지를 하였다."를 "납부고지(이하 '이 사건 이의결정 통지'라 한다)를 하였다."로 고친다.
+2. 원고의 주장 요지
+가. 이 사건 처분 및 이 사건 이의결정 통지는 다음과 같은 위법이 있다.
+1) 이 사건 토지에 관한 감정평가 기준시점의 위법
+지적재조사에 관한 특별법(이하 '지적재조사법'이라 한다) 제20조 제3항에 의하면 이 사건 토지에 대한 감정평가 기준 시점은 같은 법 제18조에 따른 경계확정 시점, 즉 '경계결정에 대한 이의신청 기간에 이의를 신청하지 않음으로써 경계가 확정된 시점'이므로, 원고가 피고로부터 이 사건 경계결정 통지를 받은 2017. 1. 13.로부터 60일이 경과한 2017. 3. 13.이 감정평가 기준시점이 되어야 한다. 그러나 피고는 감정평가 기준시점을 임의로 2018. 6. 29.로 선정하여 조정금을 산정하였다.
+2) 비교표준지 선정의 위법
+감정평가에 관한 규칙 제2조 제9호, 제14조 제2항 제1호, 감정평가 실무기준에 의하면, 비교표준지는 대상토지 인근에 위치하되 그 주변 환경 요인 등이 대상토지와 동일하거나 유사한 별개의 토지를 선정하여야 한다. 그런데 피고는 이 사건 토지와 별개의 토지를 비교표준지로 선정하지 않고, 대상토지인 이 사건 토지 그 자체를 비교표준지로 선정한 위법이 있다.
+3) 재량권 일탈·남용
+피고는 이 사건 감정평가 시 증가된 토지는 그 기존 지목 및 용도지역 등을 기준으로 편입된 면적에 관한 부과 조정금을 산정하고, 편입됨으로써 감소된 토지 역시 기존 현황대로 수령 조정금을 산정하는 방법을 취하였는데, 이러한 피고의 산정방법은 '토지면적의 증감으로 발생한 토지소유자 간 이해 조정'이라는 지적재조사 목적에 반하고, 지적재조사법령상 위와 같은 산정방법에 관한 규정도 없다. 따라서 이 사건 처분 및 이 사건 이의결정 통지는 지적재조사의 목적에 위배되고 법령의 규정 없이 재량권을 일탈·남용한 위법이 있다.
+나. 이 사건 처분에 있는 이러한 위법은 중대하고 명백한 것이므로 이 사건 처분의 무효 확인을 구한다. 설령 그와 같은 위법의 정도가 중대·명백하지 않더라도 원고는 취소소송의 제소기간을 준수하였으므로, 이 사건 처분의 취소를 구한다. 아울러 원고는 이 사건 이의결정 통지에도 그와 같은 위법이 동일하게 존재하므로 그 취소를 구한다.
+3. 관련 법령
+별지 기재와 같다.
+4. 이 사건 처분의 무효확인을 구하는 부분의 적법 여부
+가. 이 사건 처분이 소멸하였는지 여부
+이 사건 처분과 이 사건 이의결정 통지는, 모두 F지구 지적재조사 사업지구에 있는 원고 소유의 이 사건 토지의 면적이 864m²에서 1,052m²로 경정등기되어 지적공부상 면적이 증가함에 따라 그 조정금을 산정하는 내용으로서 동일한데, 아래에서 보는 것처럼 원고가 피고의 이 사건 처분에 대하여 지적재조사법 제21조의2에 따라 이의신청을 하여 피고가 조정금을 다시 재산정, 심의·의결하는 절차를 거친 결과 그 조정금이 종전과 동일하게 산정되었다는 취지로 항고소송의 대상적격, 즉 처분성이 인정되고 최종적으로 결정한 새로운 조정금의 통지를 한 이상 당초처분인 이 사건 처분은 소멸하여 이미 효력을 잃었다고 봄이 타당하다.
+나. 이 사건 처분의 제소기간 준수 여부[1]
+2) 원고는 대전광역시 행정심판위원회에 이 사건 이의결정의 취소를 구하는 행정심판 청구를 하였다가 2019. 6. 24. 기각재결을 받았고, 그 후 2019. 9. 27. 이 사건 소 제기 당시 2019. 2. 21.자 지적재조사 조정금 이의신청에 대한 결정처분의 취소를 구하다가 제1심 법원의 석명준비명령에 따라 2020. 12. 2. 이 사건 처분의 무효확인을 구하는 것으로 청구취지를 변경하였는데, 항소심에 이르러 다시 이 사건 이의결정 통지의 취소를 구하는 청구취지를 추가하였다. 따라서 원고가 제1심법원으로부터 이 사건 이의결정의 처분성을 검토하라는 취지의 석명준비명령을 받은 다음 이 사건 처분이 있었던 2018. 10. 8.로부터 1년이 경과한 2020. 12. 2.에야 이 사건 처분의 무효확인을 구하는 것으로 청구취지를 변경한 이상 그 제소기간을 경과하였다고 봄이 타당하다.
+3) 한편 아래에서 보는 것처럼 이 사건 이의결정 통지는 이 사건 처분과는 별개로 항고소송의 대상이 되는 '처분'에 해당하므로, 원고의 2020. 12. 2.자 청구취지 변경이 처분성이 인정되지 아니하는 행정청의 행위를 항고소송의 대상으로 삼았다가 처분성이 인정되는 행위를 대상으로 청구취지를 변경 또는 정정하여 명확히 한 것에 해당한다거나 당초의 소 제기시를 기준으로 제소기간의 준수여부를 살펴야 하는 밀접한 관계에 있는 청구로 변경한 것이라고 볼 수 없다.
+다. 소결론
+따라서 이 사건 처분은 이 사건 이의결정 통지에 의하여 소멸하였을 뿐만 아니라 그 취소를 구하는 부분의 경우 원고가 그 제소기간을 준수하지도 못하였으므로, 이 사건 소 중 이 사건 처분의 무효확인 또는 취소를 구하는 부분은 부적법하다.
+5. 이 사건 이의결정 통지의 위법 여부
+가. 이 사건 이의결정 통지의 처분성
+1) 어떠한 처분이 수익적 행정처분을 구하는 신청에 대한 거부처분이 아니라고 하더라도, 해당 처분에 대한 이의신청의 내용이 새로운 신청을 하는 취지로 볼 수 있는 경우에는, 그 이의신청에 대한 결정의 통보를 새로운 처분으로 볼 수 있다(대법원 2022. 3. 17. 선고 2021두53894 판결 등 참조).
+2) 지적재조사법 제21조의2가 신설되어 조정금에 대한 이의신청 절차가 법률상 절차로 변경되었으므로 그 절차적 권리는 이제 법률상 권리로 볼 수 있다. 원고가 이의신청을 하기 전에는 피고의 이 사건 처분에 관한 통지만 존재하였고 원고는 '신청' 자체를 한 적이 없으므로, 구체적인 사유를 주장하며 그 소명자료를 첨부한 원고의 이의신청은 새로운 신청으로 볼 수 있다. 또한 이 사건 이의결정 통지는 그 문언상 종전 통지와 별도로 심의·의결하였다는 내용임이 명백하고, 단순히 이의신청을 받아들이지 않는다는 내용에 그치는 것이 아니라 조정금에 대하여 다시 재산정, 심의·의결절차를 거친 결과, 그 조정금이 종전 금액과 동일하게 산정되었다는 내용을 알리는 것이므로, 새로운 조정금의 통지에 해당한다. 이러한 사정에 비추어 보면, 이 사건 이의결정 통지는 이 사건 처분 또는 그 통지와는 별도로 행정쟁송의 대상이 되는 '처분'으로 봄이 타당하다(대법원 2022. 3. 17. 선고 2021두53894 판결 등 참조).
+나. 이 사건 이의결정 통지의 제소기간 준수 여부
+1) 선행처분의 취소를 구하는 소가 그 후속처분의 취소를 구하는 소로 교환적으로 변경되었다가 다시 선행처분의 취소를 구하는 소로 변경된 경우 후속처분의 취소를 구하는 소에 선행처분의 취소를 구하는 취지가 그대로 남아 있었던 것으로 볼 수 있다면 선행처분의 취소를 구하는 소의 제소기간은 최초의 소가 제기된 때를 기준으로 정하여야 할 것이다(대법원 2013. 7. 11. 선고 2011두27544 판결 등 참조). 이러한 법리는 후속처분의 취소를 구하는 소가 선행처분의 취소를 구하는 소로 교환적으로 변경되었다가 다시 후속처분의 취소를 구하는 소로 변경된 경우에도 마찬가지라 할 것이다.
+2) 갑 제4, 5호증 및 변론 전체의 취지를 종합하여 보면 아래의 사실이 인정된다.
+① 피고는 2018. 10. 8. 원고에 대하여 이 사건 처분을 하면서 조정금에 대한 이의신청 이외에 행정심판 내지 행정소송에 관한 불복절차를 안내하지 않았다.
+② 피고는 2019. 2. 25.에서야 비로소 원고에게 조정금 이의신청 토지 금액결정 및 납부통지를 하면서 '해당 처분내용에 이의가 있을 경우 행정심판법 및 행정소송법이 정한 기간 내에 행정심판을 청구하거나 행정소송을 제기할 수 있다'고 안내하였다.
+③ 원고는 2019. 4. 24. 대전광역시 행정심판위원회에 이 사건 이의결정의 취소를 구하는 행정심판 청구를 하였으나, 대전광역시 행정심판위원회는 2019. 6. 24. 기각재결을 하였고, 원고는 2019. 7. 3. 그 재결서 정본을 송달받았다.
+④ 피고는 이 법정에서 2019. 2. 25. 원고에게 조정금 이의신청 토지 금액결정 및 납부통지를 하면서 행정심판청구 기간 및 행정소송 제소기간과 관련하여 언급한 처분은 이 사건 처분이 아닌 이 사건 이의결정이라고 답하였다.
+3) 앞에서 인정한 사실과 원고의 청구취지 변경의 경위 등을 앞서 본 법리에 비추어 보면, 원고는 2020. 12. 2. 이 사건 이의결정 통지의 처분성이 인정되지 않음을 전제로 이 사건 처분의 무효확인 또는 취소를 구하는 것으로 청구취지를 변경한 것이므로, 원고의 2020. 12. 2.자 청구취지 변경에도 불구하고 이 사건 이의결정 통지의 처분성이 인정되는 경우에 이 사건 이의결정 (통지)의 취소를 구하는 취지가 그대로 남아 있었다고 볼 수 있고, 원고가 2022. 4. 8. 청구취지 및 청구원인 변경신청을 하면서 다시 이 사건 이의결정 통지의 취소를 구하는 취지를 추가한 이상 원고의 소 중 이 사건 이의결정 통지의 취소를 구하는 부분은 취소소송의 제소기간을 준수하여 적법하게 제기되었다고 봄이 타당하다.
+다. 이 사건 이의결정 통지의 위법 여부
+1) 감정평가 기준시점의 위법 주장에 관한 판단
+가) 지적재조사법에 따른 경계의 확정 및 사업완료 공고 절차는 다음과 같다.
+① 지적소관청이 경계결정위원회로부터 경계에 관한 결정을 통지받은 후 지체없이 토지소유자에게 통지(제16조 제6항) ⇒ ② 경계에 관한 결정을 통지받은 토지소유자는 이에 불복하는 경우 통지를 받은 날부터 60일 이내에 지적소관청에 이의신청 가능(제17조 제1항) ⇒ ③ 토지소유자가 제17조 제1항에 따른 이의신청 기간에 이의를 신청하지 아니하면 경계가 확정(제18조 제1항) ⇒ ④ 지적소관청은 제18조에 따른 경계 확정으로 지적공부상의 면적이 증감된 경우, 제18조에 따라 경계가 확정된 시점을 기준으로 감정평가업자가 평가한 감정평가액으로 산정한 조정금을 부과 또는 징수(제20조 제1항, 제3항) ⇒ ⑤ 지적재조사지구 내 모든 토지에 대하여 제18조에 따른 경계 확정이 있었을 때에는 사업완료 공고를 하고 관계 서류를 일반인이 공람하도록 함(제23조 제1항)
+나) 별지 기재 지적재조사법의 내용에 의하면, 지적재조사지구의 경계는 지적재조사법 제18조에 따라 토지소유자나 이해관계인의 이의신청 여부나 그에 대한 결정 또는 행정소송의 결과에 따라 개별적으로 정하여질 뿐이고, 지적재조사법 제23조, 제24조도 지적재조사지구에 있는 토지의 경계가 개별적으로 확정됨을 전제로 "지적재조사지구에 있는 '모든 토지에 대하여' 제18조에 따른 경계 확정이 있었을 때"를 사업완료 공고 및 공람시기로 정하되 예외적으로 경계가 확정되지 아니한 토지의 면적이 지적재조사지구 전체 토지면적의 10분의 1 이하인 경우 또는 경계가 확정되지 아니한 토지소유자의 수가 지적재조사지구 전체 토지소유자 수의 10분의 1 이하인 경우 모든 토지에 대한 경계 확정이 이루어지지 않더라도 사업완료 공고를 할 수 있다고 정하고 있으며, 그 경우 '경계미확정 토지'로 기재하여 지적공부를 정리할 수 있다는 규정을 두고 있다. 반면 조정금의 산정에 관한 지적재조사법 제20조 제3항은 조정금을 제18조에 따라 경계가 확정된 때를 기준으로 한다고 정할 뿐 '지적재조사지구에 있는 모든 토지에 대하여 경계가 확정되었을 때'를 기준으로 조정금을 산정한다고 정한 것은 아니다.
+다) 이와 같은 지적조사법의 내용과 앞서 인정한 사실을 더하여 보면, 지적재조사지구 내의 모든 토지에 대하여 경계 확정이 있었을 때 또는 사업완료 공고가 이루어진 때를 기준으로 조정금을 산정하여야 한다고 볼 수 없고, 지적재조사지구 내의 토지별로 경계가 확정된 때를 기준으로 조정금을 산정하여야 한다. 결국 이 사건 토지에 대한 경계는 원고가 이 사건 경계결정 통지를 받은 2017. 1. 13.로부터 이의신청기간인 60일이 도과한 2017. 3. 13. 확정되었으므로, 이 사건 토지에 대한 감정평가는 2017.3. 13.을 기준시점으로 하여 이루어져야 한다. 그런데 감정평가서(갑 제6호증)에 의하면 이 사건 토지에 대한 감정평가의 기준시점은 위와 같은 경계확정일이 아닌 2018. 6. 29.(사업완료 공고일)인 사실을 인정할 수 있는바, 경계확정 시점이 아닌 다른 일자를 기준으로 한 감정평가액을 바탕으로 이 사건 토지에 대한 조정금을 산정한 이 사건 이의결정 통지는 위법하다.
+2) 비교표준지 선정의 위법 주장에 관한 판단
+가) 별지 기재 부동산 가격공시에 관한 법률, 감정평가 및 감정평가사에 관한 법률 및 감정평가에 관한 규칙의 내용을 종합하여 보면, 표준지는 국토교통부장관이 토지가 이용상황이나 주변환경, 그 밖의 자연적·사회적 조건이 일반적으로 유사하다고 인정되는 일단의 토지 중에서 선정한 토지를 의미하고, 국토교통부장관은 표준지에 대하여 매년 공시기준일 현재의 단위면적당 적정가격(표준지공시지가)을 조사·평가한 다음에 이를 공시하여야 하며, 감정평가법인등이 토지를 감정평가하는 경우에는 그 토지와 이용가치가 비슷하다고 인정되는 「부동산 가격공시에 관한 법률」 에 따른 표준지공시지가를 기준으로 대상토지의 현황에 맞게 시점수정, 지역요인 및 개별요인 비교, 그 밖의 요인의 보정(補正)을 거쳐 대상토지의 가액을 산정하여야 한다.
+나) 수용대상토지 자체가 표준지인 경우에는 그 표준지에 관한 공시지가를 그대로 반영하여 보상금을 산정하면 되는 것이고, 용도지역, 이용상황, 지목, 주변환경 등이 유사한 표준지를 새로이 선정하여 표준지와의 개별성 및 지역성의 비교를 할 필요는 없다(대법원 1995. 5. 12. 선고 95누2678 판결 등 참조). 따라서 대상토지인 이 사건 토지 자체를 비교표준지로 선정하여 감정평가를 한 것에는 위법이 없다. 원고의 이 부분 주장은 이유 없다.
+3) 재량권 일탈·남용 주장에 관한 판단
+지적재조사법 제20조의 규정에 의하면, 지적재조사법은 지적소관청에게 감정평가액에 따라 선정한 조정금을 징수 또는 부과하도록 규정하고 있을 뿐 조정금의 부과 여부 및 그 액수에 관하여 어떠한 재량권을 부여하고 있다고 볼 수 없으므로, 이 사건 이의결정은 기속행위에 해당한다. 따라서 이 사건 이의결정이 재량행위임을 전제로 한 원고의 이 부분 주장은 이유 없다.
+4) 소결론
+결국 경계확정 시점이 아닌 다른 일자를 기준으로 한 감정평가액을 바탕으로 이 사건 토지에 대한 조정금을 산정한 이 사건 이의결정 통지는 위법하므로, 취소되어야 한다.
+라. 취소의 범위
+1) 부담금부과처분 취소소송에서 당사자가 제출한 자료에 의하여 적법하게 부과될 정당한 부담금액이 산출되는 때에는 그 정당한 금액을 초과하는 부분만 취소하여야 하지만, 그렇지 않은 경우에는 부과처분 전부를 취소할 수밖에 없는데(대법원 2016. 1. 28. 선고 2013두22451 판결 등 참조), 이와 같은 법리는 조정금 부과처분에도 적용된다고 할 것이다.
+2) 이 사건 이의결정 통지에 관하여 보면, 이 사건 토지에 관하여 그 경계확정일을 기준시점으로 한 감정평가액이 존재하지 아니하여 정당한 조정금액을 산정할 수 없으므로 이 사건 이의결정 통지를 전부 취소할 수밖에 없다.
+6. 결론
+그렇다면 이 사건 소 중 이 사건 처분의 무효확인을 구하는 부분은 부적법하여 각하하고, 이 사건 이의결정 통지의 취소를 구하는 부분은 이유 있어 인용하여야 한다. 제1심판결은 이와 결론을 달리하므로 제1심판결을 취소하고, 이 사건 처분의 무효확인을 구하는 부분을 각하하며, 이 법원에서 변경한 원고의 청구에 따라 이 사건 이의결정 통지를 취소하기로 하여, 주문과 같이 판결한다.
+판사 신동헌(재판장) 송진호 백승준
+상하급심 판례2
+별지
+별지
+미주
+[1] 원고는 2022. 1. 13.자 준비서면을 통해 이 사건 처분의 무효확인을 구하는 취지에는 그 취소를 구하는 취지도 포함되어 있다고 주장하므로, 그 제소기간의 준수 여부에 관하여 살펴본다. 한편, 위에서 본 바와 달리, 이 사행정소송법상 취소소송은 처분 등이 있음을 안 날부터 90일 이내에 제기하여야 하고, 처분 등이 있는 날부터 1년을 경과하면 제기하지 못한다(행정소송법 제20조 제1항, 제2항). 한편 청구취지를 교환적으로 변경하여 종전의 소가 취하되고 새로운 소가 제기된 것으로 보게 되는 경우에 새로운 소에 대한 제소기간의 준수 등은 원칙적으로 소의 변경이 있는 때를 기준으로 하여 판단된다(대법원 2004. 11. 25. 선고 2004두7023 판결, 대법원 2013. 7. 11. 선고 2011두27544 판결 등 참조).
+유사판례
+대전지방법원 2021. 2. 10. 선고 2019구합106995 판결 지적재조사조정금이의신청결정취소청구의소
+1. 처분의 경위 가. 원고는 대전 유성구 B동(이하 지번은 동 이하로만 표시한다) C, D, E 토지(이하 합하여 '이 사건 토지'라 한다)의 소유자이다. 나. 피고는 2015. 5. 26. 이 사건 토지 및 그 일원 총 248필지를 'F지구 지적재조사 사업지구'로 ...
+광주지방법원 2025. 2. 13. 선고 2024구합662 판결 지적재조사조정금이의신청결정처분취소
+1. 처분의 경위 가. 원고는 광주 동구 B 대 198m²(이하 '이 사건 종전 토지'라 한다)의 소유자이다. 나. 광주광역시는 2021. 10. 12. 이 사건 종전 토지가 포함된 광주 동구 C 일원 1,592필지(면적 428,448.5m²)를 지적재조사 사업지구(동...
+대전고등법원 2022. 11. 4. 선고 2022누10755 판결 지적재조사사업조장금이의신청기각처분취소청구의소
+1. 이 사건 소송의 경과 및 심판의 범위 가. 원고는, 피고의 2018. 1. 9. 지적재조사사업 조정금 수령통지를 비롯하여 2018. 6. 12. 지적재조사사업 조정금 이의신청 결과통지와 그에 따른 지적재조사사업 조정금 수 령통지의 취소를 구하는 이 사건 소를 제기...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금취소(2017누20958)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부산고등법원 제1행정부 판결
+사건2017누20958 조정금 취소
+원고,항소인A
+피고,피항소인부산광역시동래구청장
+제1심판결부산지방법원 2017. 2. 3. 선고 2016구합21986 판결
+변론종결2017. 4. 28.
+판결선고2017. 6. 2.
+주 문
+1. 원고의 항소를 기각한다.
+2. 항소비용은 원고가 부담한다.
+청구취지 및 항소취지
+제1심판결을 취소한다. 피고가 2015. 11. 16. 원고에 대하여 한 조정금 116,116,000원의 납부처분 중 82,706,000원을 초과하는 부분을 취소한다.
+이 유
+1. 제1심 판결의 인용
+이 법원이 이 사건에 관하여 설시할 이유는 당심에서의 원고의 주장에 대한 판단을 아래 제2항에서 추가하는 외에는 제1심 판결 이유와 같으므로, 행정소송법 제8조 제2항, 민사소송법 제420조 본문에 의하여 이를 인용한다.
+2. 추가 판단
+1) 원고의 주장
+피고의 지적재조사 과정에서 이 사건 토지의 지적공부상 면적이 증가됨으로써 원고가 원치 않게 토지를 취득하는 결과가 되었으므로 증가된 면적에 대한 조정금은 원고에게 유리하게 책정되어야 한다. 따라서 1 이 사건 토지의 조정금은 개별공시지가로 정한 가격이 가장 합리적이라고 할 것이고, 2 그렇지 않고 감정평가액에 의하는 경우에도 이 사건 토지와 E 토지는 임대차 만료시 지상 건축물이 철거되어야 하는 등 일시적으로 일단지로 이용되고 있는 것에 불과하므로 위치 등 조건 면에서 차이가 큰 위 2필지를 일단지로 보아 동일한 가격으로 평가한 것은 부당하다.
+2) 판단
+가) 1 주장에 대한 판단
+구 지적재조사에 관한 특별법(2016. 1.19. 법률 제13782, 13796호로 개정되기 전의 것, 약칭하여 '지적재조사법'이라고만 한다) 제20조 제3항은 "조정금은 지적소관청이 사업지구를 지정하여 고시하였을 때의 「부동산 가격공시 및 감정평가에 관한 법률」 에 따른 개별공시지가를 기준으로 정하거나, 같은 법 제28조에 따른 감정평가법인에 의뢰하여 평가한 감정평가액으로 산정한다."라고 규정하고 있는바, 피고는 이 사건 토지의 특성 등을 고려하여 부산광역시 동래구 지적재조사위원회의 심의를 거쳐 감정평가금액을 채택한 것으로 보이고, 2017. 4. 18. 법률 제14800호로 개정된 지적재조사 법에서 조정금을 원칙적으로 감정평가액에 의해 산정하도록 규정하고 있는 점 등에 비추어 피고가 이 사건 토지에 관한 조정금을 감정평가액으로 산정한 데에 잘못이 있다고 보기 어렵다.
+나) 2 주장에 대한 판단
+살피건대, 갑 제9호증의 기재에 의하면 2013. 9. 4. 이 사건 토지와 인접한 부산 동래구 E 토지(이하 '인접 토지'라고 하고, 위 2필지 토지를 합하여 '이 사건 토지 등'이라 한다) 등 2필지에 관하여 임차인 주식회사 I, 임대인 원고 및 인접 토지의 소유자인 H(이하 '원고 등'이라 한다) 사이에 체결된 토지 임대차계약의 임대차기간 종기를 2015. 2. 28.에서 2018. 8. 31.로 변경하는 변경계약이 체결된 사실이 인정된다. 그러나 한편 갑 제6호증, 을 제21, 24, 25, 26호증의 각 기재에 변론 전체의 취지를 더하면, 주식회사 I가 2004년에 이 사건 토지 등 지상에 일반철골구조물 2층 건물을 신축하여 상업용으로 사용하다가 2013년에 이를 철거하고 다시 2014년 일반철골구조물 4층 건물을 신축하여 상업용으로 사용하고 있는 사실이 인정되는바, 기존의 주식회사 I의 이 사건 토지 등 사용현황, 이 사건 토지와 인접 토지의 위치, 형상, 면적, 환경 등을 종합하여 고려하면, 이 사건 토지와 인접 토지가 일단의 토지로 이용되고 있는 상황이 사회적·경제적·행정적 측면에서 합리적이며 대상토지의 가치형성 측면에서 타당하다고 인정되는 관계에 있어 용도상 불가분의 관계에 있다고 봄이 상당하고(이 사건 토지와 인접 토지는 공시지가가 동일하며 이에 대하여 원고가 이의한 바도 없다), 주식회사 I와 원고 등 사이의 임대차계약의 갱신 가능성 등을 고려하면 이 사건 토지 등을 일단으로 이용하는 상황이 일시적인 것이라고 보기도 어렵다.
+3. 결론
+그렇다면 원고의 청구는 이유 없어 이를 기각할 것인바, 제1심 판결은 이와 결론을 같이하여 정당하므로 원고의 항소를 기각한다.
+판사 김형천(재판장) 채대원 주성화
+상하급심 판례2
+유사판례
+대전지방법원 2018. 10. 12. 선고 2018구합274 판결 지적재조사조정금감액청구
+1. 처분의 경위 가. 원고는 천안시 서북구 B 공장용지 4605m2(이하 '이 사건 토지'라 한다)의 소유자이다. 나. 천안시장은 2016. 6. 15. 구 지적재조사에 관한 특별법(2017. 4. 18. 법률 제14800호로 개정되기 전의 것, 이하 '구 지적재조사...
+서울고등법원 2019. 11. 22. 선고 2019누42558 판결 조정금납부등처분취소
+1. 처분의 경위 가. 원고는 인천 강화군 C 창고용지를 포함한 별지 1 조정금 내역표 기재 13필지 토지(이하 '이 사건 토지'라 하고, 각각의 토지를 지칭할 때는 지번만으로 특정한다)의 소유자이다. 나. 인천광역시장은 2015. 11. 5. 구 지적재조사에 관한 특...
+인천지방법원 2019. 4. 5. 선고 2017구합55347 판결 조정금납부등처분취소
+1. 처분의 경위 가. 원고 A은 인천 강화군 C 창고용지를 포함한 별지 조정금 내역표 기재 13필지의토지(이하 '원고 A 소유 토지'라고 한다)의 소유자이고, 원고 B은 D 도로(이하 '원고 B 소유 토지'라고 하고, '원고 A 소유 토지'와 '원고 B 소유 토지'를...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지적재조사조정금부과처분취소(2019구합288)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대구지방법원 제2행정부 판결
+사건2019구합288 지적재조사조정금부과처분취소
+원고1. A
+2.B
+3. C
+4. D
+피고대구광역시 동구청장
+변론종결2021. 4. 22.
+판결선고2021. 5. 13.
+주 문
+1. 피고가 2018. 12. 6. 원고 A에게 한 조정금 50,064,000원의 부과처분 중 46,656,000원을 초과하는 부분, 같은 날 B에게 한 조정금 35,425,200원의 부과처분 중 33,241,600원을 초과하는 부분, 같은 날 C에게 한 조정금 60,648,800원의 부과처분 중 55,986,400원을 초과하는 부분, 같은 날 D에게 한 조정금 138,109,000원의 부과처분 중 129,592,000원을 초과하는 부분을 모두 취소한다.
+2. 원고들의 나머지 청구를 모두 기각한다.
+3. 소송비용 중 3/4는 원고들이 부담하고, 나머지는 피고가 각 부담한다.
+청구취지
+피고가 2018. 12. 6. 원고 A에게 한 조정금 50,064,000원의 부과처분 중 37,440,000원을 초과하는 부분, 같은 날 원고 B에게 한 조정금 35,425,200원의 부과처분 중 24,570,000원을 초과하는 부분, 같은 날 원고 C에게 한 조정금 60,648,800원의 부과처분 중 43,992,000원을 초과하는 부분, 같은 날 원고 D에게 한 조정금 138,109,000원의 부과처분 중 97,695,000원을 초과하는 부분을 모두 취소한다.
+이 유
+1. 처분의 경위
+가. 피고의 지적재조사사업 실시
+1) 원고 A은 대구 동구 E 대 192m2의 소유자이고, 원고 B는 F대 345m2의 소유자이며, 원고 C은 G 대 149m2의 소유자이고, 원고 D는 H대 241m2의 소유자이다(이하 위 토지들을 지번으로 특정하고, 위 토지들을 통틀어 '이 사건 각 토지'라 한다).
+2) 피고는 2015. 12. 10. 이 사건 각 토지를 포함한 대구 동구 I 일대를 사업지구로 하여 J 지적재조사사업(이하 '이 사건 사업'이라 한다)의 실시계획을 수립하고, 토지 소유자들로부터 동의를 받아 이 사건 사업을 시행하였다.
+3) 대구광역시장은 2016. 3. 21. 지적재조사에 관한 특별법 제8조 제1항에 따라 대구 동구 I 일대(128필지, 38,682m2, 이하 '이 사건 사업지구'라 한다)를 2016년도 대구광역시 지적재조사 사업지구로 지정 고시하였다.
+나. 이 사건 토지의 경계 확정 및 면적 증가
+1) 대구광역시 동구 경계결정위원회는 2017. 12. 27. 지적재조사에 따른 이 사건 사업지구 내 토지들의 경계를 결정하였고, 그 결과 이 사건 각 토지의 면적이 아래 [경 계결정 필지조서 표] 중 '증가면적' 기재와 같이 증가되었다.
+[경계결정 필지조서표]
+이 유 표
+2) 피고는 2017. 12. 27. 원고들에게 위 경계결정의 내용을 통지하였고, 원고들은 이에 대하여 이의하지 아니하였다.
+3) 피고는 2018. 6. 21. 이 사건 사업을 완료하였음을 공고하였고, 그에 따라 토지대장상 표시된 이 사건 각 토지의 면적이 위 [경계결정 필지조서 표] 중 '확정면적' 기재로 변경되었으며, 2018. 6. 29. 이 사건 각 토지의 등기 표제부에 관하여 '지적재조사 완료'를 원인으로 면적을 위 [경계결정 필지조서 표] 중 '확정면적' 기재로 변경하는 등기가 마쳐졌다.
+다. 원고들에 대한 조정금 부과처분
+1) 피고는 2018. 8. 2. 원고들에게 위 [경계결정 필지조서 표] 중 각 '증가면적'에 대하여 아래와 같은 금액의 조정금을 부과하였고, 원고들은 피고에게 아래 각 조정금 액수가 부당하게 과다하는 이유로 이의신청서를 제출하였다.
+이 유 표
+이 유 표
+2) 이에 피고는 주식회사 K, 주식회사 L에 기준시점을 2018. 6. 20.로 하여 이 사건 각 토지에 대한 감정평가를 의뢰하였고, 대구광역시 동구 지적재조사위원회는 위두 감정평가결과를 산술평균하여 조정금을 아래와 같이 각 일부 감액한 금액으로 심의·의결하였다. 피고는 2018. 12. 6. 원고들의 조정금을 위 이의신청심의결과에 따른 각 조정금으로 변경하고, 원고들에게 이를 통지하였다(이하 '이 사건 처분'이라 한다).
+이 유 표
+라. 감정인 M이 2018. 6. 21.을 기준으로 산정한 이 사건 각 토지의 m2당 감정평가액은 780,000원이다.
+[인정근거] 다툼 없는 사실, 갑 제1 내지 4호증, 을 제1 내지 9호증의 각 기재, 이법원의 감정인 M에 대한 감정촉탁결과(이하 '이 법원의 감정촉탁결과'라 한다)변론 전체의 취지
+2. 이 사건의 처분의 적법 여부
+가. 원고들의 주장
+이 사건 처분은 아래와 같은 이유에서 위법하므로 취소되어야 한다.
+1) 피고는 이 사건 처분을 함에 있어 이 사건 각 토지에 대한 공정하고 객관적인 가치 평가절차를 거쳐 합리적인 기대 범위 내에서 공평하게 부과하여야 함에도 통상적인 기대 범위를 벗어나 자의적으로 평가액을 지나치게 높게 책정함으로써 형평의 원칙을 위반하였다.
+2) 이 사건 처분에서 정한 조정금은 원고들의 재산권에 직접적이고 막대한 지장을 초래하는 것으로서 재량권을 일탈·남용하였다.
+나. 관계 법령
+별지 관계 법령 기재와 같다.
+다. 판단
+1) 이의신청으로 이루어진 감정결과가 자의적인 방법으로 이루어졌는지 여부
+살피건대 앞서 든 증거들 및 변론 전체의 취지에 의하면, 피고로부터 감정을 의뢰받은 주식회사 K, 주식회사 L은 이 사건 토지와 용도지역·이용상황·주변환경 등이 비슷한 토지를 비교표준지로 선정하여 감정을 실시하였는데, 감정과정에서 원고들이 주장하는 것과 같은 위법 사항은 존재하지 않은 것으로 보이고, 달리 위 감정법인들이 자의적인 방법으로 감정하였음을 인정할 증거도 없다. 따라서 원고들의 이 부분 주장은 이유 없다.
+2) 재량권 일탈·남용 여부
+지적재조사법은 경계 확정으로 지적공부상의 면적이 증감된 경우에는 필지별 면적 증감내역을 기준으로 조정금을 부과하거나 지급할 의무를 지적소관청에 부과하고 있고(제20조 제1항), 그 조정금은 감정평가업자가 평가한 감정평가액으로 산정하도록 하고 있다(제20조 제3항).
+위와 같은 법률규정에 의하면, 지적재조사법은 지적소관청에게 조정금의 부과여부 및 그 액수에 관하여 어떠한 재량권을 부여하고 있다고 볼 수 없으므로, 이 사건 처분은 기속행위에 해당한다. 따라서 이와 다른 전제에 선 원고들의 이 부분 주장도 이유 없다.
+3) 이 사건 각 토지에 대한 정당한 조정금의 액수 산정
+지적재조사법 제20조 제3항에 의하면, 조정금도 경계가 확정된 시점을 기준으로 감정평가 및 감정평가사에 관한 법률에 따른 감정평가업자가 평가한 감정평가액으로 산정하도록 정하고 있는바, 조정금 부과의 기초가 된 감정평가와 법원감정인의 감정평가가 모두 위법사유가 없는 경우에는 그 중 어느 감정평가의 품등비교 내용 등에 오류가 있음을 인정할 자료가 없는 이상, 각 감정평가 중 어느 것을 더 신뢰하는가 하는 것은 사실심 법원의 재량에 속한다고 봄이 타당하다(대법원 2005. 1. 28. 선고 2002두4679 판결이 유 표 등 참조).
+살피건대, 앞서 든 증거들에 변론 전체의 취지를 더하여 인정되는 다음과 같은 사정들, 즉 1 주식회사 K, 주식회사 L, 이 법원의 감정인은 모두 이 사건 토지의 접근조건, 환경조건, 획지조건, 행정적조건, 기타조건에 관하여 각 세부사항별로 상세하게 평가하였고, 그 밖의 요인 보정치 산정에 있어서도 용도지역 등을 고려하여 거래사례를 선정하고 이 사건 각 비교표준지와의 개별요인 비교·평가를 거쳐 감정결과에 반영한 점, 2 이와 같은 개별요인 분석은 객관적인 측정절차에 따른 구체적인 수치로의 확정이 불가능하며 감정평가업자의 전문적인 견해에 따라 다소 차이가 있을 수밖에 없는 점 등을 고려하면, 이 사건 처분의 조정금 산정을 위한 주식회사 K, 주식회사 L의 각 감정평가와 이 법원의 감정촉탁결과는 모두 관련 법령에 따라 조정금을 적절히 산정한 것으로 보이고 달리 위 각 감정의 비교표준지 및 거래사례의 선정, 품등비교 내용, 방식 등에 오류가 있음을 인정할 자료가 없으므로 위 각 감정은 모두 적법하다고 할 것이나, 주식회사 K, 주식회사 L의 각 감정결과는 조정금에 이의신청 있는 토지를 일괄하여 평가한 반면 이 법원의 감정촉탁결과는 이 사건 각 토지의 특성을 구체적으로 살펴보고 이를 바탕으로 감정평가가 이루어진 것으로 보여 이 사건 각 토지의 특성과 가격형성상 제반요인 등을 보다 더 적절히 반영하였다고 판단되므로 이 법원의 감정촉탁결과에 따라 조정금을 산정하기로 한다.
+4) 이 사건 처분의 위법 및 취소 범위
+따라서 피고가 원고들에게 부과하여야 할 이 사건 각 토지에 대한 정당한 조정 금은 아래와 같으므로, 이 사건 처분 중 아래 각 금액을 초과하는 부분은 위법하여 취소되어야 한다.
+3. 결론
+그렇다면 원고들의 이 사건 청구는 위 인정범위 내에서 이유 있어 이를 인용하고, 나머지는 이유 없어 이를 모두 기각한다.
+판사 이진관(재판장) 박가연 이도경
+별지
+별지
+유사판례
+대구지방법원 2020. 5. 20. 선고 2019구합271 판결 지적재조사조정금부과처분취소
+1. 처분의 경위 가. 피고의 지적재조사사업 실시 1) 원고는 대구 동구 B 대 321㎡(이하 '이 사건 토지'라 한다)의 소유자이다. 2) 피고는 2015. 12. 10. 이 사건 토지를 포함한 대구 동구 C 일원을 사업지구로 하여 D 지적재조사사업(이하 '이 사건 ...
+부산지방법원 2017. 4. 13. 선고 2016구합1166 판결 지적재조사조정금부과처분취소
+1. 처분의 경위 가. 부산광역시장은 2013. 10. 23. 구 지적재조사에 관한 특별법(2016. 1. 19. 법률 제13782호로 개정되기 전의 것, 이하 '지적재조사법'이라 한다) 제8조 제1항에 따라 E 지구(부산 해운대구 F 일원 250필지 40,635m2)...
+부산지방법원 2024. 8. 22. 선고 2023구합21526 판결 지적재조사조정금부과처분취소
+1. 처분의 경위 가. 피고의 지적재조사사업 실시 (1) 피고는 2020. 9. 14. I지구 지적재조사사업(이하 '이 사건 사업'이라 함)의 실시계획을 수립하였고, 부산광역시장은 2021. 3. 31. 부산 금정구 J 일원을 I지구 지적재조사 지구로 지정하여 고시하였...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정금청구(2017구합6785)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9766,6 +10385,37 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F2225"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -9787,7 +10437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9800,6 +10450,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11615,7 +12268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF1320A-8011-43B2-81F0-3F2013FBE1D1}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.5" style="1" bestFit="1" customWidth="1"/>
@@ -11929,9 +12582,133 @@
         <v>448</v>
       </c>
     </row>
+    <row r="39" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA00B5BA-E6CB-44B7-B79D-D84CEB100CBA}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D450B221-6928-49B5-85E2-0BDC0C6ADE8C}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>